--- a/data/output/workbook/2026-06-29.xlsx
+++ b/data/output/workbook/2026-06-29.xlsx
@@ -550,7 +550,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9410700"/>
+    <ext cx="10125075" cy="10048875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -580,7 +580,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9810750"/>
+    <ext cx="10125075" cy="9401175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29 04:21</t>
+          <t>2026-06-29 09:09</t>
         </is>
       </c>
     </row>
@@ -4529,7 +4529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:Q78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4546,823 +4546,823 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="28" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="28" t="inlineStr">
         <is>
           <t>Cincinnati Reds offense vs Milwaukee Brewers defense</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="29" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B61" s="29" t="inlineStr">
+      <c r="B65" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C61" s="29" t="inlineStr">
+      <c r="C65" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D61" s="29" t="inlineStr">
+      <c r="D65" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E61" s="29" t="inlineStr">
+      <c r="E65" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F61" s="29" t="inlineStr">
+      <c r="F65" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G61" s="29" t="inlineStr">
+      <c r="G65" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H61" s="29" t="inlineStr">
+      <c r="H65" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I61" s="29" t="inlineStr">
+      <c r="I65" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J61" s="29" t="inlineStr">
+      <c r="J65" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K61" s="29" t="inlineStr">
+      <c r="K65" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L61" s="29" t="inlineStr">
+      <c r="L65" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M61" s="29" t="inlineStr">
+      <c r="M65" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N61" s="29" t="inlineStr">
+      <c r="N65" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O61" s="29" t="inlineStr">
+      <c r="O65" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P61" s="29" t="inlineStr">
+      <c r="P65" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q61" s="29" t="inlineStr">
+      <c r="Q65" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B62" s="31" t="n">
-        <v>4.132</v>
-      </c>
-      <c r="C62" s="31" t="n">
-        <v>4.433</v>
-      </c>
-      <c r="D62" s="31" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="E62" s="31" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="F62" s="31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="G62" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="H62" s="32" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I62" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J62" s="35" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K62" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="L62" s="31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M62" s="31" t="n">
-        <v>3.267</v>
-      </c>
-      <c r="N62" s="31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O62" s="31" t="n">
-        <v>4.033</v>
-      </c>
-      <c r="P62" s="31" t="n">
-        <v>3.784</v>
-      </c>
-      <c r="Q62" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B63" s="31" t="n">
-        <v>7.216</v>
-      </c>
-      <c r="C63" s="31" t="n">
-        <v>7.345</v>
-      </c>
-      <c r="D63" s="31" t="n">
-        <v>7.632</v>
-      </c>
-      <c r="E63" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="F63" s="31" t="n">
-        <v>7.667</v>
-      </c>
-      <c r="G63" s="31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H63" s="35" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I63" s="31" t="inlineStr"/>
-      <c r="J63" s="32" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="K63" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L63" s="31" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="M63" s="31" t="n">
-        <v>6.308</v>
-      </c>
-      <c r="N63" s="31" t="n">
-        <v>6.722</v>
-      </c>
-      <c r="O63" s="31" t="n">
-        <v>7.536</v>
-      </c>
-      <c r="P63" s="31" t="n">
-        <v>7.371</v>
-      </c>
-      <c r="Q63" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="30" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B64" s="31" t="n">
-        <v>1.216</v>
-      </c>
-      <c r="C64" s="31" t="n">
-        <v>1.241</v>
-      </c>
-      <c r="D64" s="31" t="n">
-        <v>1.263</v>
-      </c>
-      <c r="E64" s="31" t="n">
-        <v>1.643</v>
-      </c>
-      <c r="F64" s="31" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="G64" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H64" s="35" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="I64" s="31" t="inlineStr"/>
-      <c r="J64" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K64" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L64" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M64" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N64" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O64" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P64" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q64" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B65" s="31" t="n">
-        <v>9.27</v>
-      </c>
-      <c r="C65" s="31" t="n">
-        <v>9.103</v>
-      </c>
-      <c r="D65" s="31" t="n">
-        <v>9.420999999999999</v>
-      </c>
-      <c r="E65" s="31" t="n">
-        <v>9.286</v>
-      </c>
-      <c r="F65" s="31" t="n">
-        <v>8.888999999999999</v>
-      </c>
-      <c r="G65" s="31" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H65" s="33" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="I65" s="31" t="inlineStr"/>
-      <c r="J65" s="32" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K65" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="L65" s="31" t="n">
-        <v>10.625</v>
-      </c>
-      <c r="M65" s="31" t="n">
-        <v>10.538</v>
-      </c>
-      <c r="N65" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="O65" s="31" t="n">
-        <v>8.929</v>
-      </c>
-      <c r="P65" s="31" t="n">
-        <v>9.571</v>
-      </c>
-      <c r="Q65" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="30" t="inlineStr">
         <is>
-          <t>1st Inn R/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B66" s="31" t="n">
-        <v>0.595</v>
+        <v>4.132</v>
       </c>
       <c r="C66" s="31" t="n">
-        <v>0.621</v>
+        <v>4.433</v>
       </c>
       <c r="D66" s="31" t="n">
-        <v>0.421</v>
+        <v>4.65</v>
       </c>
       <c r="E66" s="31" t="n">
-        <v>0.429</v>
+        <v>4.867</v>
       </c>
       <c r="F66" s="31" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="G66" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="33" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="I66" s="31" t="inlineStr"/>
-      <c r="J66" s="32" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="H66" s="32" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I66" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J66" s="35" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K66" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L66" s="31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M66" s="31" t="n">
+        <v>3.267</v>
+      </c>
+      <c r="N66" s="31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O66" s="31" t="n">
+        <v>4.033</v>
+      </c>
+      <c r="P66" s="31" t="n">
+        <v>3.784</v>
+      </c>
+      <c r="Q66" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B67" s="31" t="n">
+        <v>7.216</v>
+      </c>
+      <c r="C67" s="31" t="n">
+        <v>7.345</v>
+      </c>
+      <c r="D67" s="31" t="n">
+        <v>7.632</v>
+      </c>
+      <c r="E67" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="F67" s="31" t="n">
+        <v>7.667</v>
+      </c>
+      <c r="G67" s="31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H67" s="35" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="I67" s="31" t="inlineStr"/>
+      <c r="J67" s="32" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="K67" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L67" s="31" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="M67" s="31" t="n">
+        <v>6.308</v>
+      </c>
+      <c r="N67" s="31" t="n">
+        <v>6.722</v>
+      </c>
+      <c r="O67" s="31" t="n">
+        <v>7.536</v>
+      </c>
+      <c r="P67" s="31" t="n">
+        <v>7.371</v>
+      </c>
+      <c r="Q67" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B68" s="31" t="n">
+        <v>1.216</v>
+      </c>
+      <c r="C68" s="31" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="D68" s="31" t="n">
+        <v>1.263</v>
+      </c>
+      <c r="E68" s="31" t="n">
+        <v>1.643</v>
+      </c>
+      <c r="F68" s="31" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="G68" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="35" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="I68" s="31" t="inlineStr"/>
+      <c r="J68" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q68" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="C69" s="31" t="n">
+        <v>9.103</v>
+      </c>
+      <c r="D69" s="31" t="n">
+        <v>9.420999999999999</v>
+      </c>
+      <c r="E69" s="31" t="n">
+        <v>9.286</v>
+      </c>
+      <c r="F69" s="31" t="n">
+        <v>8.888999999999999</v>
+      </c>
+      <c r="G69" s="31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="I69" s="31" t="inlineStr"/>
+      <c r="J69" s="32" t="inlineStr">
         <is>
           <t>5th</t>
         </is>
       </c>
-      <c r="K66" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="31" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="M66" s="31" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="N66" s="31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O66" s="31" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="P66" s="31" t="n">
-        <v>0.486</v>
-      </c>
-      <c r="Q66" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="28" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers offense vs Cincinnati Reds defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="K69" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="L69" s="31" t="n">
+        <v>10.625</v>
+      </c>
+      <c r="M69" s="31" t="n">
+        <v>10.538</v>
+      </c>
+      <c r="N69" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="O69" s="31" t="n">
+        <v>8.929</v>
+      </c>
+      <c r="P69" s="31" t="n">
+        <v>9.571</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B70" s="31" t="n">
-        <v>4.703</v>
+        <v>0.595</v>
       </c>
       <c r="C70" s="31" t="n">
-        <v>4.133</v>
+        <v>0.621</v>
       </c>
       <c r="D70" s="31" t="n">
-        <v>4.25</v>
+        <v>0.421</v>
       </c>
       <c r="E70" s="31" t="n">
-        <v>3.733</v>
+        <v>0.429</v>
       </c>
       <c r="F70" s="31" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="G70" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J70" s="33" t="inlineStr">
-        <is>
-          <t>25th</t>
+        <v>0</v>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr"/>
+      <c r="J70" s="32" t="inlineStr">
+        <is>
+          <t>5th</t>
         </is>
       </c>
       <c r="K70" s="31" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="L70" s="31" t="n">
-        <v>6</v>
+        <v>0.125</v>
       </c>
       <c r="M70" s="31" t="n">
-        <v>6</v>
+        <v>0.231</v>
       </c>
       <c r="N70" s="31" t="n">
-        <v>5.15</v>
+        <v>0.333</v>
       </c>
       <c r="O70" s="31" t="n">
-        <v>4.933</v>
+        <v>0.357</v>
       </c>
       <c r="P70" s="31" t="n">
-        <v>4.658</v>
+        <v>0.486</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B71" s="31" t="n">
-        <v>7.629</v>
-      </c>
-      <c r="C71" s="31" t="n">
-        <v>7.143</v>
-      </c>
-      <c r="D71" s="31" t="n">
-        <v>7.389</v>
-      </c>
-      <c r="E71" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="F71" s="31" t="n">
-        <v>7.625</v>
-      </c>
-      <c r="G71" s="31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J71" s="33" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="L71" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="M71" s="31" t="n">
-        <v>8.714</v>
-      </c>
-      <c r="N71" s="31" t="n">
-        <v>8.263</v>
-      </c>
-      <c r="O71" s="31" t="n">
-        <v>8.207000000000001</v>
-      </c>
-      <c r="P71" s="31" t="n">
-        <v>8.054</v>
-      </c>
-      <c r="Q71" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="30" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B72" s="31" t="n">
-        <v>0.657</v>
-      </c>
-      <c r="C72" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D72" s="31" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="E72" s="31" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="F72" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G72" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H72" s="33" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I72" s="31" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q72" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
+      <c r="A72" s="28" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers offense vs Cincinnati Reds defense</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B73" s="31" t="n">
-        <v>8.228999999999999</v>
-      </c>
-      <c r="C73" s="31" t="n">
-        <v>8.179</v>
-      </c>
-      <c r="D73" s="31" t="n">
-        <v>7.944</v>
-      </c>
-      <c r="E73" s="31" t="n">
-        <v>8.077</v>
-      </c>
-      <c r="F73" s="31" t="n">
-        <v>7.875</v>
-      </c>
-      <c r="G73" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I73" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L73" s="31" t="n">
-        <v>6.667</v>
-      </c>
-      <c r="M73" s="31" t="n">
-        <v>7.143</v>
-      </c>
-      <c r="N73" s="31" t="n">
-        <v>7.105</v>
-      </c>
-      <c r="O73" s="31" t="n">
-        <v>6.966</v>
-      </c>
-      <c r="P73" s="31" t="n">
-        <v>7.432</v>
-      </c>
-      <c r="Q73" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+      <c r="A73" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B73" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C73" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D73" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E73" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F73" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G73" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H73" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I73" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J73" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K73" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L73" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M73" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N73" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O73" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P73" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q73" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>4.703</v>
+      </c>
+      <c r="C74" s="31" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="D74" s="31" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E74" s="31" t="n">
+        <v>3.733</v>
+      </c>
+      <c r="F74" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G74" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L74" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="M74" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="N74" s="31" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="O74" s="31" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>4.658</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B75" s="31" t="n">
+        <v>7.629</v>
+      </c>
+      <c r="C75" s="31" t="n">
+        <v>7.143</v>
+      </c>
+      <c r="D75" s="31" t="n">
+        <v>7.389</v>
+      </c>
+      <c r="E75" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="F75" s="31" t="n">
+        <v>7.625</v>
+      </c>
+      <c r="G75" s="31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H75" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="I75" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J75" s="33" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K75" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="L75" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="M75" s="31" t="n">
+        <v>8.714</v>
+      </c>
+      <c r="N75" s="31" t="n">
+        <v>8.263</v>
+      </c>
+      <c r="O75" s="31" t="n">
+        <v>8.207000000000001</v>
+      </c>
+      <c r="P75" s="31" t="n">
+        <v>8.054</v>
+      </c>
+      <c r="Q75" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B76" s="31" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="C76" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D76" s="31" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="E76" s="31" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="F76" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G76" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H76" s="33" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="I76" s="31" t="inlineStr"/>
+      <c r="J76" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q76" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B77" s="31" t="n">
+        <v>8.228999999999999</v>
+      </c>
+      <c r="C77" s="31" t="n">
+        <v>8.179</v>
+      </c>
+      <c r="D77" s="31" t="n">
+        <v>7.944</v>
+      </c>
+      <c r="E77" s="31" t="n">
+        <v>8.077</v>
+      </c>
+      <c r="F77" s="31" t="n">
+        <v>7.875</v>
+      </c>
+      <c r="G77" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I77" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K77" s="31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L77" s="31" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="M77" s="31" t="n">
+        <v>7.143</v>
+      </c>
+      <c r="N77" s="31" t="n">
+        <v>7.105</v>
+      </c>
+      <c r="O77" s="31" t="n">
+        <v>6.966</v>
+      </c>
+      <c r="P77" s="31" t="n">
+        <v>7.432</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="31" t="n">
+      <c r="B78" s="31" t="n">
         <v>0.629</v>
       </c>
-      <c r="C74" s="31" t="n">
+      <c r="C78" s="31" t="n">
         <v>0.536</v>
       </c>
-      <c r="D74" s="31" t="n">
+      <c r="D78" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="E74" s="31" t="n">
+      <c r="E78" s="31" t="n">
         <v>0.6919999999999999</v>
       </c>
-      <c r="F74" s="31" t="n">
+      <c r="F78" s="31" t="n">
         <v>1.125</v>
       </c>
-      <c r="G74" s="31" t="n">
+      <c r="G78" s="31" t="n">
         <v>1.6</v>
       </c>
-      <c r="H74" s="32" t="inlineStr">
+      <c r="H78" s="32" t="inlineStr">
         <is>
           <t>2nd</t>
         </is>
       </c>
-      <c r="I74" s="31" t="inlineStr">
+      <c r="I78" s="31" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J74" s="32" t="inlineStr">
+      <c r="J78" s="32" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
       </c>
-      <c r="K74" s="31" t="n">
+      <c r="K78" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="L74" s="31" t="n">
+      <c r="L78" s="31" t="n">
         <v>0.111</v>
       </c>
-      <c r="M74" s="31" t="n">
+      <c r="M78" s="31" t="n">
         <v>0.286</v>
       </c>
-      <c r="N74" s="31" t="n">
+      <c r="N78" s="31" t="n">
         <v>0.421</v>
       </c>
-      <c r="O74" s="31" t="n">
+      <c r="O78" s="31" t="n">
         <v>0.483</v>
       </c>
-      <c r="P74" s="31" t="n">
+      <c r="P78" s="31" t="n">
         <v>0.459</v>
       </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="Q78" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5381,7 +5381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5398,815 +5398,815 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="28" t="inlineStr">
+        <is>
+          <t>San Diego Padres offense vs Chicago Cubs defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B61" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C61" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D61" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E61" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F61" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G61" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H61" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I61" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J61" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K61" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L61" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M61" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N61" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O61" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P61" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q61" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B62" s="31" t="n">
+        <v>4.279</v>
+      </c>
+      <c r="C62" s="31" t="n">
+        <v>4.433</v>
+      </c>
+      <c r="D62" s="31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="E62" s="31" t="n">
+        <v>3.733</v>
+      </c>
+      <c r="F62" s="31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G62" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="H62" s="35" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="I62" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J62" s="33" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K62" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="L62" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M62" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="N62" s="31" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="O62" s="31" t="n">
+        <v>4.767</v>
+      </c>
+      <c r="P62" s="31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q62" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
     <row r="63">
-      <c r="A63" s="28" t="inlineStr">
-        <is>
-          <t>San Diego Padres offense vs Chicago Cubs defense</t>
+      <c r="A63" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B63" s="31" t="n">
+        <v>7.139</v>
+      </c>
+      <c r="C63" s="31" t="n">
+        <v>7.167</v>
+      </c>
+      <c r="D63" s="31" t="n">
+        <v>6.444</v>
+      </c>
+      <c r="E63" s="31" t="n">
+        <v>6.357</v>
+      </c>
+      <c r="F63" s="31" t="n">
+        <v>5.111</v>
+      </c>
+      <c r="G63" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H63" s="33" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="I63" s="31" t="inlineStr"/>
+      <c r="J63" s="33" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K63" s="31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L63" s="31" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M63" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="N63" s="31" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O63" s="31" t="n">
+        <v>7.966</v>
+      </c>
+      <c r="P63" s="31" t="n">
+        <v>7.595</v>
+      </c>
+      <c r="Q63" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B64" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C64" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D64" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E64" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F64" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G64" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H64" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I64" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J64" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K64" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L64" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M64" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N64" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O64" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P64" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q64" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A64" s="30" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B64" s="31" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="C64" s="31" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="D64" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="31" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="F64" s="31" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="G64" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="35" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I64" s="31" t="inlineStr"/>
+      <c r="J64" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K64" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L64" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M64" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N64" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O64" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P64" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q64" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B65" s="31" t="n">
-        <v>4.279</v>
+        <v>8.138999999999999</v>
       </c>
       <c r="C65" s="31" t="n">
-        <v>4.433</v>
+        <v>8.042</v>
       </c>
       <c r="D65" s="31" t="n">
-        <v>3.55</v>
+        <v>9</v>
       </c>
       <c r="E65" s="31" t="n">
-        <v>3.733</v>
+        <v>8.714</v>
       </c>
       <c r="F65" s="31" t="n">
-        <v>2.9</v>
+        <v>7.889</v>
       </c>
       <c r="G65" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="H65" s="35" t="inlineStr">
-        <is>
-          <t>19th</t>
+        <v>7.2</v>
+      </c>
+      <c r="H65" s="32" t="inlineStr">
+        <is>
+          <t>5th</t>
         </is>
       </c>
       <c r="I65" s="31" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="J65" s="33" t="inlineStr">
         <is>
-          <t>24th</t>
+          <t>25th</t>
         </is>
       </c>
       <c r="K65" s="31" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="L65" s="31" t="n">
-        <v>4.6</v>
+        <v>7.3</v>
       </c>
       <c r="M65" s="31" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="N65" s="31" t="n">
-        <v>4.25</v>
+        <v>7.35</v>
       </c>
       <c r="O65" s="31" t="n">
-        <v>4.767</v>
+        <v>7.552</v>
       </c>
       <c r="P65" s="31" t="n">
-        <v>4.5</v>
+        <v>7.838</v>
       </c>
       <c r="Q65" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="30" t="inlineStr">
         <is>
+          <t>1st Inn R/G</t>
+        </is>
+      </c>
+      <c r="B66" s="31" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="C66" s="31" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="D66" s="31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E66" s="31" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="F66" s="31" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="G66" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H66" s="35" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="I66" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J66" s="33" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="K66" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L66" s="31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M66" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N66" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O66" s="31" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="P66" s="31" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="Q66" s="34" t="inlineStr">
+        <is>
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="28" t="inlineStr">
+        <is>
+          <t>Chicago Cubs offense vs San Diego Padres defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="n">
+        <v>4.947</v>
+      </c>
+      <c r="C70" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D70" s="31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E70" s="31" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="F70" s="31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G70" s="31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr"/>
+      <c r="J70" s="32" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L70" s="31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M70" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N70" s="31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O70" s="31" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="P70" s="31" t="n">
+        <v>3.674</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="30" t="inlineStr">
+        <is>
           <t>Hits/G</t>
         </is>
       </c>
-      <c r="B66" s="31" t="n">
-        <v>7.139</v>
-      </c>
-      <c r="C66" s="31" t="n">
-        <v>7.167</v>
-      </c>
-      <c r="D66" s="31" t="n">
-        <v>6.444</v>
-      </c>
-      <c r="E66" s="31" t="n">
-        <v>6.357</v>
-      </c>
-      <c r="F66" s="31" t="n">
-        <v>5.111</v>
-      </c>
-      <c r="G66" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H66" s="33" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="I66" s="31" t="inlineStr"/>
-      <c r="J66" s="33" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K66" s="31" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L66" s="31" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="M66" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="N66" s="31" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O66" s="31" t="n">
-        <v>7.966</v>
-      </c>
-      <c r="P66" s="31" t="n">
-        <v>7.595</v>
-      </c>
-      <c r="Q66" s="34" t="inlineStr">
+      <c r="B71" s="31" t="n">
+        <v>8.432</v>
+      </c>
+      <c r="C71" s="31" t="n">
+        <v>8.965999999999999</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G71" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L71" s="31" t="n">
+        <v>7.778</v>
+      </c>
+      <c r="M71" s="31" t="n">
+        <v>8.856999999999999</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>8.444000000000001</v>
+      </c>
+      <c r="O71" s="31" t="n">
+        <v>8.125</v>
+      </c>
+      <c r="P71" s="31" t="n">
+        <v>8.111000000000001</v>
+      </c>
+      <c r="Q71" s="34" t="inlineStr">
         <is>
           <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="30" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="30" t="inlineStr">
         <is>
           <t>HR/G</t>
         </is>
       </c>
-      <c r="B67" s="31" t="n">
-        <v>0.972</v>
-      </c>
-      <c r="C67" s="31" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="D67" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" s="31" t="n">
-        <v>1.286</v>
-      </c>
-      <c r="F67" s="31" t="n">
-        <v>1.111</v>
-      </c>
-      <c r="G67" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67" s="35" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I67" s="31" t="inlineStr"/>
-      <c r="J67" s="34" t="inlineStr">
+      <c r="B72" s="31" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="C72" s="31" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="D72" s="31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E72" s="31" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="F72" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G72" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H72" s="33" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="I72" s="31" t="inlineStr"/>
+      <c r="J72" s="34" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K67" s="31" t="inlineStr">
+      <c r="K72" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L67" s="31" t="inlineStr">
+      <c r="L72" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M67" s="31" t="inlineStr">
+      <c r="M72" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N67" s="31" t="inlineStr">
+      <c r="N72" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O67" s="31" t="inlineStr">
+      <c r="O72" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P67" s="31" t="inlineStr">
+      <c r="P72" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q67" s="34" t="inlineStr">
+      <c r="Q72" s="34" t="inlineStr">
         <is>
           <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B68" s="31" t="n">
-        <v>8.138999999999999</v>
-      </c>
-      <c r="C68" s="31" t="n">
-        <v>8.042</v>
-      </c>
-      <c r="D68" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="E68" s="31" t="n">
-        <v>8.714</v>
-      </c>
-      <c r="F68" s="31" t="n">
-        <v>7.889</v>
-      </c>
-      <c r="G68" s="31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H68" s="32" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="I68" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J68" s="33" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K68" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L68" s="31" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="M68" s="31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N68" s="31" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="O68" s="31" t="n">
-        <v>7.552</v>
-      </c>
-      <c r="P68" s="31" t="n">
-        <v>7.838</v>
-      </c>
-      <c r="Q68" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B69" s="31" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="C69" s="31" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="D69" s="31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="E69" s="31" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="F69" s="31" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="G69" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="I69" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J69" s="33" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="K69" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L69" s="31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M69" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N69" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O69" s="31" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="P69" s="31" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="Q69" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="28" t="inlineStr">
-        <is>
-          <t>Chicago Cubs offense vs San Diego Padres defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B72" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C72" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D72" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E72" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F72" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G72" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H72" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I72" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J72" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K72" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L72" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M72" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N72" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O72" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P72" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q72" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>4.947</v>
+        <v>8.541</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>5.2</v>
+        <v>8.516999999999999</v>
       </c>
       <c r="D73" s="31" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E73" s="31" t="n">
-        <v>4.267</v>
+        <v>8.6</v>
       </c>
       <c r="F73" s="31" t="n">
-        <v>3.2</v>
+        <v>8.5</v>
       </c>
       <c r="G73" s="31" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="H73" s="33" t="inlineStr">
         <is>
-          <t>30th</t>
+          <t>25th</t>
         </is>
       </c>
       <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="32" t="inlineStr">
-        <is>
-          <t>4th</t>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>24th</t>
         </is>
       </c>
       <c r="K73" s="31" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="L73" s="31" t="n">
-        <v>3.4</v>
+        <v>8.333</v>
       </c>
       <c r="M73" s="31" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="N73" s="31" t="n">
-        <v>3.95</v>
+        <v>8.167</v>
       </c>
       <c r="O73" s="31" t="n">
-        <v>3.667</v>
+        <v>8.708</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>3.674</v>
+        <v>8.805999999999999</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="31" t="n">
-        <v>8.432</v>
+        <v>0.297</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>8.965999999999999</v>
+        <v>0.276</v>
       </c>
       <c r="D74" s="31" t="n">
-        <v>8.699999999999999</v>
+        <v>0.35</v>
       </c>
       <c r="E74" s="31" t="n">
-        <v>8.333</v>
+        <v>0.2</v>
       </c>
       <c r="F74" s="31" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="G74" s="31" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="H74" s="33" t="inlineStr">
         <is>
-          <t>30th</t>
+          <t>29th</t>
         </is>
       </c>
       <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>19th</t>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>25th</t>
         </is>
       </c>
       <c r="K74" s="31" t="n">
-        <v>7.8</v>
+        <v>1</v>
       </c>
       <c r="L74" s="31" t="n">
-        <v>7.778</v>
+        <v>0.556</v>
       </c>
       <c r="M74" s="31" t="n">
-        <v>8.856999999999999</v>
+        <v>0.429</v>
       </c>
       <c r="N74" s="31" t="n">
-        <v>8.444000000000001</v>
+        <v>0.333</v>
       </c>
       <c r="O74" s="31" t="n">
-        <v>8.125</v>
+        <v>0.333</v>
       </c>
       <c r="P74" s="31" t="n">
-        <v>8.111000000000001</v>
+        <v>0.417</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B75" s="31" t="n">
-        <v>1.135</v>
-      </c>
-      <c r="C75" s="31" t="n">
-        <v>1.241</v>
-      </c>
-      <c r="D75" s="31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E75" s="31" t="n">
-        <v>1.133</v>
-      </c>
-      <c r="F75" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G75" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr"/>
-      <c r="J75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B76" s="31" t="n">
-        <v>8.541</v>
-      </c>
-      <c r="C76" s="31" t="n">
-        <v>8.516999999999999</v>
-      </c>
-      <c r="D76" s="31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="E76" s="31" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="F76" s="31" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G76" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="H76" s="33" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="I76" s="31" t="inlineStr"/>
-      <c r="J76" s="33" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K76" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L76" s="31" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="M76" s="31" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="N76" s="31" t="n">
-        <v>8.167</v>
-      </c>
-      <c r="O76" s="31" t="n">
-        <v>8.708</v>
-      </c>
-      <c r="P76" s="31" t="n">
-        <v>8.805999999999999</v>
-      </c>
-      <c r="Q76" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B77" s="31" t="n">
-        <v>0.297</v>
-      </c>
-      <c r="C77" s="31" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="D77" s="31" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E77" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F77" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G77" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="33" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="I77" s="31" t="inlineStr"/>
-      <c r="J77" s="33" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K77" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L77" s="31" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="M77" s="31" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="N77" s="31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O77" s="31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="P77" s="31" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="Q77" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7995,7 +7995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8139,13 +8139,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.5502970297029702</v>
+        <v>0.554</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-122</v>
+        <v>-124</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.4879295154185022</v>
+        <v>0.4875330396475771</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>105</v>
@@ -8271,13 +8271,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6443409836065574</v>
+        <v>0.6433344398340248</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-181</v>
+        <v>-180</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-144</v>
+        <v>-141</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 64.3% (fair -180). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8313,17 +8313,17 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -8333,17 +8333,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4803964757709251</v>
+        <v>0.5051851851851852</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>108</v>
+        <v>-102</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8379,17 +8379,17 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -8399,17 +8399,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5318627450980392</v>
+        <v>0.4803964757709251</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-114</v>
+        <v>108</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8450,12 +8450,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -8465,17 +8465,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5011627906976744</v>
+        <v>0.534264705882353</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-100</v>
+        <v>-115</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8535,13 +8535,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4633913043478262</v>
+        <v>0.4607659574468085</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -8597,17 +8597,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4800900900900902</v>
+        <v>0.383273381294964</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>108</v>
+        <v>161</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8643,17 +8643,17 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.3814748201438848</v>
+        <v>0.4869124423963134</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>162</v>
+        <v>105</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>178</v>
+        <v>117</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 38.1% (fair +162). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8714,12 +8714,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -8729,17 +8729,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4849769585253456</v>
+        <v>0.4528755364806866</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8841,17 +8841,17 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8861,17 +8861,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4308298755186722</v>
+        <v>0.4469957081545065</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8912,12 +8912,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -8927,17 +8927,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.456079295154185</v>
+        <v>0.4603111111111111</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8973,17 +8973,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>San Diego Padres @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8993,17 +8993,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5888532188841202</v>
+        <v>0.4344957983193278</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-143</v>
+        <v>130</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-133</v>
+        <v>138</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 43.4% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9039,17 +9039,17 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9059,17 +9059,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.462286995515695</v>
+        <v>0.5899377682403434</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>116</v>
+        <v>-144</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>123</v>
+        <v>-133</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +116). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9110,12 +9110,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>San Diego Padres @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9125,17 +9125,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.638612927756654</v>
+        <v>0.5867982832618026</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-177</v>
+        <v>-142</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-163</v>
+        <v>-133</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 63.9% (fair -177). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9171,37 +9171,37 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres +1.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5796304347826088</v>
+        <v>0.6435444444444444</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-138</v>
+        <v>-181</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-130</v>
+        <v>-170</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 64.4% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9234,75 +9234,9 @@
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>00:05</t>
-        </is>
-      </c>
-      <c r="D22" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="n">
-        <v>0.5836017167381974</v>
-      </c>
-      <c r="G22" s="14" t="n">
-        <v>-140</v>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v>-133</v>
-      </c>
-      <c r="I22" s="13">
-        <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
-        <v/>
-      </c>
-      <c r="J22" s="16">
-        <f>IF($H$22="","",$F$22*IF($H$22&lt;0,-100/$H$22,$H$22/100)-(1-$F$22))</f>
-        <v/>
-      </c>
-      <c r="K22" s="17">
-        <f>IF($H$22="","",MAX(0,($F$22*IF($H$22&lt;0,-100/$H$22,$H$22/100)-(1-$F$22))/IF($H$22&lt;0,-100/$H$22,$H$22/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L22" s="18">
-        <f>IF($H$22="","",ROUND(MIN($K$22,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M22" s="12">
-        <f>IF($J$22="","",IF($J$22&lt;0,"Pass",IF($J$22&lt;'Settings'!$B$4,"Thin",IF($J$22&lt;0.06,"✅ Sharp band",IF($J$22&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N22" s="19" t="inlineStr">
-        <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
-        </is>
-      </c>
-      <c r="O22" s="15" t="n"/>
-      <c r="P22" s="16">
-        <f>IF(OR($H$22="",$O$22=""),"",(1+IF($H$22&lt;0,-100/$H$22,$H$22/100))/(1+IF($O$22&lt;0,-100/$O$22,$O$22/100))-1)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J22">
+  <conditionalFormatting sqref="J5:J21">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -9468,13 +9402,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.462286995515695</v>
+        <v>0.4603111111111111</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -9498,7 +9432,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +116). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9534,13 +9468,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5377222222222222</v>
+        <v>0.5397220264317181</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-116</v>
+        <v>-117</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-125</v>
+        <v>-127</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -9564,7 +9498,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -116). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -9596,7 +9530,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
@@ -9606,7 +9540,7 @@
         <v>110</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9662,7 +9596,7 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
@@ -9672,7 +9606,7 @@
         <v>-110</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9804,7 +9738,7 @@
         <v>-155</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9864,13 +9798,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5502970297029702</v>
+        <v>0.554</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-122</v>
+        <v>-124</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9894,7 +9828,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9930,13 +9864,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4497089108910891</v>
+        <v>0.445990099009901</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-102</v>
+        <v>102</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9960,7 +9894,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9992,17 +9926,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4931</v>
+        <v>0.5928</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>103</v>
+        <v>-146</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -10026,7 +9960,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 59.3% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -10058,17 +9992,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5069</v>
+        <v>0.4072</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-103</v>
+        <v>146</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -10092,7 +10026,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 40.7% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -10134,7 +10068,7 @@
         <v>255</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -10200,7 +10134,7 @@
         <v>-255</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -10260,13 +10194,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.456079295154185</v>
+        <v>0.4528755364806866</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -10290,7 +10224,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10326,10 +10260,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5439300429184549</v>
+        <v>0.5471266094420602</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-119</v>
+        <v>-121</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>-133</v>
@@ -10356,7 +10290,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10398,7 +10332,7 @@
         <v>106</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10656,10 +10590,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4849769585253456</v>
+        <v>0.4869124423963134</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>117</v>
@@ -10686,7 +10620,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10722,13 +10656,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5150181818181818</v>
+        <v>0.5130851851851852</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-120</v>
+        <v>-116</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10752,7 +10686,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10794,7 +10728,7 @@
         <v>133</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10860,7 +10794,7 @@
         <v>-133</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -11058,7 +10992,7 @@
         <v>157</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11124,7 +11058,7 @@
         <v>-157</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -11180,7 +11114,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
@@ -11190,7 +11124,7 @@
         <v>109</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -11246,7 +11180,7 @@
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
@@ -11256,7 +11190,7 @@
         <v>-109</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -11322,7 +11256,7 @@
         <v>111</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -11388,7 +11322,7 @@
         <v>-111</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11448,13 +11382,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4633913043478262</v>
+        <v>0.4607659574468085</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -11478,7 +11412,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11514,10 +11448,10 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5366236051502147</v>
+        <v>0.5392493562231759</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-116</v>
+        <v>-117</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>-133</v>
@@ -11544,7 +11478,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -11586,7 +11520,7 @@
         <v>161</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -11652,7 +11586,7 @@
         <v>-161</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -11718,7 +11652,7 @@
         <v>179</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -11844,10 +11778,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.3556302521008404</v>
+        <v>0.3566806722689076</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>138</v>
@@ -11874,7 +11808,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 35.6% (fair +181). Your call.</t>
+          <t>Model 35.7% (fair +180). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -11910,13 +11844,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.6443409836065574</v>
+        <v>0.6433344398340248</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-181</v>
+        <v>-180</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-144</v>
+        <v>-141</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -11940,7 +11874,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 64.3% (fair -180). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -11972,7 +11906,7 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
@@ -11982,7 +11916,7 @@
         <v>111</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -12038,7 +11972,7 @@
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
@@ -12048,7 +11982,7 @@
         <v>-111</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12114,7 +12048,7 @@
         <v>-133</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12180,7 +12114,7 @@
         <v>133</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12240,13 +12174,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4308298755186722</v>
+        <v>0.4344957983193278</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12270,7 +12204,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 43.4% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12306,13 +12240,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5692131147540984</v>
+        <v>0.5655100840336135</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-132</v>
+        <v>-130</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-144</v>
+        <v>-138</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -12336,7 +12270,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 56.6% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12368,7 +12302,7 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Over 12.5</t>
+          <t>Over 12</t>
         </is>
       </c>
       <c r="F49" s="13" t="n">
@@ -12378,7 +12312,7 @@
         <v>767</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -12434,7 +12368,7 @@
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>Under 12.5</t>
+          <t>Under 12</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
@@ -12504,13 +12438,13 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4203862660944206</v>
+        <v>0.4092</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -12534,7 +12468,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 40.9% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -12570,13 +12504,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5796304347826088</v>
+        <v>0.5908</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-138</v>
+        <v>-144</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>-130</v>
+        <v>101</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -12600,7 +12534,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 59.1% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -12774,7 +12708,7 @@
         <v>107</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -12906,7 +12840,7 @@
         <v>183</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -12972,7 +12906,7 @@
         <v>-183</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-118</v>
+        <v>-121</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13032,13 +12966,13 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5120283185840708</v>
+        <v>0.5124757709251102</v>
       </c>
       <c r="G59" s="14" t="n">
         <v>-105</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>-126</v>
+        <v>-127</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -13098,7 +13032,7 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4879295154185022</v>
+        <v>0.4875330396475771</v>
       </c>
       <c r="G60" s="14" t="n">
         <v>105</v>
@@ -13160,17 +13094,17 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Over 11.5</t>
+          <t>Over 12</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.378</v>
+        <v>0.2727</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>165</v>
+        <v>267</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -13194,7 +13128,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 37.8% (fair +165). Your call.</t>
+          <t>Model 27.3% (fair +267). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -13226,17 +13160,17 @@
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>Under 11.5</t>
+          <t>Under 12</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.622</v>
+        <v>0.7273000000000001</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-165</v>
+        <v>-267</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -13260,7 +13194,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 62.2% (fair -165). Your call.</t>
+          <t>Model 72.7% (fair -267). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -13944,10 +13878,10 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5318627450980392</v>
+        <v>0.534264705882353</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="H73" s="15" t="n">
         <v>104</v>
@@ -13974,7 +13908,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -14010,13 +13944,13 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4681529411764705</v>
+        <v>0.46575</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -14040,7 +13974,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14076,10 +14010,10 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.3814748201438848</v>
+        <v>0.383273381294964</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H75" s="15" t="n">
         <v>178</v>
@@ -14106,7 +14040,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 38.1% (fair +162). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14142,13 +14076,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.6185475524475526</v>
+        <v>0.6167251798561151</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-162</v>
+        <v>-161</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>-186</v>
+        <v>-178</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -14172,7 +14106,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14208,13 +14142,13 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4111453744493392</v>
+        <v>0.4100873362445415</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -14238,7 +14172,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 41.1% (fair +143). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14274,10 +14208,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5888532188841202</v>
+        <v>0.5899377682403434</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-143</v>
+        <v>-144</v>
       </c>
       <c r="H78" s="15" t="n">
         <v>-133</v>
@@ -14304,7 +14238,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14340,10 +14274,10 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.4800900900900902</v>
+        <v>0.505</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>108</v>
+        <v>-102</v>
       </c>
       <c r="H79" s="15" t="n">
         <v>122</v>
@@ -14370,7 +14304,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14406,13 +14340,13 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5199221198156682</v>
+        <v>0.495</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>-108</v>
+        <v>102</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-117</v>
+        <v>-111</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14436,7 +14370,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14478,7 +14412,7 @@
         <v>-121</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -14604,13 +14538,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4510810810810811</v>
+        <v>0.4469957081545065</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -14634,7 +14568,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 45.1% (fair +122). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -14670,13 +14604,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5489316872427984</v>
+        <v>0.5530436974789915</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-122</v>
+        <v>-124</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-143</v>
+        <v>-138</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -14700,7 +14634,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -14736,13 +14670,13 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4988246696035242</v>
+        <v>0.4947967741935483</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>-127</v>
+        <v>-117</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -14766,7 +14700,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -14802,13 +14736,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5011627906976744</v>
+        <v>0.5051851851851852</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-100</v>
+        <v>-102</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -14832,7 +14766,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -14868,13 +14802,13 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.3613688212927757</v>
+        <v>0.3564444444444445</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -14898,7 +14832,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 36.1% (fair +177). Your call.</t>
+          <t>Model 35.6% (fair +181). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -14934,13 +14868,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.638612927756654</v>
+        <v>0.6435444444444444</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-177</v>
+        <v>-181</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-163</v>
+        <v>-170</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -14964,7 +14898,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 63.9% (fair -177). Your call.</t>
+          <t>Model 64.4% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15000,13 +14934,13 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.4163876651982379</v>
+        <v>0.413175965665236</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -15030,7 +14964,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15066,10 +15000,10 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.5836017167381974</v>
+        <v>0.5867982832618026</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>-140</v>
+        <v>-142</v>
       </c>
       <c r="H90" s="15" t="n">
         <v>-133</v>
@@ -15096,7 +15030,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>

--- a/data/output/workbook/2026-06-29.xlsx
+++ b/data/output/workbook/2026-06-29.xlsx
@@ -580,7 +580,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9401175"/>
+    <ext cx="10125075" cy="9810750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29 09:09</t>
+          <t>2026-06-29 12:57</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5398,815 +5398,815 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="28" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="28" t="inlineStr">
         <is>
           <t>San Diego Padres offense vs Chicago Cubs defense</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="29" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B61" s="29" t="inlineStr">
+      <c r="B64" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C61" s="29" t="inlineStr">
+      <c r="C64" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D61" s="29" t="inlineStr">
+      <c r="D64" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E61" s="29" t="inlineStr">
+      <c r="E64" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F61" s="29" t="inlineStr">
+      <c r="F64" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G61" s="29" t="inlineStr">
+      <c r="G64" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H61" s="29" t="inlineStr">
+      <c r="H64" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I61" s="29" t="inlineStr">
+      <c r="I64" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J61" s="29" t="inlineStr">
+      <c r="J64" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K61" s="29" t="inlineStr">
+      <c r="K64" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L61" s="29" t="inlineStr">
+      <c r="L64" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M61" s="29" t="inlineStr">
+      <c r="M64" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N61" s="29" t="inlineStr">
+      <c r="N64" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O61" s="29" t="inlineStr">
+      <c r="O64" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P61" s="29" t="inlineStr">
+      <c r="P64" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q61" s="29" t="inlineStr">
+      <c r="Q64" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B62" s="31" t="n">
-        <v>4.279</v>
-      </c>
-      <c r="C62" s="31" t="n">
-        <v>4.433</v>
-      </c>
-      <c r="D62" s="31" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="E62" s="31" t="n">
-        <v>3.733</v>
-      </c>
-      <c r="F62" s="31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G62" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="H62" s="35" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I62" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J62" s="33" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K62" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="L62" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="M62" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="N62" s="31" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="O62" s="31" t="n">
-        <v>4.767</v>
-      </c>
-      <c r="P62" s="31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Q62" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B63" s="31" t="n">
-        <v>7.139</v>
-      </c>
-      <c r="C63" s="31" t="n">
-        <v>7.167</v>
-      </c>
-      <c r="D63" s="31" t="n">
-        <v>6.444</v>
-      </c>
-      <c r="E63" s="31" t="n">
-        <v>6.357</v>
-      </c>
-      <c r="F63" s="31" t="n">
-        <v>5.111</v>
-      </c>
-      <c r="G63" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H63" s="33" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="I63" s="31" t="inlineStr"/>
-      <c r="J63" s="33" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K63" s="31" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L63" s="31" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="M63" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="N63" s="31" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O63" s="31" t="n">
-        <v>7.966</v>
-      </c>
-      <c r="P63" s="31" t="n">
-        <v>7.595</v>
-      </c>
-      <c r="Q63" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="30" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B64" s="31" t="n">
-        <v>0.972</v>
-      </c>
-      <c r="C64" s="31" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="D64" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="31" t="n">
-        <v>1.286</v>
-      </c>
-      <c r="F64" s="31" t="n">
-        <v>1.111</v>
-      </c>
-      <c r="G64" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H64" s="35" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I64" s="31" t="inlineStr"/>
-      <c r="J64" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K64" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L64" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M64" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N64" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O64" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P64" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q64" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B65" s="31" t="n">
-        <v>8.138999999999999</v>
+        <v>4.279</v>
       </c>
       <c r="C65" s="31" t="n">
-        <v>8.042</v>
+        <v>4.433</v>
       </c>
       <c r="D65" s="31" t="n">
-        <v>9</v>
+        <v>3.55</v>
       </c>
       <c r="E65" s="31" t="n">
-        <v>8.714</v>
+        <v>3.733</v>
       </c>
       <c r="F65" s="31" t="n">
-        <v>7.889</v>
+        <v>2.9</v>
       </c>
       <c r="G65" s="31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H65" s="32" t="inlineStr">
-        <is>
-          <t>5th</t>
+        <v>3</v>
+      </c>
+      <c r="H65" s="35" t="inlineStr">
+        <is>
+          <t>19th</t>
         </is>
       </c>
       <c r="I65" s="31" t="inlineStr">
         <is>
-          <t>★★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="J65" s="33" t="inlineStr">
         <is>
-          <t>25th</t>
+          <t>24th</t>
         </is>
       </c>
       <c r="K65" s="31" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="L65" s="31" t="n">
-        <v>7.3</v>
+        <v>4.6</v>
       </c>
       <c r="M65" s="31" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="N65" s="31" t="n">
-        <v>7.35</v>
+        <v>4.25</v>
       </c>
       <c r="O65" s="31" t="n">
-        <v>7.552</v>
+        <v>4.767</v>
       </c>
       <c r="P65" s="31" t="n">
-        <v>7.838</v>
+        <v>4.5</v>
       </c>
       <c r="Q65" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="30" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B66" s="31" t="n">
+        <v>7.139</v>
+      </c>
+      <c r="C66" s="31" t="n">
+        <v>7.167</v>
+      </c>
+      <c r="D66" s="31" t="n">
+        <v>6.444</v>
+      </c>
+      <c r="E66" s="31" t="n">
+        <v>6.357</v>
+      </c>
+      <c r="F66" s="31" t="n">
+        <v>5.111</v>
+      </c>
+      <c r="G66" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H66" s="33" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="I66" s="31" t="inlineStr"/>
+      <c r="J66" s="33" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K66" s="31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L66" s="31" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M66" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="N66" s="31" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O66" s="31" t="n">
+        <v>7.966</v>
+      </c>
+      <c r="P66" s="31" t="n">
+        <v>7.595</v>
+      </c>
+      <c r="Q66" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B67" s="31" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="C67" s="31" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="D67" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="31" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="F67" s="31" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="G67" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" s="35" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I67" s="31" t="inlineStr"/>
+      <c r="J67" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K67" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L67" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M67" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N67" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O67" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P67" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q67" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B68" s="31" t="n">
+        <v>8.138999999999999</v>
+      </c>
+      <c r="C68" s="31" t="n">
+        <v>8.042</v>
+      </c>
+      <c r="D68" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="E68" s="31" t="n">
+        <v>8.714</v>
+      </c>
+      <c r="F68" s="31" t="n">
+        <v>7.889</v>
+      </c>
+      <c r="G68" s="31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H68" s="32" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="I68" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J68" s="33" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K68" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L68" s="31" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="M68" s="31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N68" s="31" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="O68" s="31" t="n">
+        <v>7.552</v>
+      </c>
+      <c r="P68" s="31" t="n">
+        <v>7.838</v>
+      </c>
+      <c r="Q68" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B66" s="31" t="n">
+      <c r="B69" s="31" t="n">
         <v>0.222</v>
       </c>
-      <c r="C66" s="31" t="n">
+      <c r="C69" s="31" t="n">
         <v>0.292</v>
       </c>
-      <c r="D66" s="31" t="n">
+      <c r="D69" s="31" t="n">
         <v>0.333</v>
       </c>
-      <c r="E66" s="31" t="n">
+      <c r="E69" s="31" t="n">
         <v>0.429</v>
       </c>
-      <c r="F66" s="31" t="n">
+      <c r="F69" s="31" t="n">
         <v>0.556</v>
       </c>
-      <c r="G66" s="31" t="n">
+      <c r="G69" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="H66" s="35" t="inlineStr">
+      <c r="H69" s="35" t="inlineStr">
         <is>
           <t>11th</t>
         </is>
       </c>
-      <c r="I66" s="31" t="inlineStr">
+      <c r="I69" s="31" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J66" s="33" t="inlineStr">
+      <c r="J69" s="33" t="inlineStr">
         <is>
           <t>28th</t>
         </is>
       </c>
-      <c r="K66" s="31" t="n">
+      <c r="K69" s="31" t="n">
         <v>1.2</v>
       </c>
-      <c r="L66" s="31" t="n">
+      <c r="L69" s="31" t="n">
         <v>0.9</v>
       </c>
-      <c r="M66" s="31" t="n">
+      <c r="M69" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="N66" s="31" t="n">
+      <c r="N69" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="O66" s="31" t="n">
+      <c r="O69" s="31" t="n">
         <v>0.414</v>
       </c>
-      <c r="P66" s="31" t="n">
+      <c r="P69" s="31" t="n">
         <v>0.405</v>
       </c>
-      <c r="Q66" s="34" t="inlineStr">
+      <c r="Q69" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="28" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="28" t="inlineStr">
         <is>
           <t>Chicago Cubs offense vs San Diego Padres defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B72" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="29" t="inlineStr">
+      <c r="C72" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="29" t="inlineStr">
+      <c r="D72" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="29" t="inlineStr">
+      <c r="E72" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="29" t="inlineStr">
+      <c r="F72" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="29" t="inlineStr">
+      <c r="G72" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="29" t="inlineStr">
+      <c r="H72" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="29" t="inlineStr">
+      <c r="I72" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="29" t="inlineStr">
+      <c r="J72" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="29" t="inlineStr">
+      <c r="K72" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="29" t="inlineStr">
+      <c r="L72" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="29" t="inlineStr">
+      <c r="M72" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="29" t="inlineStr">
+      <c r="N72" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="29" t="inlineStr">
+      <c r="O72" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="29" t="inlineStr">
+      <c r="P72" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="29" t="inlineStr">
+      <c r="Q72" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>4.947</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr"/>
-      <c r="J70" s="32" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O70" s="31" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>3.674</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B71" s="31" t="n">
-        <v>8.432</v>
-      </c>
-      <c r="C71" s="31" t="n">
-        <v>8.965999999999999</v>
-      </c>
-      <c r="D71" s="31" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="E71" s="31" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="F71" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G71" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H71" s="33" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="L71" s="31" t="n">
-        <v>7.778</v>
-      </c>
-      <c r="M71" s="31" t="n">
-        <v>8.856999999999999</v>
-      </c>
-      <c r="N71" s="31" t="n">
-        <v>8.444000000000001</v>
-      </c>
-      <c r="O71" s="31" t="n">
-        <v>8.125</v>
-      </c>
-      <c r="P71" s="31" t="n">
-        <v>8.111000000000001</v>
-      </c>
-      <c r="Q71" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="30" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B72" s="31" t="n">
-        <v>1.135</v>
-      </c>
-      <c r="C72" s="31" t="n">
-        <v>1.241</v>
-      </c>
-      <c r="D72" s="31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E72" s="31" t="n">
-        <v>1.133</v>
-      </c>
-      <c r="F72" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G72" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H72" s="33" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="I72" s="31" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q72" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>8.541</v>
+        <v>4.947</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>8.516999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="D73" s="31" t="n">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="E73" s="31" t="n">
-        <v>8.6</v>
+        <v>4.267</v>
       </c>
       <c r="F73" s="31" t="n">
-        <v>8.5</v>
+        <v>3.2</v>
       </c>
       <c r="G73" s="31" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="H73" s="33" t="inlineStr">
         <is>
-          <t>25th</t>
+          <t>30th</t>
         </is>
       </c>
       <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="33" t="inlineStr">
-        <is>
-          <t>24th</t>
+      <c r="J73" s="32" t="inlineStr">
+        <is>
+          <t>4th</t>
         </is>
       </c>
       <c r="K73" s="31" t="n">
-        <v>7.4</v>
+        <v>2.4</v>
       </c>
       <c r="L73" s="31" t="n">
-        <v>8.333</v>
+        <v>3.4</v>
       </c>
       <c r="M73" s="31" t="n">
-        <v>7.5</v>
+        <v>4.4</v>
       </c>
       <c r="N73" s="31" t="n">
-        <v>8.167</v>
+        <v>3.95</v>
       </c>
       <c r="O73" s="31" t="n">
-        <v>8.708</v>
+        <v>3.667</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>8.805999999999999</v>
+        <v>3.674</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>8.432</v>
+      </c>
+      <c r="C74" s="31" t="n">
+        <v>8.965999999999999</v>
+      </c>
+      <c r="D74" s="31" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E74" s="31" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="F74" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G74" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L74" s="31" t="n">
+        <v>7.778</v>
+      </c>
+      <c r="M74" s="31" t="n">
+        <v>8.856999999999999</v>
+      </c>
+      <c r="N74" s="31" t="n">
+        <v>8.444000000000001</v>
+      </c>
+      <c r="O74" s="31" t="n">
+        <v>8.125</v>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>8.111000000000001</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B75" s="31" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="C75" s="31" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="D75" s="31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E75" s="31" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="F75" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G75" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H75" s="33" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q75" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B76" s="31" t="n">
+        <v>8.541</v>
+      </c>
+      <c r="C76" s="31" t="n">
+        <v>8.516999999999999</v>
+      </c>
+      <c r="D76" s="31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E76" s="31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F76" s="31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G76" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H76" s="33" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="I76" s="31" t="inlineStr"/>
+      <c r="J76" s="33" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K76" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L76" s="31" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="M76" s="31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N76" s="31" t="n">
+        <v>8.167</v>
+      </c>
+      <c r="O76" s="31" t="n">
+        <v>8.708</v>
+      </c>
+      <c r="P76" s="31" t="n">
+        <v>8.805999999999999</v>
+      </c>
+      <c r="Q76" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="31" t="n">
+      <c r="B77" s="31" t="n">
         <v>0.297</v>
       </c>
-      <c r="C74" s="31" t="n">
+      <c r="C77" s="31" t="n">
         <v>0.276</v>
       </c>
-      <c r="D74" s="31" t="n">
+      <c r="D77" s="31" t="n">
         <v>0.35</v>
       </c>
-      <c r="E74" s="31" t="n">
+      <c r="E77" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="F74" s="31" t="n">
+      <c r="F77" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="G74" s="31" t="n">
+      <c r="G77" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H74" s="33" t="inlineStr">
+      <c r="H77" s="33" t="inlineStr">
         <is>
           <t>29th</t>
         </is>
       </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="33" t="inlineStr">
+      <c r="I77" s="31" t="inlineStr"/>
+      <c r="J77" s="33" t="inlineStr">
         <is>
           <t>25th</t>
         </is>
       </c>
-      <c r="K74" s="31" t="n">
+      <c r="K77" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="L74" s="31" t="n">
+      <c r="L77" s="31" t="n">
         <v>0.556</v>
       </c>
-      <c r="M74" s="31" t="n">
+      <c r="M77" s="31" t="n">
         <v>0.429</v>
       </c>
-      <c r="N74" s="31" t="n">
+      <c r="N77" s="31" t="n">
         <v>0.333</v>
       </c>
-      <c r="O74" s="31" t="n">
+      <c r="O77" s="31" t="n">
         <v>0.333</v>
       </c>
-      <c r="P74" s="31" t="n">
+      <c r="P77" s="31" t="n">
         <v>0.417</v>
       </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="Q77" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8120,32 +8120,32 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.554</v>
+        <v>0.5757692307692307</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-124</v>
+        <v>-136</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8186,12 +8186,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8201,17 +8201,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.4875330396475771</v>
+        <v>0.6390913043478261</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>105</v>
+        <v>-177</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>127</v>
+        <v>-130</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 63.9% (fair -177). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8252,12 +8252,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8267,17 +8267,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6433344398340248</v>
+        <v>0.4846521739130435</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-180</v>
+        <v>106</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-141</v>
+        <v>130</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 64.3% (fair -180). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8313,17 +8313,17 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -8333,17 +8333,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5051851851851852</v>
+        <v>0.5502970297029702</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-102</v>
+        <v>-122</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8379,17 +8379,17 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -8399,17 +8399,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4803964757709251</v>
+        <v>0.5318269230769231</v>
       </c>
       <c r="G9" s="14" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H9" s="15" t="n">
         <v>108</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>127</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8445,17 +8445,17 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -8465,17 +8465,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.534264705882353</v>
+        <v>0.4787826086956522</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-115</v>
+        <v>109</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8511,17 +8511,17 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -8531,17 +8531,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4607659574468085</v>
+        <v>0.5077674418604651</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>117</v>
+        <v>-103</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8577,17 +8577,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -8597,17 +8597,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.383273381294964</v>
+        <v>0.4602118644067796</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8667,10 +8667,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4869124423963134</v>
+        <v>0.4864055299539171</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>117</v>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8714,12 +8714,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>San Diego Padres @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -8729,17 +8729,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4528755364806866</v>
+        <v>0.4293032786885246</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8775,17 +8775,17 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -8795,17 +8795,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4487124463519314</v>
+        <v>0.4607929515418502</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8846,12 +8846,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8861,14 +8861,14 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4469957081545065</v>
+        <v>0.4487124463519314</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>133</v>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8907,17 +8907,17 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -8927,17 +8927,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4603111111111111</v>
+        <v>0.4469957081545065</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8978,32 +8978,32 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>Washington Nationals @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Boston Red Sox -1.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4344957983193278</v>
+        <v>0.4526521739130435</v>
       </c>
       <c r="G18" s="14" t="n">
+        <v>121</v>
+      </c>
+      <c r="H18" s="15" t="n">
         <v>130</v>
-      </c>
-      <c r="H18" s="15" t="n">
-        <v>138</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +130). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9039,17 +9039,17 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9059,17 +9059,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5899377682403434</v>
+        <v>0.4603111111111111</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-144</v>
+        <v>117</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-133</v>
+        <v>125</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9110,12 +9110,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9125,14 +9125,14 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5867982832618026</v>
+        <v>0.5899377682403434</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-142</v>
+        <v>-144</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>-133</v>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9176,12 +9176,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>San Diego Padres @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9191,17 +9191,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.6435444444444444</v>
+        <v>0.5867982832618026</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-181</v>
+        <v>-142</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-170</v>
+        <v>-133</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9540,7 +9540,7 @@
         <v>110</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9606,7 +9606,7 @@
         <v>-110</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9672,7 +9672,7 @@
         <v>155</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9738,7 +9738,7 @@
         <v>-155</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9798,13 +9798,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.554</v>
+        <v>0.5502970297029702</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-124</v>
+        <v>-122</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9864,13 +9864,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.445990099009901</v>
+        <v>0.4497089108910891</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>102</v>
+        <v>-102</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 45.0% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9926,17 +9926,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5928</v>
+        <v>0.4931</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-146</v>
+        <v>103</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 59.3% (fair -146). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9992,17 +9992,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4072</v>
+        <v>0.5069</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>146</v>
+        <v>-103</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 40.7% (fair +146). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -10194,13 +10194,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4528755364806866</v>
+        <v>0.4607929515418502</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10260,13 +10260,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5471266094420602</v>
+        <v>0.5392180180180179</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-121</v>
+        <v>-117</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-133</v>
+        <v>-122</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10332,7 +10332,7 @@
         <v>106</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10398,7 +10398,7 @@
         <v>-106</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -10464,7 +10464,7 @@
         <v>162</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -10530,7 +10530,7 @@
         <v>-162</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-114</v>
+        <v>-125</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10590,10 +10590,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4869124423963134</v>
+        <v>0.4864055299539171</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>117</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10656,13 +10656,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5130851851851852</v>
+        <v>0.5135599078341013</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-116</v>
+        <v>-117</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10718,17 +10718,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4297</v>
+        <v>0.4242502487562189</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-104</v>
+        <v>-101</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 43.0% (fair +133). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10784,17 +10784,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5703</v>
+        <v>0.5757692307692307</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-133</v>
+        <v>-136</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -133). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10860,7 +10860,7 @@
         <v>187</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10992,7 +10992,7 @@
         <v>157</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11124,7 +11124,7 @@
         <v>109</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -11190,7 +11190,7 @@
         <v>-109</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4737</v>
+        <v>0.4526521739130435</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11316,13 +11316,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5263</v>
+        <v>0.5473384615384616</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-111</v>
+        <v>-121</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>108</v>
+        <v>-134</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11382,13 +11382,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4607659574468085</v>
+        <v>0.4602118644067796</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>117</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11448,7 +11448,7 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5392493562231759</v>
+        <v>0.5397630901287553</v>
       </c>
       <c r="G36" s="14" t="n">
         <v>-117</v>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -11520,7 +11520,7 @@
         <v>161</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -11652,7 +11652,7 @@
         <v>179</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -11778,10 +11778,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.3566806722689076</v>
+        <v>0.3608823529411765</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>138</v>
@@ -11808,7 +11808,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 35.7% (fair +180). Your call.</t>
+          <t>Model 36.1% (fair +177). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -11844,13 +11844,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.6433344398340248</v>
+        <v>0.6390913043478261</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-180</v>
+        <v>-177</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-141</v>
+        <v>-130</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 64.3% (fair -180). Your call.</t>
+          <t>Model 63.9% (fair -177). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -11906,7 +11906,7 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
@@ -11916,7 +11916,7 @@
         <v>111</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
@@ -12048,7 +12048,7 @@
         <v>-133</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12114,7 +12114,7 @@
         <v>133</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12174,13 +12174,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4344957983193278</v>
+        <v>0.4293032786885246</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +130). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12240,13 +12240,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5655100840336135</v>
+        <v>0.5706885245901639</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-130</v>
+        <v>-133</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-138</v>
+        <v>-144</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -130). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12302,17 +12302,17 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Over 12</t>
+          <t>Over 11.5</t>
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.1153</v>
+        <v>0.185</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>767</v>
+        <v>441</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 11.5% (fair +767). Your call.</t>
+          <t>Model 18.5% (fair +441). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12368,17 +12368,17 @@
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>Under 12</t>
+          <t>Under 11.5</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.8847</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-767</v>
+        <v>-441</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 88.5% (fair -767). Your call.</t>
+          <t>Model 81.5% (fair -441). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12510,7 +12510,7 @@
         <v>-144</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -12570,13 +12570,13 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4803964757709251</v>
+        <v>0.4787826086956522</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -12600,7 +12600,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -12636,10 +12636,10 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5195810572687225</v>
+        <v>0.5212035242290749</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="H54" s="15" t="n">
         <v>-127</v>
@@ -12666,7 +12666,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -12708,7 +12708,7 @@
         <v>107</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>107</v>
+        <v>-101</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -12774,7 +12774,7 @@
         <v>-107</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -12840,7 +12840,7 @@
         <v>183</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -12906,7 +12906,7 @@
         <v>-183</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-121</v>
+        <v>-115</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -12966,13 +12966,13 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5124757709251102</v>
+        <v>0.5153652173913044</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>-127</v>
+        <v>-130</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -12996,7 +12996,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -13032,13 +13032,13 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4875330396475771</v>
+        <v>0.4846521739130435</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -13062,7 +13062,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -13094,17 +13094,17 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Over 12</t>
+          <t>Over 11.5</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.2727</v>
+        <v>0.378</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>267</v>
+        <v>165</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>129</v>
+        <v>-108</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -13128,7 +13128,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 27.3% (fair +267). Your call.</t>
+          <t>Model 37.8% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -13160,17 +13160,17 @@
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>Under 12</t>
+          <t>Under 11.5</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.7273000000000001</v>
+        <v>0.622</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-267</v>
+        <v>-165</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 72.7% (fair -267). Your call.</t>
+          <t>Model 62.2% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -13302,7 +13302,7 @@
         <v>-144</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -13878,13 +13878,13 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.534264705882353</v>
+        <v>0.5318269230769231</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-115</v>
+        <v>-114</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -13908,7 +13908,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -13944,10 +13944,10 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.46575</v>
+        <v>0.46815</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H74" s="15" t="n">
         <v>100</v>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14010,10 +14010,10 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.383273381294964</v>
+        <v>0.4068</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="H75" s="15" t="n">
         <v>178</v>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 40.7% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14076,13 +14076,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.6167251798561151</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-161</v>
+        <v>-146</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>-178</v>
+        <v>-163</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 59.3% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14346,7 +14346,7 @@
         <v>102</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-111</v>
+        <v>-108</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14670,13 +14670,13 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4947967741935483</v>
+        <v>0.4922131455399061</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>-117</v>
+        <v>-113</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -14700,7 +14700,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -14736,13 +14736,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5051851851851852</v>
+        <v>0.5077674418604651</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -14766,7 +14766,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -14802,13 +14802,13 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.3564444444444445</v>
+        <v>0.3595057034220532</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -14832,7 +14832,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 35.6% (fair +181). Your call.</t>
+          <t>Model 36.0% (fair +178). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -14868,10 +14868,10 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.6435444444444444</v>
+        <v>0.6405222222222222</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-181</v>
+        <v>-178</v>
       </c>
       <c r="H88" s="15" t="n">
         <v>-170</v>
@@ -14898,7 +14898,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 64.1% (fair -178). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15847,10 +15847,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.5591</v>
+        <v>0.4423</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-127</v>
+        <v>126</v>
       </c>
       <c r="H5" s="15" t="n"/>
       <c r="I5" s="13">
@@ -15875,7 +15875,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -15911,10 +15911,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.4409</v>
+        <v>0.5577</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>127</v>
+        <v>-126</v>
       </c>
       <c r="H6" s="15" t="n"/>
       <c r="I6" s="13">
@@ -15939,7 +15939,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>

--- a/data/output/workbook/2026-06-29.xlsx
+++ b/data/output/workbook/2026-06-29.xlsx
@@ -550,7 +550,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10048875"/>
+    <ext cx="10125075" cy="9610725"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29 12:57</t>
+          <t>2026-06-29 15:07</t>
         </is>
       </c>
     </row>
@@ -4529,7 +4529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q78"/>
+  <dimension ref="A1:Q76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4546,823 +4546,823 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="28" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds offense vs Milwaukee Brewers defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B63" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C63" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D63" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E63" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F63" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G63" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H63" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I63" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J63" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K63" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L63" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M63" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N63" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O63" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P63" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q63" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="64">
-      <c r="A64" s="28" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds offense vs Milwaukee Brewers defense</t>
+      <c r="A64" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B64" s="31" t="n">
+        <v>4.132</v>
+      </c>
+      <c r="C64" s="31" t="n">
+        <v>4.433</v>
+      </c>
+      <c r="D64" s="31" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="E64" s="31" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="F64" s="31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G64" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="H64" s="32" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I64" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J64" s="35" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K64" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L64" s="31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M64" s="31" t="n">
+        <v>3.267</v>
+      </c>
+      <c r="N64" s="31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O64" s="31" t="n">
+        <v>4.033</v>
+      </c>
+      <c r="P64" s="31" t="n">
+        <v>3.784</v>
+      </c>
+      <c r="Q64" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B65" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C65" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D65" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E65" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F65" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G65" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H65" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I65" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J65" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K65" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L65" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M65" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N65" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O65" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P65" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q65" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A65" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B65" s="31" t="n">
+        <v>7.216</v>
+      </c>
+      <c r="C65" s="31" t="n">
+        <v>7.345</v>
+      </c>
+      <c r="D65" s="31" t="n">
+        <v>7.632</v>
+      </c>
+      <c r="E65" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="F65" s="31" t="n">
+        <v>7.667</v>
+      </c>
+      <c r="G65" s="31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H65" s="35" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="I65" s="31" t="inlineStr"/>
+      <c r="J65" s="32" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="K65" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L65" s="31" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="M65" s="31" t="n">
+        <v>6.308</v>
+      </c>
+      <c r="N65" s="31" t="n">
+        <v>6.722</v>
+      </c>
+      <c r="O65" s="31" t="n">
+        <v>7.536</v>
+      </c>
+      <c r="P65" s="31" t="n">
+        <v>7.371</v>
+      </c>
+      <c r="Q65" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B66" s="31" t="n">
-        <v>4.132</v>
+        <v>1.216</v>
       </c>
       <c r="C66" s="31" t="n">
-        <v>4.433</v>
+        <v>1.241</v>
       </c>
       <c r="D66" s="31" t="n">
-        <v>4.65</v>
+        <v>1.263</v>
       </c>
       <c r="E66" s="31" t="n">
-        <v>4.867</v>
+        <v>1.643</v>
       </c>
       <c r="F66" s="31" t="n">
-        <v>3.9</v>
+        <v>0.889</v>
       </c>
       <c r="G66" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="H66" s="32" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I66" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J66" s="35" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K66" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="L66" s="31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M66" s="31" t="n">
-        <v>3.267</v>
-      </c>
-      <c r="N66" s="31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O66" s="31" t="n">
-        <v>4.033</v>
-      </c>
-      <c r="P66" s="31" t="n">
-        <v>3.784</v>
+        <v>1</v>
+      </c>
+      <c r="H66" s="35" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="I66" s="31" t="inlineStr"/>
+      <c r="J66" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K66" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L66" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M66" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N66" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O66" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P66" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q66" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B67" s="31" t="n">
-        <v>7.216</v>
+        <v>9.27</v>
       </c>
       <c r="C67" s="31" t="n">
-        <v>7.345</v>
+        <v>9.103</v>
       </c>
       <c r="D67" s="31" t="n">
-        <v>7.632</v>
+        <v>9.420999999999999</v>
       </c>
       <c r="E67" s="31" t="n">
-        <v>8</v>
+        <v>9.286</v>
       </c>
       <c r="F67" s="31" t="n">
-        <v>7.667</v>
+        <v>8.888999999999999</v>
       </c>
       <c r="G67" s="31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H67" s="35" t="inlineStr">
-        <is>
-          <t>16th</t>
+        <v>9.6</v>
+      </c>
+      <c r="H67" s="33" t="inlineStr">
+        <is>
+          <t>22nd</t>
         </is>
       </c>
       <c r="I67" s="31" t="inlineStr"/>
       <c r="J67" s="32" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="K67" s="31" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="L67" s="31" t="n">
-        <v>5.75</v>
+        <v>10.625</v>
       </c>
       <c r="M67" s="31" t="n">
-        <v>6.308</v>
+        <v>10.538</v>
       </c>
       <c r="N67" s="31" t="n">
-        <v>6.722</v>
+        <v>10</v>
       </c>
       <c r="O67" s="31" t="n">
-        <v>7.536</v>
+        <v>8.929</v>
       </c>
       <c r="P67" s="31" t="n">
-        <v>7.371</v>
+        <v>9.571</v>
       </c>
       <c r="Q67" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B68" s="31" t="n">
-        <v>1.216</v>
+        <v>0.595</v>
       </c>
       <c r="C68" s="31" t="n">
-        <v>1.241</v>
+        <v>0.621</v>
       </c>
       <c r="D68" s="31" t="n">
-        <v>1.263</v>
+        <v>0.421</v>
       </c>
       <c r="E68" s="31" t="n">
-        <v>1.643</v>
+        <v>0.429</v>
       </c>
       <c r="F68" s="31" t="n">
-        <v>0.889</v>
+        <v>0</v>
       </c>
       <c r="G68" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H68" s="35" t="inlineStr">
-        <is>
-          <t>13th</t>
+        <v>0</v>
+      </c>
+      <c r="H68" s="33" t="inlineStr">
+        <is>
+          <t>26th</t>
         </is>
       </c>
       <c r="I68" s="31" t="inlineStr"/>
-      <c r="J68" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J68" s="32" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="K68" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="31" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M68" s="31" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="N68" s="31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O68" s="31" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="P68" s="31" t="n">
+        <v>0.486</v>
       </c>
       <c r="Q68" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B69" s="31" t="n">
-        <v>9.27</v>
-      </c>
-      <c r="C69" s="31" t="n">
-        <v>9.103</v>
-      </c>
-      <c r="D69" s="31" t="n">
-        <v>9.420999999999999</v>
-      </c>
-      <c r="E69" s="31" t="n">
-        <v>9.286</v>
-      </c>
-      <c r="F69" s="31" t="n">
-        <v>8.888999999999999</v>
-      </c>
-      <c r="G69" s="31" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="I69" s="31" t="inlineStr"/>
-      <c r="J69" s="32" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K69" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="L69" s="31" t="n">
-        <v>10.625</v>
-      </c>
-      <c r="M69" s="31" t="n">
-        <v>10.538</v>
-      </c>
-      <c r="N69" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="O69" s="31" t="n">
-        <v>8.929</v>
-      </c>
-      <c r="P69" s="31" t="n">
-        <v>9.571</v>
-      </c>
-      <c r="Q69" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>0.621</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr"/>
-      <c r="J70" s="32" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O70" s="31" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>0.486</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
+      <c r="A70" s="28" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers offense vs Cincinnati Reds defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B71" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C71" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D71" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E71" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F71" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G71" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H71" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I71" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J71" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K71" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L71" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M71" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N71" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O71" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P71" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q71" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="28" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers offense vs Cincinnati Reds defense</t>
+      <c r="A72" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B72" s="31" t="n">
+        <v>4.703</v>
+      </c>
+      <c r="C72" s="31" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="D72" s="31" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E72" s="31" t="n">
+        <v>3.733</v>
+      </c>
+      <c r="F72" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G72" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I72" s="31" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J72" s="33" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K72" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L72" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="M72" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="N72" s="31" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="O72" s="31" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="P72" s="31" t="n">
+        <v>4.658</v>
+      </c>
+      <c r="Q72" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B73" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C73" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D73" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E73" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F73" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G73" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H73" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I73" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J73" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K73" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L73" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M73" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N73" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O73" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P73" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q73" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A73" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B73" s="31" t="n">
+        <v>7.629</v>
+      </c>
+      <c r="C73" s="31" t="n">
+        <v>7.143</v>
+      </c>
+      <c r="D73" s="31" t="n">
+        <v>7.389</v>
+      </c>
+      <c r="E73" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="F73" s="31" t="n">
+        <v>7.625</v>
+      </c>
+      <c r="G73" s="31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="L73" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="M73" s="31" t="n">
+        <v>8.714</v>
+      </c>
+      <c r="N73" s="31" t="n">
+        <v>8.263</v>
+      </c>
+      <c r="O73" s="31" t="n">
+        <v>8.207000000000001</v>
+      </c>
+      <c r="P73" s="31" t="n">
+        <v>8.054</v>
+      </c>
+      <c r="Q73" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B74" s="31" t="n">
-        <v>4.703</v>
+        <v>0.657</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>4.133</v>
+        <v>0.5</v>
       </c>
       <c r="D74" s="31" t="n">
-        <v>4.25</v>
+        <v>0.278</v>
       </c>
       <c r="E74" s="31" t="n">
-        <v>3.733</v>
+        <v>0.308</v>
       </c>
       <c r="F74" s="31" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="G74" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J74" s="33" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L74" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="M74" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="N74" s="31" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="O74" s="31" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="P74" s="31" t="n">
-        <v>4.658</v>
+        <v>0.6</v>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B75" s="31" t="n">
-        <v>7.629</v>
+        <v>8.228999999999999</v>
       </c>
       <c r="C75" s="31" t="n">
+        <v>8.179</v>
+      </c>
+      <c r="D75" s="31" t="n">
+        <v>7.944</v>
+      </c>
+      <c r="E75" s="31" t="n">
+        <v>8.077</v>
+      </c>
+      <c r="F75" s="31" t="n">
+        <v>7.875</v>
+      </c>
+      <c r="G75" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="H75" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I75" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J75" s="35" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K75" s="31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L75" s="31" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="M75" s="31" t="n">
         <v>7.143</v>
       </c>
-      <c r="D75" s="31" t="n">
-        <v>7.389</v>
-      </c>
-      <c r="E75" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="F75" s="31" t="n">
-        <v>7.625</v>
-      </c>
-      <c r="G75" s="31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H75" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J75" s="33" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="L75" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="M75" s="31" t="n">
-        <v>8.714</v>
-      </c>
       <c r="N75" s="31" t="n">
-        <v>8.263</v>
+        <v>7.105</v>
       </c>
       <c r="O75" s="31" t="n">
-        <v>8.207000000000001</v>
+        <v>6.966</v>
       </c>
       <c r="P75" s="31" t="n">
-        <v>8.054</v>
+        <v>7.432</v>
       </c>
       <c r="Q75" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B76" s="31" t="n">
-        <v>0.657</v>
+        <v>0.629</v>
       </c>
       <c r="C76" s="31" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="D76" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="D76" s="31" t="n">
-        <v>0.278</v>
-      </c>
       <c r="E76" s="31" t="n">
-        <v>0.308</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="F76" s="31" t="n">
-        <v>0.5</v>
+        <v>1.125</v>
       </c>
       <c r="G76" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H76" s="33" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I76" s="31" t="inlineStr"/>
-      <c r="J76" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1.6</v>
+      </c>
+      <c r="H76" s="32" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I76" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J76" s="32" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="K76" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L76" s="31" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="M76" s="31" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="N76" s="31" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="O76" s="31" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="P76" s="31" t="n">
+        <v>0.459</v>
       </c>
       <c r="Q76" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B77" s="31" t="n">
-        <v>8.228999999999999</v>
-      </c>
-      <c r="C77" s="31" t="n">
-        <v>8.179</v>
-      </c>
-      <c r="D77" s="31" t="n">
-        <v>7.944</v>
-      </c>
-      <c r="E77" s="31" t="n">
-        <v>8.077</v>
-      </c>
-      <c r="F77" s="31" t="n">
-        <v>7.875</v>
-      </c>
-      <c r="G77" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I77" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K77" s="31" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L77" s="31" t="n">
-        <v>6.667</v>
-      </c>
-      <c r="M77" s="31" t="n">
-        <v>7.143</v>
-      </c>
-      <c r="N77" s="31" t="n">
-        <v>7.105</v>
-      </c>
-      <c r="O77" s="31" t="n">
-        <v>6.966</v>
-      </c>
-      <c r="P77" s="31" t="n">
-        <v>7.432</v>
-      </c>
-      <c r="Q77" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B78" s="31" t="n">
-        <v>0.629</v>
-      </c>
-      <c r="C78" s="31" t="n">
-        <v>0.536</v>
-      </c>
-      <c r="D78" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E78" s="31" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="F78" s="31" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="G78" s="31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H78" s="32" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I78" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J78" s="32" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L78" s="31" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="M78" s="31" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="N78" s="31" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="O78" s="31" t="n">
-        <v>0.483</v>
-      </c>
-      <c r="P78" s="31" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7995,7 +7995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8115,17 +8115,17 @@
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>San Diego Padres @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -8135,17 +8135,17 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 11.5</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.5757692307692307</v>
+        <v>0.6805024390243902</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-136</v>
+        <v>-213</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>108</v>
+        <v>-105</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 68.1% (fair -213). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8181,37 +8181,37 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>New York Yankees -1.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6390913043478261</v>
+        <v>0.4086785714285715</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-177</v>
+        <v>145</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-130</v>
+        <v>180</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 63.9% (fair -177). Your call.</t>
+          <t>Model 40.9% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8252,12 +8252,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8267,17 +8267,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4846521739130435</v>
+        <v>0.6332695652173914</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>106</v>
+        <v>-173</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>130</v>
+        <v>-130</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 63.3% (fair -173). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8313,37 +8313,37 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5502970297029702</v>
+        <v>0.5712512195121952</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-122</v>
+        <v>-133</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>102</v>
+        <v>-105</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8379,12 +8379,12 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -8399,17 +8399,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5318269230769231</v>
+        <v>0.549059405940594</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-114</v>
+        <v>-122</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8445,37 +8445,37 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.4787826086956522</v>
+        <v>0.5650024390243903</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>109</v>
+        <v>-130</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>130</v>
+        <v>-105</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8535,10 +8535,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5077674418604651</v>
+        <v>0.5104651162790698</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-103</v>
+        <v>-104</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>115</v>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8577,37 +8577,37 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4602118644067796</v>
+        <v>0.5272115384615385</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>117</v>
+        <v>-112</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 52.7% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8643,37 +8643,37 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4864055299539171</v>
+        <v>0.4716379310344827</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8709,17 +8709,17 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -8729,17 +8729,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4293032786885246</v>
+        <v>0.5355392156862745</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>133</v>
+        <v>-115</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8780,12 +8780,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -8795,14 +8795,14 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4607929515418502</v>
+        <v>0.4803964757709251</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>127</v>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8841,17 +8841,17 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8861,17 +8861,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4487124463519314</v>
+        <v>0.4602118644067796</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8912,32 +8912,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4469957081545065</v>
+        <v>0.6254067226890756</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>124</v>
+        <v>-167</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>133</v>
+        <v>-138</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 62.5% (fair -167). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8973,37 +8973,37 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Boston Red Sox</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox -1.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4526521739130435</v>
+        <v>0.4821171171171172</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 48.2% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9044,12 +9044,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9059,17 +9059,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4603111111111111</v>
+        <v>0.4641304347826087</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 46.4% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9110,12 +9110,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9125,17 +9125,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5899377682403434</v>
+        <v>0.4407053941908713</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-144</v>
+        <v>127</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-133</v>
+        <v>141</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9176,12 +9176,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9191,17 +9191,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5867982832618026</v>
+        <v>0.3814748201438848</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-142</v>
+        <v>162</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-133</v>
+        <v>178</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 38.1% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9234,9 +9234,537 @@
         <v/>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Texas Rangers @ Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>Texas Rangers -1.5</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>0.3998113207547169</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>165</v>
+      </c>
+      <c r="I22" s="13">
+        <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
+        <v/>
+      </c>
+      <c r="J22" s="16">
+        <f>IF($H$22="","",$F$22*IF($H$22&lt;0,-100/$H$22,$H$22/100)-(1-$F$22))</f>
+        <v/>
+      </c>
+      <c r="K22" s="17">
+        <f>IF($H$22="","",MAX(0,($F$22*IF($H$22&lt;0,-100/$H$22,$H$22/100)-(1-$F$22))/IF($H$22&lt;0,-100/$H$22,$H$22/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L22" s="18">
+        <f>IF($H$22="","",ROUND(MIN($K$22,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M22" s="12">
+        <f>IF($J$22="","",IF($J$22&lt;0,"Pass",IF($J$22&lt;'Settings'!$B$4,"Thin",IF($J$22&lt;0.06,"✅ Sharp band",IF($J$22&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N22" s="19" t="inlineStr">
+        <is>
+          <t>Model 40.0% (fair +150). Your call.</t>
+        </is>
+      </c>
+      <c r="O22" s="15" t="n"/>
+      <c r="P22" s="16">
+        <f>IF(OR($H$22="",$O$22=""),"",(1+IF($H$22&lt;0,-100/$H$22,$H$22/100))/(1+IF($O$22&lt;0,-100/$O$22,$O$22/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>New York Mets @ Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>23:07</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0.4859447004608295</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>106</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>117</v>
+      </c>
+      <c r="I23" s="13">
+        <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
+        <v/>
+      </c>
+      <c r="J23" s="16">
+        <f>IF($H$23="","",$F$23*IF($H$23&lt;0,-100/$H$23,$H$23/100)-(1-$F$23))</f>
+        <v/>
+      </c>
+      <c r="K23" s="17">
+        <f>IF($H$23="","",MAX(0,($F$23*IF($H$23&lt;0,-100/$H$23,$H$23/100)-(1-$F$23))/IF($H$23&lt;0,-100/$H$23,$H$23/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L23" s="18">
+        <f>IF($H$23="","",ROUND(MIN($K$23,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M23" s="12">
+        <f>IF($J$23="","",IF($J$23&lt;0,"Pass",IF($J$23&lt;'Settings'!$B$4,"Thin",IF($J$23&lt;0.06,"✅ Sharp band",IF($J$23&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N23" s="19" t="inlineStr">
+        <is>
+          <t>Model 48.6% (fair +106). Your call.</t>
+        </is>
+      </c>
+      <c r="O23" s="15" t="n"/>
+      <c r="P23" s="16">
+        <f>IF(OR($H$23="",$O$23=""),"",(1+IF($H$23&lt;0,-100/$H$23,$H$23/100))/(1+IF($O$23&lt;0,-100/$O$23,$O$23/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>Detroit Tigers @ New York Yankees</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>23:05</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>0.4607929515418502</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>117</v>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>127</v>
+      </c>
+      <c r="I24" s="13">
+        <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
+        <v/>
+      </c>
+      <c r="J24" s="16">
+        <f>IF($H$24="","",$F$24*IF($H$24&lt;0,-100/$H$24,$H$24/100)-(1-$F$24))</f>
+        <v/>
+      </c>
+      <c r="K24" s="17">
+        <f>IF($H$24="","",MAX(0,($F$24*IF($H$24&lt;0,-100/$H$24,$H$24/100)-(1-$F$24))/IF($H$24&lt;0,-100/$H$24,$H$24/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L24" s="18">
+        <f>IF($H$24="","",ROUND(MIN($K$24,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M24" s="12">
+        <f>IF($J$24="","",IF($J$24&lt;0,"Pass",IF($J$24&lt;'Settings'!$B$4,"Thin",IF($J$24&lt;0.06,"✅ Sharp band",IF($J$24&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N24" s="19" t="inlineStr">
+        <is>
+          <t>Model 46.1% (fair +117). Your call.</t>
+        </is>
+      </c>
+      <c r="O24" s="15" t="n"/>
+      <c r="P24" s="16">
+        <f>IF(OR($H$24="",$O$24=""),"",(1+IF($H$24&lt;0,-100/$H$24,$H$24/100))/(1+IF($O$24&lt;0,-100/$O$24,$O$24/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>22:35</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0.4487124463519314</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>123</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>133</v>
+      </c>
+      <c r="I25" s="13">
+        <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
+        <v/>
+      </c>
+      <c r="J25" s="16">
+        <f>IF($H$25="","",$F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))</f>
+        <v/>
+      </c>
+      <c r="K25" s="17">
+        <f>IF($H$25="","",MAX(0,($F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))/IF($H$25&lt;0,-100/$H$25,$H$25/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L25" s="18">
+        <f>IF($H$25="","",ROUND(MIN($K$25,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M25" s="12">
+        <f>IF($J$25="","",IF($J$25&lt;0,"Pass",IF($J$25&lt;'Settings'!$B$4,"Thin",IF($J$25&lt;0.06,"✅ Sharp band",IF($J$25&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N25" s="19" t="inlineStr">
+        <is>
+          <t>Model 44.9% (fair +123). Your call.</t>
+        </is>
+      </c>
+      <c r="O25" s="15" t="n"/>
+      <c r="P25" s="16">
+        <f>IF(OR($H$25="",$O$25=""),"",(1+IF($H$25&lt;0,-100/$H$25,$H$25/100))/(1+IF($O$25&lt;0,-100/$O$25,$O$25/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>22:35</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>0.4600881057268723</v>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>117</v>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>127</v>
+      </c>
+      <c r="I26" s="13">
+        <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
+        <v/>
+      </c>
+      <c r="J26" s="16">
+        <f>IF($H$26="","",$F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))</f>
+        <v/>
+      </c>
+      <c r="K26" s="17">
+        <f>IF($H$26="","",MAX(0,($F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))/IF($H$26&lt;0,-100/$H$26,$H$26/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L26" s="18">
+        <f>IF($H$26="","",ROUND(MIN($K$26,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M26" s="12">
+        <f>IF($J$26="","",IF($J$26&lt;0,"Pass",IF($J$26&lt;'Settings'!$B$4,"Thin",IF($J$26&lt;0.06,"✅ Sharp band",IF($J$26&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N26" s="19" t="inlineStr">
+        <is>
+          <t>Model 46.0% (fair +117). Your call.</t>
+        </is>
+      </c>
+      <c r="O26" s="15" t="n"/>
+      <c r="P26" s="16">
+        <f>IF(OR($H$26="",$O$26=""),"",(1+IF($H$26&lt;0,-100/$H$26,$H$26/100))/(1+IF($O$26&lt;0,-100/$O$26,$O$26/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>San Diego Padres @ Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Chicago Cubs -1.5</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>0.4460515021459227</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>124</v>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>133</v>
+      </c>
+      <c r="I27" s="13">
+        <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
+        <v/>
+      </c>
+      <c r="J27" s="16">
+        <f>IF($H$27="","",$F$27*IF($H$27&lt;0,-100/$H$27,$H$27/100)-(1-$F$27))</f>
+        <v/>
+      </c>
+      <c r="K27" s="17">
+        <f>IF($H$27="","",MAX(0,($F$27*IF($H$27&lt;0,-100/$H$27,$H$27/100)-(1-$F$27))/IF($H$27&lt;0,-100/$H$27,$H$27/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L27" s="18">
+        <f>IF($H$27="","",ROUND(MIN($K$27,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M27" s="12">
+        <f>IF($J$27="","",IF($J$27&lt;0,"Pass",IF($J$27&lt;'Settings'!$B$4,"Thin",IF($J$27&lt;0.06,"✅ Sharp band",IF($J$27&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N27" s="19" t="inlineStr">
+        <is>
+          <t>Model 44.6% (fair +124). Your call.</t>
+        </is>
+      </c>
+      <c r="O27" s="15" t="n"/>
+      <c r="P27" s="16">
+        <f>IF(OR($H$27="",$O$27=""),"",(1+IF($H$27&lt;0,-100/$H$27,$H$27/100))/(1+IF($O$27&lt;0,-100/$O$27,$O$27/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>Washington Nationals @ Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>Washington Nationals +1.5</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>0.6436330798479087</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>-181</v>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>-163</v>
+      </c>
+      <c r="I28" s="13">
+        <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
+        <v/>
+      </c>
+      <c r="J28" s="16">
+        <f>IF($H$28="","",$F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))</f>
+        <v/>
+      </c>
+      <c r="K28" s="17">
+        <f>IF($H$28="","",MAX(0,($F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))/IF($H$28&lt;0,-100/$H$28,$H$28/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L28" s="18">
+        <f>IF($H$28="","",ROUND(MIN($K$28,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M28" s="12">
+        <f>IF($J$28="","",IF($J$28&lt;0,"Pass",IF($J$28&lt;'Settings'!$B$4,"Thin",IF($J$28&lt;0.06,"✅ Sharp band",IF($J$28&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N28" s="19" t="inlineStr">
+        <is>
+          <t>Model 64.4% (fair -181). Your call.</t>
+        </is>
+      </c>
+      <c r="O28" s="15" t="n"/>
+      <c r="P28" s="16">
+        <f>IF(OR($H$28="",$O$28=""),"",(1+IF($H$28&lt;0,-100/$H$28,$H$28/100))/(1+IF($O$28&lt;0,-100/$O$28,$O$28/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Detroit Tigers @ New York Yankees</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>23:05</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>0.5899377682403434</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>-144</v>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>-133</v>
+      </c>
+      <c r="I29" s="13">
+        <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
+        <v/>
+      </c>
+      <c r="J29" s="16">
+        <f>IF($H$29="","",$F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))</f>
+        <v/>
+      </c>
+      <c r="K29" s="17">
+        <f>IF($H$29="","",MAX(0,($F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))/IF($H$29&lt;0,-100/$H$29,$H$29/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L29" s="18">
+        <f>IF($H$29="","",ROUND(MIN($K$29,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M29" s="12">
+        <f>IF($J$29="","",IF($J$29&lt;0,"Pass",IF($J$29&lt;'Settings'!$B$4,"Thin",IF($J$29&lt;0.06,"✅ Sharp band",IF($J$29&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N29" s="19" t="inlineStr">
+        <is>
+          <t>Model 59.0% (fair -144). Your call.</t>
+        </is>
+      </c>
+      <c r="O29" s="15" t="n"/>
+      <c r="P29" s="16">
+        <f>IF(OR($H$29="",$O$29=""),"",(1+IF($H$29&lt;0,-100/$H$29,$H$29/100))/(1+IF($O$29&lt;0,-100/$O$29,$O$29/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J21">
+  <conditionalFormatting sqref="J5:J29">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -9258,7 +9786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P100"/>
+  <dimension ref="A1:P140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9402,13 +9930,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4603111111111111</v>
+        <v>0.4600881057268723</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>117</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -9468,13 +9996,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5397220264317181</v>
+        <v>0.5399444444444444</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>-117</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-127</v>
+        <v>-125</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -9530,17 +10058,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4763</v>
+        <v>0.3786</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>110</v>
+        <v>164</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9564,7 +10092,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9596,17 +10124,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.6214</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-110</v>
+        <v>-164</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9630,7 +10158,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9672,7 +10200,7 @@
         <v>155</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9798,7 +10326,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5502970297029702</v>
+        <v>0.549059405940594</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>-122</v>
@@ -9828,7 +10356,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9864,13 +10392,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4497089108910891</v>
+        <v>0.4509215686274509</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>122</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-102</v>
+        <v>-104</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9894,7 +10422,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9936,7 +10464,7 @@
         <v>103</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -10002,7 +10530,7 @@
         <v>-103</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -10134,7 +10662,7 @@
         <v>-255</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -10332,7 +10860,7 @@
         <v>106</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10464,7 +10992,7 @@
         <v>162</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -10590,7 +11118,7 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4864055299539171</v>
+        <v>0.4859447004608295</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>106</v>
@@ -10656,13 +11184,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5135599078341013</v>
+        <v>0.5140577981651376</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>-106</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-117</v>
+        <v>-118</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10722,10 +11250,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4242502487562189</v>
+        <v>0.3375</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>-101</v>
@@ -10752,7 +11280,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 33.8% (fair +196). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10788,13 +11316,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5757692307692307</v>
+        <v>0.6625</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-136</v>
+        <v>-196</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10818,7 +11346,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 66.2% (fair -196). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -11058,7 +11586,7 @@
         <v>-157</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -11114,17 +11642,17 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4783</v>
+        <v>0.3833</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>109</v>
+        <v>161</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -11148,7 +11676,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -11180,17 +11708,17 @@
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.6167</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-109</v>
+        <v>-161</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -11214,7 +11742,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -11250,10 +11778,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4526521739130435</v>
+        <v>0.4737</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>130</v>
@@ -11280,7 +11808,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11316,13 +11844,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5473384615384616</v>
+        <v>0.5263</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-121</v>
+        <v>-111</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-134</v>
+        <v>109</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11346,7 +11874,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11520,7 +12048,7 @@
         <v>161</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -11778,13 +12306,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.3608823529411765</v>
+        <v>0.3666960352422908</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -11808,7 +12336,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 36.1% (fair +177). Your call.</t>
+          <t>Model 36.7% (fair +173). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -11844,10 +12372,10 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.6390913043478261</v>
+        <v>0.6332695652173914</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-177</v>
+        <v>-173</v>
       </c>
       <c r="H42" s="15" t="n">
         <v>-130</v>
@@ -11874,7 +12402,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 63.9% (fair -177). Your call.</t>
+          <t>Model 63.3% (fair -173). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -11916,7 +12444,7 @@
         <v>111</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>100</v>
+        <v>-101</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -12174,10 +12702,10 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4293032786885246</v>
+        <v>0.4030327868852459</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>144</v>
@@ -12204,7 +12732,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 40.3% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12240,10 +12768,10 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5706885245901639</v>
+        <v>0.5970098360655738</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-133</v>
+        <v>-148</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>-144</v>
@@ -12270,7 +12798,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 59.7% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12306,10 +12834,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.185</v>
+        <v>0.2407</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>441</v>
+        <v>315</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>117</v>
@@ -12336,7 +12864,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 18.5% (fair +441). Your call.</t>
+          <t>Model 24.1% (fair +315). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12372,13 +12900,13 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.7593</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-441</v>
+        <v>-315</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -12402,7 +12930,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 81.5% (fair -441). Your call.</t>
+          <t>Model 75.9% (fair -315). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12438,13 +12966,13 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4092</v>
+        <v>0.4460515021459227</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -12468,7 +12996,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +144). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -12504,13 +13032,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5908</v>
+        <v>0.5539694915254237</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-144</v>
+        <v>-124</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>105</v>
+        <v>-136</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -12534,7 +13062,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -144). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -12570,13 +13098,13 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4787826086956522</v>
+        <v>0.4803964757709251</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -12600,7 +13128,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -12636,10 +13164,10 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5212035242290749</v>
+        <v>0.5195810572687225</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-109</v>
+        <v>-108</v>
       </c>
       <c r="H54" s="15" t="n">
         <v>-127</v>
@@ -12666,7 +13194,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -12708,7 +13236,7 @@
         <v>107</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>-101</v>
+        <v>-103</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -12774,7 +13302,7 @@
         <v>-107</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -12906,7 +13434,7 @@
         <v>-183</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-115</v>
+        <v>-117</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -12966,13 +13494,13 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5153652173913044</v>
+        <v>0.5358815450643777</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>-106</v>
+        <v>-115</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>-130</v>
+        <v>-133</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -12996,7 +13524,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -13032,10 +13560,10 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4846521739130435</v>
+        <v>0.4641304347826087</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="H60" s="15" t="n">
         <v>130</v>
@@ -13062,7 +13590,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 46.4% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -13098,10 +13626,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.378</v>
+        <v>0.4303</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>-108</v>
@@ -13128,7 +13656,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 37.8% (fair +165). Your call.</t>
+          <t>Model 43.0% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -13164,13 +13692,13 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.622</v>
+        <v>0.5697</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-165</v>
+        <v>-132</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -13194,7 +13722,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 62.2% (fair -165). Your call.</t>
+          <t>Model 57.0% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -13230,10 +13758,10 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.4096</v>
+        <v>0.3761</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="H63" s="15" t="n">
         <v>122</v>
@@ -13260,7 +13788,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 37.6% (fair +166). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -13296,10 +13824,10 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.5904</v>
+        <v>0.6239</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-144</v>
+        <v>-166</v>
       </c>
       <c r="H64" s="15" t="n">
         <v>113</v>
@@ -13326,7 +13854,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 62.4% (fair -166). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -13859,32 +14387,32 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5318269230769231</v>
+        <v>0.5433</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-114</v>
+        <v>-119</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -13908,7 +14436,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -13925,29 +14453,29 @@
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.46815</v>
+        <v>0.4567</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H74" s="15" t="n">
         <v>100</v>
@@ -13974,7 +14502,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -13991,32 +14519,32 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Baltimore Orioles -1.5</t>
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.4068</v>
+        <v>0.4098</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -14040,7 +14568,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 40.7% (fair +146). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14057,32 +14585,32 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Chicago White Sox +1.5</t>
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.5902000000000001</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-146</v>
+        <v>-144</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>-163</v>
+        <v>160</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -14106,7 +14634,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 59.3% (fair -146). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14123,12 +14651,12 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -14138,17 +14666,17 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4100873362445415</v>
+        <v>0.5355392156862745</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>144</v>
+        <v>-115</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -14172,7 +14700,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14189,12 +14717,12 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -14204,17 +14732,17 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5899377682403434</v>
+        <v>0.4645049504950495</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-144</v>
+        <v>115</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-133</v>
+        <v>102</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -14238,7 +14766,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14255,32 +14783,32 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.505</v>
+        <v>0.5134235294117647</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-102</v>
+        <v>-106</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>122</v>
+        <v>-104</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -14304,7 +14832,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 51.3% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14321,32 +14849,32 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.495</v>
+        <v>0.4866078431372549</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14370,7 +14898,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 48.7% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14387,32 +14915,32 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Boston Red Sox</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5483</v>
+        <v>0.6001629629629629</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-121</v>
+        <v>-150</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>122</v>
+        <v>-170</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -14436,7 +14964,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 60.0% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14453,32 +14981,32 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Boston Red Sox</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Texas Rangers -1.5</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4517</v>
+        <v>0.3998113207547169</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -14502,7 +15030,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 40.0% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -14519,12 +15047,12 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
@@ -14534,17 +15062,17 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4469957081545065</v>
+        <v>0.3814748201438848</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -14568,7 +15096,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 38.1% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -14585,12 +15113,12 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
@@ -14600,17 +15128,17 @@
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5530436974789915</v>
+        <v>0.6185475524475526</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-124</v>
+        <v>-162</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-138</v>
+        <v>-186</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -14634,7 +15162,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 61.9% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -14651,32 +15179,32 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4922131455399061</v>
+        <v>0.5272115384615385</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>103</v>
+        <v>-112</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>-113</v>
+        <v>108</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -14700,7 +15228,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 52.7% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -14717,32 +15245,32 @@
       </c>
       <c r="B86" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C86" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5077674418604651</v>
+        <v>0.4728073170731708</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-103</v>
+        <v>112</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>115</v>
+        <v>-105</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -14766,7 +15294,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 47.3% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -14783,32 +15311,32 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Philadelphia Phillies -1.5</t>
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.3595057034220532</v>
+        <v>0.4586854460093897</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>178</v>
+        <v>118</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -14832,7 +15360,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 36.0% (fair +178). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -14849,32 +15377,32 @@
       </c>
       <c r="B88" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C88" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E88" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.6405222222222222</v>
+        <v>0.5412777777777777</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-178</v>
+        <v>-118</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-170</v>
+        <v>-125</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -14898,7 +15426,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 64.1% (fair -178). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -14915,12 +15443,12 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
@@ -14930,17 +15458,17 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.413175965665236</v>
+        <v>0.4100873362445415</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -14964,7 +15492,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 41.3% (fair +142). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -14981,12 +15509,12 @@
       </c>
       <c r="B90" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C90" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
@@ -14996,14 +15524,14 @@
       </c>
       <c r="E90" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.5867982832618026</v>
+        <v>0.5899377682403434</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>-142</v>
+        <v>-144</v>
       </c>
       <c r="H90" s="15" t="n">
         <v>-133</v>
@@ -15030,7 +15558,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15047,31 +15575,33 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.645</v>
+        <v>0.493921568627451</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>-182</v>
-      </c>
-      <c r="H91" s="15" t="n"/>
+        <v>102</v>
+      </c>
+      <c r="H91" s="15" t="n">
+        <v>104</v>
+      </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
         <v/>
@@ -15094,7 +15624,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 64.5% (fair -182). Your call.</t>
+          <t>Model 49.4% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15111,31 +15641,33 @@
       </c>
       <c r="B92" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.355</v>
+        <v>0.5060654377880184</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>182</v>
-      </c>
-      <c r="H92" s="15" t="n"/>
+        <v>-102</v>
+      </c>
+      <c r="H92" s="15" t="n">
+        <v>-117</v>
+      </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
         <v/>
@@ -15158,7 +15690,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 35.5% (fair +182). Your call.</t>
+          <t>Model 50.6% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -15175,31 +15707,33 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>New York Yankees -1.5</t>
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.4859</v>
+        <v>0.4086785714285715</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>106</v>
-      </c>
-      <c r="H93" s="15" t="n"/>
+        <v>145</v>
+      </c>
+      <c r="H93" s="15" t="n">
+        <v>180</v>
+      </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
         <v/>
@@ -15222,7 +15756,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 40.9% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15239,31 +15773,33 @@
       </c>
       <c r="B94" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C94" s="20" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Detroit Tigers +1.5</t>
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.5141</v>
+        <v>0.5913057553956834</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-106</v>
-      </c>
-      <c r="H94" s="15" t="n"/>
+        <v>-145</v>
+      </c>
+      <c r="H94" s="15" t="n">
+        <v>-178</v>
+      </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
         <v/>
@@ -15286,7 +15822,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 59.1% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -15303,12 +15839,12 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ Athletics</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
@@ -15318,16 +15854,18 @@
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.6152</v>
+        <v>0.4821171171171172</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>-160</v>
-      </c>
-      <c r="H95" s="15" t="n"/>
+        <v>107</v>
+      </c>
+      <c r="H95" s="15" t="n">
+        <v>122</v>
+      </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
         <v/>
@@ -15350,7 +15888,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 61.5% (fair -160). Your call.</t>
+          <t>Model 48.2% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -15367,12 +15905,12 @@
       </c>
       <c r="B96" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ Athletics</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C96" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
@@ -15382,16 +15920,18 @@
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.3848</v>
+        <v>0.5178901408450703</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>160</v>
-      </c>
-      <c r="H96" s="15" t="n"/>
+        <v>-107</v>
+      </c>
+      <c r="H96" s="15" t="n">
+        <v>-113</v>
+      </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
         <v/>
@@ -15414,7 +15954,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 38.5% (fair +160). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -15431,31 +15971,33 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.4587</v>
+        <v>0.4414</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>118</v>
-      </c>
-      <c r="H97" s="15" t="n"/>
+        <v>127</v>
+      </c>
+      <c r="H97" s="15" t="n">
+        <v>-105</v>
+      </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
         <v/>
@@ -15478,7 +16020,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -15495,31 +16037,33 @@
       </c>
       <c r="B98" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C98" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.5586</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-118</v>
-      </c>
-      <c r="H98" s="15" t="n"/>
+        <v>-127</v>
+      </c>
+      <c r="H98" s="15" t="n">
+        <v>122</v>
+      </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
         <v/>
@@ -15542,7 +16086,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -15559,31 +16103,33 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Arizona Diamondbacks</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Toronto Blue Jays -1.5</t>
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.6268</v>
+        <v>0.3528</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>-168</v>
-      </c>
-      <c r="H99" s="15" t="n"/>
+        <v>183</v>
+      </c>
+      <c r="H99" s="15" t="n">
+        <v>165</v>
+      </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
         <v/>
@@ -15606,7 +16152,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 62.7% (fair -168). Your call.</t>
+          <t>Model 35.3% (fair +183). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -15623,31 +16169,33 @@
       </c>
       <c r="B100" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Arizona Diamondbacks</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C100" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D100" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>New York Mets +1.5</t>
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.3732</v>
+        <v>0.6472</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>168</v>
-      </c>
-      <c r="H100" s="15" t="n"/>
+        <v>-183</v>
+      </c>
+      <c r="H100" s="15" t="n">
+        <v>172</v>
+      </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
         <v/>
@@ -15670,7 +16218,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 37.3% (fair +168). Your call.</t>
+          <t>Model 64.7% (fair -183). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -15679,9 +16227,2629 @@
         <v/>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>Washington Nationals @ Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="F101" s="13" t="n">
+        <v>0.5483</v>
+      </c>
+      <c r="G101" s="14" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H101" s="15" t="n">
+        <v>122</v>
+      </c>
+      <c r="I101" s="13">
+        <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
+        <v/>
+      </c>
+      <c r="J101" s="16">
+        <f>IF($H$101="","",$F$101*IF($H$101&lt;0,-100/$H$101,$H$101/100)-(1-$F$101))</f>
+        <v/>
+      </c>
+      <c r="K101" s="17">
+        <f>IF($H$101="","",MAX(0,($F$101*IF($H$101&lt;0,-100/$H$101,$H$101/100)-(1-$F$101))/IF($H$101&lt;0,-100/$H$101,$H$101/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L101" s="18">
+        <f>IF($H$101="","",ROUND(MIN($K$101,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M101" s="12">
+        <f>IF($J$101="","",IF($J$101&lt;0,"Pass",IF($J$101&lt;'Settings'!$B$4,"Thin",IF($J$101&lt;0.06,"✅ Sharp band",IF($J$101&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N101" s="19" t="inlineStr">
+        <is>
+          <t>Model 54.8% (fair -121). Your call.</t>
+        </is>
+      </c>
+      <c r="O101" s="15" t="n"/>
+      <c r="P101" s="16">
+        <f>IF(OR($H$101="",$O$101=""),"",(1+IF($H$101&lt;0,-100/$H$101,$H$101/100))/(1+IF($O$101&lt;0,-100/$O$101,$O$101/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B102" s="20" t="inlineStr">
+        <is>
+          <t>Washington Nationals @ Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="C102" s="20" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="D102" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E102" s="20" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="F102" s="13" t="n">
+        <v>0.4517</v>
+      </c>
+      <c r="G102" s="14" t="n">
+        <v>121</v>
+      </c>
+      <c r="H102" s="15" t="n">
+        <v>133</v>
+      </c>
+      <c r="I102" s="13">
+        <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
+        <v/>
+      </c>
+      <c r="J102" s="16">
+        <f>IF($H$102="","",$F$102*IF($H$102&lt;0,-100/$H$102,$H$102/100)-(1-$F$102))</f>
+        <v/>
+      </c>
+      <c r="K102" s="17">
+        <f>IF($H$102="","",MAX(0,($F$102*IF($H$102&lt;0,-100/$H$102,$H$102/100)-(1-$F$102))/IF($H$102&lt;0,-100/$H$102,$H$102/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L102" s="18">
+        <f>IF($H$102="","",ROUND(MIN($K$102,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M102" s="12">
+        <f>IF($J$102="","",IF($J$102&lt;0,"Pass",IF($J$102&lt;'Settings'!$B$4,"Thin",IF($J$102&lt;0.06,"✅ Sharp band",IF($J$102&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N102" s="19" t="inlineStr">
+        <is>
+          <t>Model 45.2% (fair +121). Your call.</t>
+        </is>
+      </c>
+      <c r="O102" s="15" t="n"/>
+      <c r="P102" s="16">
+        <f>IF(OR($H$102="",$O$102=""),"",(1+IF($H$102&lt;0,-100/$H$102,$H$102/100))/(1+IF($O$102&lt;0,-100/$O$102,$O$102/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>Washington Nationals @ Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>Over 10.5</t>
+        </is>
+      </c>
+      <c r="F103" s="13" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="G103" s="14" t="n">
+        <v>165</v>
+      </c>
+      <c r="H103" s="15" t="n">
+        <v>122</v>
+      </c>
+      <c r="I103" s="13">
+        <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
+        <v/>
+      </c>
+      <c r="J103" s="16">
+        <f>IF($H$103="","",$F$103*IF($H$103&lt;0,-100/$H$103,$H$103/100)-(1-$F$103))</f>
+        <v/>
+      </c>
+      <c r="K103" s="17">
+        <f>IF($H$103="","",MAX(0,($F$103*IF($H$103&lt;0,-100/$H$103,$H$103/100)-(1-$F$103))/IF($H$103&lt;0,-100/$H$103,$H$103/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L103" s="18">
+        <f>IF($H$103="","",ROUND(MIN($K$103,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M103" s="12">
+        <f>IF($J$103="","",IF($J$103&lt;0,"Pass",IF($J$103&lt;'Settings'!$B$4,"Thin",IF($J$103&lt;0.06,"✅ Sharp band",IF($J$103&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N103" s="19" t="inlineStr">
+        <is>
+          <t>Model 37.7% (fair +165). Your call.</t>
+        </is>
+      </c>
+      <c r="O103" s="15" t="n"/>
+      <c r="P103" s="16">
+        <f>IF(OR($H$103="",$O$103=""),"",(1+IF($H$103&lt;0,-100/$H$103,$H$103/100))/(1+IF($O$103&lt;0,-100/$O$103,$O$103/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B104" s="20" t="inlineStr">
+        <is>
+          <t>Washington Nationals @ Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="C104" s="20" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="D104" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E104" s="20" t="inlineStr">
+        <is>
+          <t>Under 10.5</t>
+        </is>
+      </c>
+      <c r="F104" s="13" t="n">
+        <v>0.6231</v>
+      </c>
+      <c r="G104" s="14" t="n">
+        <v>-165</v>
+      </c>
+      <c r="H104" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I104" s="13">
+        <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
+        <v/>
+      </c>
+      <c r="J104" s="16">
+        <f>IF($H$104="","",$F$104*IF($H$104&lt;0,-100/$H$104,$H$104/100)-(1-$F$104))</f>
+        <v/>
+      </c>
+      <c r="K104" s="17">
+        <f>IF($H$104="","",MAX(0,($F$104*IF($H$104&lt;0,-100/$H$104,$H$104/100)-(1-$F$104))/IF($H$104&lt;0,-100/$H$104,$H$104/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L104" s="18">
+        <f>IF($H$104="","",ROUND(MIN($K$104,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M104" s="12">
+        <f>IF($J$104="","",IF($J$104&lt;0,"Pass",IF($J$104&lt;'Settings'!$B$4,"Thin",IF($J$104&lt;0.06,"✅ Sharp band",IF($J$104&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N104" s="19" t="inlineStr">
+        <is>
+          <t>Model 62.3% (fair -165). Your call.</t>
+        </is>
+      </c>
+      <c r="O104" s="15" t="n"/>
+      <c r="P104" s="16">
+        <f>IF(OR($H$104="",$O$104=""),"",(1+IF($H$104&lt;0,-100/$H$104,$H$104/100))/(1+IF($O$104&lt;0,-100/$O$104,$O$104/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>Washington Nationals @ Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>Boston Red Sox -1.5</t>
+        </is>
+      </c>
+      <c r="F105" s="13" t="n">
+        <v>0.3563461538461538</v>
+      </c>
+      <c r="G105" s="14" t="n">
+        <v>181</v>
+      </c>
+      <c r="H105" s="15" t="n">
+        <v>160</v>
+      </c>
+      <c r="I105" s="13">
+        <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
+        <v/>
+      </c>
+      <c r="J105" s="16">
+        <f>IF($H$105="","",$F$105*IF($H$105&lt;0,-100/$H$105,$H$105/100)-(1-$F$105))</f>
+        <v/>
+      </c>
+      <c r="K105" s="17">
+        <f>IF($H$105="","",MAX(0,($F$105*IF($H$105&lt;0,-100/$H$105,$H$105/100)-(1-$F$105))/IF($H$105&lt;0,-100/$H$105,$H$105/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L105" s="18">
+        <f>IF($H$105="","",ROUND(MIN($K$105,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M105" s="12">
+        <f>IF($J$105="","",IF($J$105&lt;0,"Pass",IF($J$105&lt;'Settings'!$B$4,"Thin",IF($J$105&lt;0.06,"✅ Sharp band",IF($J$105&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N105" s="19" t="inlineStr">
+        <is>
+          <t>Model 35.6% (fair +181). Your call.</t>
+        </is>
+      </c>
+      <c r="O105" s="15" t="n"/>
+      <c r="P105" s="16">
+        <f>IF(OR($H$105="",$O$105=""),"",(1+IF($H$105&lt;0,-100/$H$105,$H$105/100))/(1+IF($O$105&lt;0,-100/$O$105,$O$105/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B106" s="20" t="inlineStr">
+        <is>
+          <t>Washington Nationals @ Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="C106" s="20" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="D106" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E106" s="20" t="inlineStr">
+        <is>
+          <t>Washington Nationals +1.5</t>
+        </is>
+      </c>
+      <c r="F106" s="13" t="n">
+        <v>0.6436330798479087</v>
+      </c>
+      <c r="G106" s="14" t="n">
+        <v>-181</v>
+      </c>
+      <c r="H106" s="15" t="n">
+        <v>-163</v>
+      </c>
+      <c r="I106" s="13">
+        <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
+        <v/>
+      </c>
+      <c r="J106" s="16">
+        <f>IF($H$106="","",$F$106*IF($H$106&lt;0,-100/$H$106,$H$106/100)-(1-$F$106))</f>
+        <v/>
+      </c>
+      <c r="K106" s="17">
+        <f>IF($H$106="","",MAX(0,($F$106*IF($H$106&lt;0,-100/$H$106,$H$106/100)-(1-$F$106))/IF($H$106&lt;0,-100/$H$106,$H$106/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L106" s="18">
+        <f>IF($H$106="","",ROUND(MIN($K$106,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M106" s="12">
+        <f>IF($J$106="","",IF($J$106&lt;0,"Pass",IF($J$106&lt;'Settings'!$B$4,"Thin",IF($J$106&lt;0.06,"✅ Sharp band",IF($J$106&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N106" s="19" t="inlineStr">
+        <is>
+          <t>Model 64.4% (fair -181). Your call.</t>
+        </is>
+      </c>
+      <c r="O106" s="15" t="n"/>
+      <c r="P106" s="16">
+        <f>IF(OR($H$106="",$O$106=""),"",(1+IF($H$106&lt;0,-100/$H$106,$H$106/100))/(1+IF($O$106&lt;0,-100/$O$106,$O$106/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="F107" s="13" t="n">
+        <v>0.4407053941908713</v>
+      </c>
+      <c r="G107" s="14" t="n">
+        <v>127</v>
+      </c>
+      <c r="H107" s="15" t="n">
+        <v>141</v>
+      </c>
+      <c r="I107" s="13">
+        <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
+        <v/>
+      </c>
+      <c r="J107" s="16">
+        <f>IF($H$107="","",$F$107*IF($H$107&lt;0,-100/$H$107,$H$107/100)-(1-$F$107))</f>
+        <v/>
+      </c>
+      <c r="K107" s="17">
+        <f>IF($H$107="","",MAX(0,($F$107*IF($H$107&lt;0,-100/$H$107,$H$107/100)-(1-$F$107))/IF($H$107&lt;0,-100/$H$107,$H$107/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L107" s="18">
+        <f>IF($H$107="","",ROUND(MIN($K$107,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M107" s="12">
+        <f>IF($J$107="","",IF($J$107&lt;0,"Pass",IF($J$107&lt;'Settings'!$B$4,"Thin",IF($J$107&lt;0.06,"✅ Sharp band",IF($J$107&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N107" s="19" t="inlineStr">
+        <is>
+          <t>Model 44.1% (fair +127). Your call.</t>
+        </is>
+      </c>
+      <c r="O107" s="15" t="n"/>
+      <c r="P107" s="16">
+        <f>IF(OR($H$107="",$O$107=""),"",(1+IF($H$107&lt;0,-100/$H$107,$H$107/100))/(1+IF($O$107&lt;0,-100/$O$107,$O$107/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B108" s="20" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="C108" s="20" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="D108" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E108" s="20" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="F108" s="13" t="n">
+        <v>0.5592983606557377</v>
+      </c>
+      <c r="G108" s="14" t="n">
+        <v>-127</v>
+      </c>
+      <c r="H108" s="15" t="n">
+        <v>-144</v>
+      </c>
+      <c r="I108" s="13">
+        <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
+        <v/>
+      </c>
+      <c r="J108" s="16">
+        <f>IF($H$108="","",$F$108*IF($H$108&lt;0,-100/$H$108,$H$108/100)-(1-$F$108))</f>
+        <v/>
+      </c>
+      <c r="K108" s="17">
+        <f>IF($H$108="","",MAX(0,($F$108*IF($H$108&lt;0,-100/$H$108,$H$108/100)-(1-$F$108))/IF($H$108&lt;0,-100/$H$108,$H$108/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L108" s="18">
+        <f>IF($H$108="","",ROUND(MIN($K$108,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M108" s="12">
+        <f>IF($J$108="","",IF($J$108&lt;0,"Pass",IF($J$108&lt;'Settings'!$B$4,"Thin",IF($J$108&lt;0.06,"✅ Sharp band",IF($J$108&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N108" s="19" t="inlineStr">
+        <is>
+          <t>Model 55.9% (fair -127). Your call.</t>
+        </is>
+      </c>
+      <c r="O108" s="15" t="n"/>
+      <c r="P108" s="16">
+        <f>IF(OR($H$108="",$O$108=""),"",(1+IF($H$108&lt;0,-100/$H$108,$H$108/100))/(1+IF($O$108&lt;0,-100/$O$108,$O$108/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>Over 9.5</t>
+        </is>
+      </c>
+      <c r="F109" s="13" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="G109" s="14" t="n">
+        <v>130</v>
+      </c>
+      <c r="H109" s="15" t="n">
+        <v>104</v>
+      </c>
+      <c r="I109" s="13">
+        <f>IF($H$109="","",IF($H$109&lt;0,-$H$109/(-$H$109+100),100/($H$109+100)))</f>
+        <v/>
+      </c>
+      <c r="J109" s="16">
+        <f>IF($H$109="","",$F$109*IF($H$109&lt;0,-100/$H$109,$H$109/100)-(1-$F$109))</f>
+        <v/>
+      </c>
+      <c r="K109" s="17">
+        <f>IF($H$109="","",MAX(0,($F$109*IF($H$109&lt;0,-100/$H$109,$H$109/100)-(1-$F$109))/IF($H$109&lt;0,-100/$H$109,$H$109/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L109" s="18">
+        <f>IF($H$109="","",ROUND(MIN($K$109,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M109" s="12">
+        <f>IF($J$109="","",IF($J$109&lt;0,"Pass",IF($J$109&lt;'Settings'!$B$4,"Thin",IF($J$109&lt;0.06,"✅ Sharp band",IF($J$109&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N109" s="19" t="inlineStr">
+        <is>
+          <t>Model 43.5% (fair +130). Your call.</t>
+        </is>
+      </c>
+      <c r="O109" s="15" t="n"/>
+      <c r="P109" s="16">
+        <f>IF(OR($H$109="",$O$109=""),"",(1+IF($H$109&lt;0,-100/$H$109,$H$109/100))/(1+IF($O$109&lt;0,-100/$O$109,$O$109/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B110" s="20" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="C110" s="20" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="D110" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E110" s="20" t="inlineStr">
+        <is>
+          <t>Under 9.5</t>
+        </is>
+      </c>
+      <c r="F110" s="13" t="n">
+        <v>0.5650024390243903</v>
+      </c>
+      <c r="G110" s="14" t="n">
+        <v>-130</v>
+      </c>
+      <c r="H110" s="15" t="n">
+        <v>-105</v>
+      </c>
+      <c r="I110" s="13">
+        <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
+        <v/>
+      </c>
+      <c r="J110" s="16">
+        <f>IF($H$110="","",$F$110*IF($H$110&lt;0,-100/$H$110,$H$110/100)-(1-$F$110))</f>
+        <v/>
+      </c>
+      <c r="K110" s="17">
+        <f>IF($H$110="","",MAX(0,($F$110*IF($H$110&lt;0,-100/$H$110,$H$110/100)-(1-$F$110))/IF($H$110&lt;0,-100/$H$110,$H$110/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L110" s="18">
+        <f>IF($H$110="","",ROUND(MIN($K$110,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M110" s="12">
+        <f>IF($J$110="","",IF($J$110&lt;0,"Pass",IF($J$110&lt;'Settings'!$B$4,"Thin",IF($J$110&lt;0.06,"✅ Sharp band",IF($J$110&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N110" s="19" t="inlineStr">
+        <is>
+          <t>Model 56.5% (fair -130). Your call.</t>
+        </is>
+      </c>
+      <c r="O110" s="15" t="n"/>
+      <c r="P110" s="16">
+        <f>IF(OR($H$110="",$O$110=""),"",(1+IF($H$110&lt;0,-100/$H$110,$H$110/100))/(1+IF($O$110&lt;0,-100/$O$110,$O$110/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>Atlanta Braves -1.5</t>
+        </is>
+      </c>
+      <c r="F111" s="13" t="n">
+        <v>0.4051282051282051</v>
+      </c>
+      <c r="G111" s="14" t="n">
+        <v>147</v>
+      </c>
+      <c r="H111" s="15" t="n">
+        <v>134</v>
+      </c>
+      <c r="I111" s="13">
+        <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
+        <v/>
+      </c>
+      <c r="J111" s="16">
+        <f>IF($H$111="","",$F$111*IF($H$111&lt;0,-100/$H$111,$H$111/100)-(1-$F$111))</f>
+        <v/>
+      </c>
+      <c r="K111" s="17">
+        <f>IF($H$111="","",MAX(0,($F$111*IF($H$111&lt;0,-100/$H$111,$H$111/100)-(1-$F$111))/IF($H$111&lt;0,-100/$H$111,$H$111/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L111" s="18">
+        <f>IF($H$111="","",ROUND(MIN($K$111,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M111" s="12">
+        <f>IF($J$111="","",IF($J$111&lt;0,"Pass",IF($J$111&lt;'Settings'!$B$4,"Thin",IF($J$111&lt;0.06,"✅ Sharp band",IF($J$111&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N111" s="19" t="inlineStr">
+        <is>
+          <t>Model 40.5% (fair +147). Your call.</t>
+        </is>
+      </c>
+      <c r="O111" s="15" t="n"/>
+      <c r="P111" s="16">
+        <f>IF(OR($H$111="",$O$111=""),"",(1+IF($H$111&lt;0,-100/$H$111,$H$111/100))/(1+IF($O$111&lt;0,-100/$O$111,$O$111/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B112" s="20" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="C112" s="20" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="D112" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E112" s="20" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals +1.5</t>
+        </is>
+      </c>
+      <c r="F112" s="13" t="n">
+        <v>0.59484</v>
+      </c>
+      <c r="G112" s="14" t="n">
+        <v>-147</v>
+      </c>
+      <c r="H112" s="15" t="n">
+        <v>-150</v>
+      </c>
+      <c r="I112" s="13">
+        <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
+        <v/>
+      </c>
+      <c r="J112" s="16">
+        <f>IF($H$112="","",$F$112*IF($H$112&lt;0,-100/$H$112,$H$112/100)-(1-$F$112))</f>
+        <v/>
+      </c>
+      <c r="K112" s="17">
+        <f>IF($H$112="","",MAX(0,($F$112*IF($H$112&lt;0,-100/$H$112,$H$112/100)-(1-$F$112))/IF($H$112&lt;0,-100/$H$112,$H$112/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L112" s="18">
+        <f>IF($H$112="","",ROUND(MIN($K$112,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M112" s="12">
+        <f>IF($J$112="","",IF($J$112&lt;0,"Pass",IF($J$112&lt;'Settings'!$B$4,"Thin",IF($J$112&lt;0.06,"✅ Sharp band",IF($J$112&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N112" s="19" t="inlineStr">
+        <is>
+          <t>Model 59.5% (fair -147). Your call.</t>
+        </is>
+      </c>
+      <c r="O112" s="15" t="n"/>
+      <c r="P112" s="16">
+        <f>IF(OR($H$112="",$O$112=""),"",(1+IF($H$112&lt;0,-100/$H$112,$H$112/100))/(1+IF($O$112&lt;0,-100/$O$112,$O$112/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="F113" s="13" t="n">
+        <v>0.4895307692307692</v>
+      </c>
+      <c r="G113" s="14" t="n">
+        <v>104</v>
+      </c>
+      <c r="H113" s="15" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I113" s="13">
+        <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
+        <v/>
+      </c>
+      <c r="J113" s="16">
+        <f>IF($H$113="","",$F$113*IF($H$113&lt;0,-100/$H$113,$H$113/100)-(1-$F$113))</f>
+        <v/>
+      </c>
+      <c r="K113" s="17">
+        <f>IF($H$113="","",MAX(0,($F$113*IF($H$113&lt;0,-100/$H$113,$H$113/100)-(1-$F$113))/IF($H$113&lt;0,-100/$H$113,$H$113/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L113" s="18">
+        <f>IF($H$113="","",ROUND(MIN($K$113,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M113" s="12">
+        <f>IF($J$113="","",IF($J$113&lt;0,"Pass",IF($J$113&lt;'Settings'!$B$4,"Thin",IF($J$113&lt;0.06,"✅ Sharp band",IF($J$113&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N113" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.0% (fair +104). Your call.</t>
+        </is>
+      </c>
+      <c r="O113" s="15" t="n"/>
+      <c r="P113" s="16">
+        <f>IF(OR($H$113="",$O$113=""),"",(1+IF($H$113&lt;0,-100/$H$113,$H$113/100))/(1+IF($O$113&lt;0,-100/$O$113,$O$113/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B114" s="20" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="C114" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D114" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E114" s="20" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="F114" s="13" t="n">
+        <v>0.5104651162790698</v>
+      </c>
+      <c r="G114" s="14" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H114" s="15" t="n">
+        <v>115</v>
+      </c>
+      <c r="I114" s="13">
+        <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
+        <v/>
+      </c>
+      <c r="J114" s="16">
+        <f>IF($H$114="","",$F$114*IF($H$114&lt;0,-100/$H$114,$H$114/100)-(1-$F$114))</f>
+        <v/>
+      </c>
+      <c r="K114" s="17">
+        <f>IF($H$114="","",MAX(0,($F$114*IF($H$114&lt;0,-100/$H$114,$H$114/100)-(1-$F$114))/IF($H$114&lt;0,-100/$H$114,$H$114/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L114" s="18">
+        <f>IF($H$114="","",ROUND(MIN($K$114,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M114" s="12">
+        <f>IF($J$114="","",IF($J$114&lt;0,"Pass",IF($J$114&lt;'Settings'!$B$4,"Thin",IF($J$114&lt;0.06,"✅ Sharp band",IF($J$114&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N114" s="19" t="inlineStr">
+        <is>
+          <t>Model 51.0% (fair -104). Your call.</t>
+        </is>
+      </c>
+      <c r="O114" s="15" t="n"/>
+      <c r="P114" s="16">
+        <f>IF(OR($H$114="",$O$114=""),"",(1+IF($H$114&lt;0,-100/$H$114,$H$114/100))/(1+IF($O$114&lt;0,-100/$O$114,$O$114/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="inlineStr">
+        <is>
+          <t>Over 10.5</t>
+        </is>
+      </c>
+      <c r="F115" s="13" t="n">
+        <v>0.4287534653465346</v>
+      </c>
+      <c r="G115" s="14" t="n">
+        <v>133</v>
+      </c>
+      <c r="H115" s="15" t="n">
+        <v>-102</v>
+      </c>
+      <c r="I115" s="13">
+        <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
+        <v/>
+      </c>
+      <c r="J115" s="16">
+        <f>IF($H$115="","",$F$115*IF($H$115&lt;0,-100/$H$115,$H$115/100)-(1-$F$115))</f>
+        <v/>
+      </c>
+      <c r="K115" s="17">
+        <f>IF($H$115="","",MAX(0,($F$115*IF($H$115&lt;0,-100/$H$115,$H$115/100)-(1-$F$115))/IF($H$115&lt;0,-100/$H$115,$H$115/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L115" s="18">
+        <f>IF($H$115="","",ROUND(MIN($K$115,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M115" s="12">
+        <f>IF($J$115="","",IF($J$115&lt;0,"Pass",IF($J$115&lt;'Settings'!$B$4,"Thin",IF($J$115&lt;0.06,"✅ Sharp band",IF($J$115&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N115" s="19" t="inlineStr">
+        <is>
+          <t>Model 42.9% (fair +133). Your call.</t>
+        </is>
+      </c>
+      <c r="O115" s="15" t="n"/>
+      <c r="P115" s="16">
+        <f>IF(OR($H$115="",$O$115=""),"",(1+IF($H$115&lt;0,-100/$H$115,$H$115/100))/(1+IF($O$115&lt;0,-100/$O$115,$O$115/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B116" s="20" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="C116" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D116" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E116" s="20" t="inlineStr">
+        <is>
+          <t>Under 10.5</t>
+        </is>
+      </c>
+      <c r="F116" s="13" t="n">
+        <v>0.5712512195121952</v>
+      </c>
+      <c r="G116" s="14" t="n">
+        <v>-133</v>
+      </c>
+      <c r="H116" s="15" t="n">
+        <v>-105</v>
+      </c>
+      <c r="I116" s="13">
+        <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
+        <v/>
+      </c>
+      <c r="J116" s="16">
+        <f>IF($H$116="","",$F$116*IF($H$116&lt;0,-100/$H$116,$H$116/100)-(1-$F$116))</f>
+        <v/>
+      </c>
+      <c r="K116" s="17">
+        <f>IF($H$116="","",MAX(0,($F$116*IF($H$116&lt;0,-100/$H$116,$H$116/100)-(1-$F$116))/IF($H$116&lt;0,-100/$H$116,$H$116/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L116" s="18">
+        <f>IF($H$116="","",ROUND(MIN($K$116,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M116" s="12">
+        <f>IF($J$116="","",IF($J$116&lt;0,"Pass",IF($J$116&lt;'Settings'!$B$4,"Thin",IF($J$116&lt;0.06,"✅ Sharp band",IF($J$116&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N116" s="19" t="inlineStr">
+        <is>
+          <t>Model 57.1% (fair -133). Your call.</t>
+        </is>
+      </c>
+      <c r="O116" s="15" t="n"/>
+      <c r="P116" s="16">
+        <f>IF(OR($H$116="",$O$116=""),"",(1+IF($H$116&lt;0,-100/$H$116,$H$116/100))/(1+IF($O$116&lt;0,-100/$O$116,$O$116/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>Kansas City Royals +1.5</t>
+        </is>
+      </c>
+      <c r="F117" s="13" t="n">
+        <v>0.6254067226890756</v>
+      </c>
+      <c r="G117" s="14" t="n">
+        <v>-167</v>
+      </c>
+      <c r="H117" s="15" t="n">
+        <v>-138</v>
+      </c>
+      <c r="I117" s="13">
+        <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
+        <v/>
+      </c>
+      <c r="J117" s="16">
+        <f>IF($H$117="","",$F$117*IF($H$117&lt;0,-100/$H$117,$H$117/100)-(1-$F$117))</f>
+        <v/>
+      </c>
+      <c r="K117" s="17">
+        <f>IF($H$117="","",MAX(0,($F$117*IF($H$117&lt;0,-100/$H$117,$H$117/100)-(1-$F$117))/IF($H$117&lt;0,-100/$H$117,$H$117/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L117" s="18">
+        <f>IF($H$117="","",ROUND(MIN($K$117,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M117" s="12">
+        <f>IF($J$117="","",IF($J$117&lt;0,"Pass",IF($J$117&lt;'Settings'!$B$4,"Thin",IF($J$117&lt;0.06,"✅ Sharp band",IF($J$117&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N117" s="19" t="inlineStr">
+        <is>
+          <t>Model 62.5% (fair -167). Your call.</t>
+        </is>
+      </c>
+      <c r="O117" s="15" t="n"/>
+      <c r="P117" s="16">
+        <f>IF(OR($H$117="",$O$117=""),"",(1+IF($H$117&lt;0,-100/$H$117,$H$117/100))/(1+IF($O$117&lt;0,-100/$O$117,$O$117/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B118" s="20" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="C118" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D118" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E118" s="20" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays -1.5</t>
+        </is>
+      </c>
+      <c r="F118" s="13" t="n">
+        <v>0.3745833333333334</v>
+      </c>
+      <c r="G118" s="14" t="n">
+        <v>167</v>
+      </c>
+      <c r="H118" s="15" t="n">
+        <v>140</v>
+      </c>
+      <c r="I118" s="13">
+        <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
+        <v/>
+      </c>
+      <c r="J118" s="16">
+        <f>IF($H$118="","",$F$118*IF($H$118&lt;0,-100/$H$118,$H$118/100)-(1-$F$118))</f>
+        <v/>
+      </c>
+      <c r="K118" s="17">
+        <f>IF($H$118="","",MAX(0,($F$118*IF($H$118&lt;0,-100/$H$118,$H$118/100)-(1-$F$118))/IF($H$118&lt;0,-100/$H$118,$H$118/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L118" s="18">
+        <f>IF($H$118="","",ROUND(MIN($K$118,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M118" s="12">
+        <f>IF($J$118="","",IF($J$118&lt;0,"Pass",IF($J$118&lt;'Settings'!$B$4,"Thin",IF($J$118&lt;0.06,"✅ Sharp band",IF($J$118&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N118" s="19" t="inlineStr">
+        <is>
+          <t>Model 37.5% (fair +167). Your call.</t>
+        </is>
+      </c>
+      <c r="O118" s="15" t="n"/>
+      <c r="P118" s="16">
+        <f>IF(OR($H$118="",$O$118=""),"",(1+IF($H$118&lt;0,-100/$H$118,$H$118/100))/(1+IF($O$118&lt;0,-100/$O$118,$O$118/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="F119" s="13" t="n">
+        <v>0.3634765625</v>
+      </c>
+      <c r="G119" s="14" t="n">
+        <v>175</v>
+      </c>
+      <c r="H119" s="15" t="n">
+        <v>156</v>
+      </c>
+      <c r="I119" s="13">
+        <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
+        <v/>
+      </c>
+      <c r="J119" s="16">
+        <f>IF($H$119="","",$F$119*IF($H$119&lt;0,-100/$H$119,$H$119/100)-(1-$F$119))</f>
+        <v/>
+      </c>
+      <c r="K119" s="17">
+        <f>IF($H$119="","",MAX(0,($F$119*IF($H$119&lt;0,-100/$H$119,$H$119/100)-(1-$F$119))/IF($H$119&lt;0,-100/$H$119,$H$119/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L119" s="18">
+        <f>IF($H$119="","",ROUND(MIN($K$119,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M119" s="12">
+        <f>IF($J$119="","",IF($J$119&lt;0,"Pass",IF($J$119&lt;'Settings'!$B$4,"Thin",IF($J$119&lt;0.06,"✅ Sharp band",IF($J$119&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N119" s="19" t="inlineStr">
+        <is>
+          <t>Model 36.3% (fair +175). Your call.</t>
+        </is>
+      </c>
+      <c r="O119" s="15" t="n"/>
+      <c r="P119" s="16">
+        <f>IF(OR($H$119="",$O$119=""),"",(1+IF($H$119&lt;0,-100/$H$119,$H$119/100))/(1+IF($O$119&lt;0,-100/$O$119,$O$119/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B120" s="20" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="C120" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D120" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E120" s="20" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="F120" s="13" t="n">
+        <v>0.6365389513108615</v>
+      </c>
+      <c r="G120" s="14" t="n">
+        <v>-175</v>
+      </c>
+      <c r="H120" s="15" t="n">
+        <v>-167</v>
+      </c>
+      <c r="I120" s="13">
+        <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
+        <v/>
+      </c>
+      <c r="J120" s="16">
+        <f>IF($H$120="","",$F$120*IF($H$120&lt;0,-100/$H$120,$H$120/100)-(1-$F$120))</f>
+        <v/>
+      </c>
+      <c r="K120" s="17">
+        <f>IF($H$120="","",MAX(0,($F$120*IF($H$120&lt;0,-100/$H$120,$H$120/100)-(1-$F$120))/IF($H$120&lt;0,-100/$H$120,$H$120/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L120" s="18">
+        <f>IF($H$120="","",ROUND(MIN($K$120,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M120" s="12">
+        <f>IF($J$120="","",IF($J$120&lt;0,"Pass",IF($J$120&lt;'Settings'!$B$4,"Thin",IF($J$120&lt;0.06,"✅ Sharp band",IF($J$120&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N120" s="19" t="inlineStr">
+        <is>
+          <t>Model 63.7% (fair -175). Your call.</t>
+        </is>
+      </c>
+      <c r="O120" s="15" t="n"/>
+      <c r="P120" s="16">
+        <f>IF(OR($H$120="",$O$120=""),"",(1+IF($H$120&lt;0,-100/$H$120,$H$120/100))/(1+IF($O$120&lt;0,-100/$O$120,$O$120/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>Over 9</t>
+        </is>
+      </c>
+      <c r="F121" s="13" t="n">
+        <v>0.49195</v>
+      </c>
+      <c r="G121" s="14" t="n">
+        <v>103</v>
+      </c>
+      <c r="H121" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I121" s="13">
+        <f>IF($H$121="","",IF($H$121&lt;0,-$H$121/(-$H$121+100),100/($H$121+100)))</f>
+        <v/>
+      </c>
+      <c r="J121" s="16">
+        <f>IF($H$121="","",$F$121*IF($H$121&lt;0,-100/$H$121,$H$121/100)-(1-$F$121))</f>
+        <v/>
+      </c>
+      <c r="K121" s="17">
+        <f>IF($H$121="","",MAX(0,($F$121*IF($H$121&lt;0,-100/$H$121,$H$121/100)-(1-$F$121))/IF($H$121&lt;0,-100/$H$121,$H$121/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L121" s="18">
+        <f>IF($H$121="","",ROUND(MIN($K$121,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M121" s="12">
+        <f>IF($J$121="","",IF($J$121&lt;0,"Pass",IF($J$121&lt;'Settings'!$B$4,"Thin",IF($J$121&lt;0.06,"✅ Sharp band",IF($J$121&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N121" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.2% (fair +103). Your call.</t>
+        </is>
+      </c>
+      <c r="O121" s="15" t="n"/>
+      <c r="P121" s="16">
+        <f>IF(OR($H$121="",$O$121=""),"",(1+IF($H$121&lt;0,-100/$H$121,$H$121/100))/(1+IF($O$121&lt;0,-100/$O$121,$O$121/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B122" s="20" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="C122" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D122" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E122" s="20" t="inlineStr">
+        <is>
+          <t>Under 9</t>
+        </is>
+      </c>
+      <c r="F122" s="13" t="n">
+        <v>0.50805</v>
+      </c>
+      <c r="G122" s="14" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H122" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I122" s="13">
+        <f>IF($H$122="","",IF($H$122&lt;0,-$H$122/(-$H$122+100),100/($H$122+100)))</f>
+        <v/>
+      </c>
+      <c r="J122" s="16">
+        <f>IF($H$122="","",$F$122*IF($H$122&lt;0,-100/$H$122,$H$122/100)-(1-$F$122))</f>
+        <v/>
+      </c>
+      <c r="K122" s="17">
+        <f>IF($H$122="","",MAX(0,($F$122*IF($H$122&lt;0,-100/$H$122,$H$122/100)-(1-$F$122))/IF($H$122&lt;0,-100/$H$122,$H$122/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L122" s="18">
+        <f>IF($H$122="","",ROUND(MIN($K$122,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M122" s="12">
+        <f>IF($J$122="","",IF($J$122&lt;0,"Pass",IF($J$122&lt;'Settings'!$B$4,"Thin",IF($J$122&lt;0.06,"✅ Sharp band",IF($J$122&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N122" s="19" t="inlineStr">
+        <is>
+          <t>Model 50.8% (fair -103). Your call.</t>
+        </is>
+      </c>
+      <c r="O122" s="15" t="n"/>
+      <c r="P122" s="16">
+        <f>IF(OR($H$122="",$O$122=""),"",(1+IF($H$122&lt;0,-100/$H$122,$H$122/100))/(1+IF($O$122&lt;0,-100/$O$122,$O$122/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers -1.5</t>
+        </is>
+      </c>
+      <c r="F123" s="13" t="n">
+        <v>0.4716379310344827</v>
+      </c>
+      <c r="G123" s="14" t="n">
+        <v>112</v>
+      </c>
+      <c r="H123" s="15" t="n">
+        <v>132</v>
+      </c>
+      <c r="I123" s="13">
+        <f>IF($H$123="","",IF($H$123&lt;0,-$H$123/(-$H$123+100),100/($H$123+100)))</f>
+        <v/>
+      </c>
+      <c r="J123" s="16">
+        <f>IF($H$123="","",$F$123*IF($H$123&lt;0,-100/$H$123,$H$123/100)-(1-$F$123))</f>
+        <v/>
+      </c>
+      <c r="K123" s="17">
+        <f>IF($H$123="","",MAX(0,($F$123*IF($H$123&lt;0,-100/$H$123,$H$123/100)-(1-$F$123))/IF($H$123&lt;0,-100/$H$123,$H$123/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L123" s="18">
+        <f>IF($H$123="","",ROUND(MIN($K$123,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M123" s="12">
+        <f>IF($J$123="","",IF($J$123&lt;0,"Pass",IF($J$123&lt;'Settings'!$B$4,"Thin",IF($J$123&lt;0.06,"✅ Sharp band",IF($J$123&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N123" s="19" t="inlineStr">
+        <is>
+          <t>Model 47.2% (fair +112). Your call.</t>
+        </is>
+      </c>
+      <c r="O123" s="15" t="n"/>
+      <c r="P123" s="16">
+        <f>IF(OR($H$123="",$O$123=""),"",(1+IF($H$123&lt;0,-100/$H$123,$H$123/100))/(1+IF($O$123&lt;0,-100/$O$123,$O$123/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B124" s="20" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="C124" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D124" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E124" s="20" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds +1.5</t>
+        </is>
+      </c>
+      <c r="F124" s="13" t="n">
+        <v>0.5283326530612245</v>
+      </c>
+      <c r="G124" s="14" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H124" s="15" t="n">
+        <v>-145</v>
+      </c>
+      <c r="I124" s="13">
+        <f>IF($H$124="","",IF($H$124&lt;0,-$H$124/(-$H$124+100),100/($H$124+100)))</f>
+        <v/>
+      </c>
+      <c r="J124" s="16">
+        <f>IF($H$124="","",$F$124*IF($H$124&lt;0,-100/$H$124,$H$124/100)-(1-$F$124))</f>
+        <v/>
+      </c>
+      <c r="K124" s="17">
+        <f>IF($H$124="","",MAX(0,($F$124*IF($H$124&lt;0,-100/$H$124,$H$124/100)-(1-$F$124))/IF($H$124&lt;0,-100/$H$124,$H$124/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L124" s="18">
+        <f>IF($H$124="","",ROUND(MIN($K$124,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M124" s="12">
+        <f>IF($J$124="","",IF($J$124&lt;0,"Pass",IF($J$124&lt;'Settings'!$B$4,"Thin",IF($J$124&lt;0.06,"✅ Sharp band",IF($J$124&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N124" s="19" t="inlineStr">
+        <is>
+          <t>Model 52.8% (fair -112). Your call.</t>
+        </is>
+      </c>
+      <c r="O124" s="15" t="n"/>
+      <c r="P124" s="16">
+        <f>IF(OR($H$124="",$O$124=""),"",(1+IF($H$124&lt;0,-100/$H$124,$H$124/100))/(1+IF($O$124&lt;0,-100/$O$124,$O$124/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>San Diego Padres @ Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="F125" s="13" t="n">
+        <v>0.413175965665236</v>
+      </c>
+      <c r="G125" s="14" t="n">
+        <v>142</v>
+      </c>
+      <c r="H125" s="15" t="n">
+        <v>133</v>
+      </c>
+      <c r="I125" s="13">
+        <f>IF($H$125="","",IF($H$125&lt;0,-$H$125/(-$H$125+100),100/($H$125+100)))</f>
+        <v/>
+      </c>
+      <c r="J125" s="16">
+        <f>IF($H$125="","",$F$125*IF($H$125&lt;0,-100/$H$125,$H$125/100)-(1-$F$125))</f>
+        <v/>
+      </c>
+      <c r="K125" s="17">
+        <f>IF($H$125="","",MAX(0,($F$125*IF($H$125&lt;0,-100/$H$125,$H$125/100)-(1-$F$125))/IF($H$125&lt;0,-100/$H$125,$H$125/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L125" s="18">
+        <f>IF($H$125="","",ROUND(MIN($K$125,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M125" s="12">
+        <f>IF($J$125="","",IF($J$125&lt;0,"Pass",IF($J$125&lt;'Settings'!$B$4,"Thin",IF($J$125&lt;0.06,"✅ Sharp band",IF($J$125&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N125" s="19" t="inlineStr">
+        <is>
+          <t>Model 41.3% (fair +142). Your call.</t>
+        </is>
+      </c>
+      <c r="O125" s="15" t="n"/>
+      <c r="P125" s="16">
+        <f>IF(OR($H$125="",$O$125=""),"",(1+IF($H$125&lt;0,-100/$H$125,$H$125/100))/(1+IF($O$125&lt;0,-100/$O$125,$O$125/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B126" s="20" t="inlineStr">
+        <is>
+          <t>San Diego Padres @ Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="C126" s="20" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D126" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E126" s="20" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="F126" s="13" t="n">
+        <v>0.5867982832618026</v>
+      </c>
+      <c r="G126" s="14" t="n">
+        <v>-142</v>
+      </c>
+      <c r="H126" s="15" t="n">
+        <v>-133</v>
+      </c>
+      <c r="I126" s="13">
+        <f>IF($H$126="","",IF($H$126&lt;0,-$H$126/(-$H$126+100),100/($H$126+100)))</f>
+        <v/>
+      </c>
+      <c r="J126" s="16">
+        <f>IF($H$126="","",$F$126*IF($H$126&lt;0,-100/$H$126,$H$126/100)-(1-$F$126))</f>
+        <v/>
+      </c>
+      <c r="K126" s="17">
+        <f>IF($H$126="","",MAX(0,($F$126*IF($H$126&lt;0,-100/$H$126,$H$126/100)-(1-$F$126))/IF($H$126&lt;0,-100/$H$126,$H$126/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L126" s="18">
+        <f>IF($H$126="","",ROUND(MIN($K$126,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M126" s="12">
+        <f>IF($J$126="","",IF($J$126&lt;0,"Pass",IF($J$126&lt;'Settings'!$B$4,"Thin",IF($J$126&lt;0.06,"✅ Sharp band",IF($J$126&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N126" s="19" t="inlineStr">
+        <is>
+          <t>Model 58.7% (fair -142). Your call.</t>
+        </is>
+      </c>
+      <c r="O126" s="15" t="n"/>
+      <c r="P126" s="16">
+        <f>IF(OR($H$126="",$O$126=""),"",(1+IF($H$126&lt;0,-100/$H$126,$H$126/100))/(1+IF($O$126&lt;0,-100/$O$126,$O$126/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>San Diego Padres @ Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>Over 11.5</t>
+        </is>
+      </c>
+      <c r="F127" s="13" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="G127" s="14" t="n">
+        <v>213</v>
+      </c>
+      <c r="H127" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I127" s="13">
+        <f>IF($H$127="","",IF($H$127&lt;0,-$H$127/(-$H$127+100),100/($H$127+100)))</f>
+        <v/>
+      </c>
+      <c r="J127" s="16">
+        <f>IF($H$127="","",$F$127*IF($H$127&lt;0,-100/$H$127,$H$127/100)-(1-$F$127))</f>
+        <v/>
+      </c>
+      <c r="K127" s="17">
+        <f>IF($H$127="","",MAX(0,($F$127*IF($H$127&lt;0,-100/$H$127,$H$127/100)-(1-$F$127))/IF($H$127&lt;0,-100/$H$127,$H$127/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L127" s="18">
+        <f>IF($H$127="","",ROUND(MIN($K$127,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M127" s="12">
+        <f>IF($J$127="","",IF($J$127&lt;0,"Pass",IF($J$127&lt;'Settings'!$B$4,"Thin",IF($J$127&lt;0.06,"✅ Sharp band",IF($J$127&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N127" s="19" t="inlineStr">
+        <is>
+          <t>Model 31.9% (fair +213). Your call.</t>
+        </is>
+      </c>
+      <c r="O127" s="15" t="n"/>
+      <c r="P127" s="16">
+        <f>IF(OR($H$127="",$O$127=""),"",(1+IF($H$127&lt;0,-100/$H$127,$H$127/100))/(1+IF($O$127&lt;0,-100/$O$127,$O$127/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B128" s="20" t="inlineStr">
+        <is>
+          <t>San Diego Padres @ Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="C128" s="20" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D128" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E128" s="20" t="inlineStr">
+        <is>
+          <t>Under 11.5</t>
+        </is>
+      </c>
+      <c r="F128" s="13" t="n">
+        <v>0.6805024390243902</v>
+      </c>
+      <c r="G128" s="14" t="n">
+        <v>-213</v>
+      </c>
+      <c r="H128" s="15" t="n">
+        <v>-105</v>
+      </c>
+      <c r="I128" s="13">
+        <f>IF($H$128="","",IF($H$128&lt;0,-$H$128/(-$H$128+100),100/($H$128+100)))</f>
+        <v/>
+      </c>
+      <c r="J128" s="16">
+        <f>IF($H$128="","",$F$128*IF($H$128&lt;0,-100/$H$128,$H$128/100)-(1-$F$128))</f>
+        <v/>
+      </c>
+      <c r="K128" s="17">
+        <f>IF($H$128="","",MAX(0,($F$128*IF($H$128&lt;0,-100/$H$128,$H$128/100)-(1-$F$128))/IF($H$128&lt;0,-100/$H$128,$H$128/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L128" s="18">
+        <f>IF($H$128="","",ROUND(MIN($K$128,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M128" s="12">
+        <f>IF($J$128="","",IF($J$128&lt;0,"Pass",IF($J$128&lt;'Settings'!$B$4,"Thin",IF($J$128&lt;0.06,"✅ Sharp band",IF($J$128&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N128" s="19" t="inlineStr">
+        <is>
+          <t>Model 68.1% (fair -213). Your call.</t>
+        </is>
+      </c>
+      <c r="O128" s="15" t="n"/>
+      <c r="P128" s="16">
+        <f>IF(OR($H$128="",$O$128=""),"",(1+IF($H$128&lt;0,-100/$H$128,$H$128/100))/(1+IF($O$128&lt;0,-100/$O$128,$O$128/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>San Diego Padres @ Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>Chicago Cubs -1.5</t>
+        </is>
+      </c>
+      <c r="F129" s="13" t="n">
+        <v>0.4438222222222222</v>
+      </c>
+      <c r="G129" s="14" t="n">
+        <v>125</v>
+      </c>
+      <c r="H129" s="15" t="n">
+        <v>125</v>
+      </c>
+      <c r="I129" s="13">
+        <f>IF($H$129="","",IF($H$129&lt;0,-$H$129/(-$H$129+100),100/($H$129+100)))</f>
+        <v/>
+      </c>
+      <c r="J129" s="16">
+        <f>IF($H$129="","",$F$129*IF($H$129&lt;0,-100/$H$129,$H$129/100)-(1-$F$129))</f>
+        <v/>
+      </c>
+      <c r="K129" s="17">
+        <f>IF($H$129="","",MAX(0,($F$129*IF($H$129&lt;0,-100/$H$129,$H$129/100)-(1-$F$129))/IF($H$129&lt;0,-100/$H$129,$H$129/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L129" s="18">
+        <f>IF($H$129="","",ROUND(MIN($K$129,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M129" s="12">
+        <f>IF($J$129="","",IF($J$129&lt;0,"Pass",IF($J$129&lt;'Settings'!$B$4,"Thin",IF($J$129&lt;0.06,"✅ Sharp band",IF($J$129&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N129" s="19" t="inlineStr">
+        <is>
+          <t>Model 44.4% (fair +125). Your call.</t>
+        </is>
+      </c>
+      <c r="O129" s="15" t="n"/>
+      <c r="P129" s="16">
+        <f>IF(OR($H$129="",$O$129=""),"",(1+IF($H$129&lt;0,-100/$H$129,$H$129/100))/(1+IF($O$129&lt;0,-100/$O$129,$O$129/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B130" s="20" t="inlineStr">
+        <is>
+          <t>San Diego Padres @ Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="C130" s="20" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D130" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E130" s="20" t="inlineStr">
+        <is>
+          <t>San Diego Padres +1.5</t>
+        </is>
+      </c>
+      <c r="F130" s="13" t="n">
+        <v>0.5562081632653061</v>
+      </c>
+      <c r="G130" s="14" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H130" s="15" t="n">
+        <v>-145</v>
+      </c>
+      <c r="I130" s="13">
+        <f>IF($H$130="","",IF($H$130&lt;0,-$H$130/(-$H$130+100),100/($H$130+100)))</f>
+        <v/>
+      </c>
+      <c r="J130" s="16">
+        <f>IF($H$130="","",$F$130*IF($H$130&lt;0,-100/$H$130,$H$130/100)-(1-$F$130))</f>
+        <v/>
+      </c>
+      <c r="K130" s="17">
+        <f>IF($H$130="","",MAX(0,($F$130*IF($H$130&lt;0,-100/$H$130,$H$130/100)-(1-$F$130))/IF($H$130&lt;0,-100/$H$130,$H$130/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L130" s="18">
+        <f>IF($H$130="","",ROUND(MIN($K$130,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M130" s="12">
+        <f>IF($J$130="","",IF($J$130&lt;0,"Pass",IF($J$130&lt;'Settings'!$B$4,"Thin",IF($J$130&lt;0.06,"✅ Sharp band",IF($J$130&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N130" s="19" t="inlineStr">
+        <is>
+          <t>Model 55.6% (fair -125). Your call.</t>
+        </is>
+      </c>
+      <c r="O130" s="15" t="n"/>
+      <c r="P130" s="16">
+        <f>IF(OR($H$130="",$O$130=""),"",(1+IF($H$130&lt;0,-100/$H$130,$H$130/100))/(1+IF($O$130&lt;0,-100/$O$130,$O$130/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>Minnesota Twins @ Houston Astros</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>00:10</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="F131" s="13" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="G131" s="14" t="n">
+        <v>-182</v>
+      </c>
+      <c r="H131" s="15" t="n"/>
+      <c r="I131" s="13">
+        <f>IF($H$131="","",IF($H$131&lt;0,-$H$131/(-$H$131+100),100/($H$131+100)))</f>
+        <v/>
+      </c>
+      <c r="J131" s="16">
+        <f>IF($H$131="","",$F$131*IF($H$131&lt;0,-100/$H$131,$H$131/100)-(1-$F$131))</f>
+        <v/>
+      </c>
+      <c r="K131" s="17">
+        <f>IF($H$131="","",MAX(0,($F$131*IF($H$131&lt;0,-100/$H$131,$H$131/100)-(1-$F$131))/IF($H$131&lt;0,-100/$H$131,$H$131/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L131" s="18">
+        <f>IF($H$131="","",ROUND(MIN($K$131,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M131" s="12">
+        <f>IF($J$131="","",IF($J$131&lt;0,"Pass",IF($J$131&lt;'Settings'!$B$4,"Thin",IF($J$131&lt;0.06,"✅ Sharp band",IF($J$131&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N131" s="19" t="inlineStr">
+        <is>
+          <t>Model 64.5% (fair -182). Your call.</t>
+        </is>
+      </c>
+      <c r="O131" s="15" t="n"/>
+      <c r="P131" s="16">
+        <f>IF(OR($H$131="",$O$131=""),"",(1+IF($H$131&lt;0,-100/$H$131,$H$131/100))/(1+IF($O$131&lt;0,-100/$O$131,$O$131/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B132" s="20" t="inlineStr">
+        <is>
+          <t>Minnesota Twins @ Houston Astros</t>
+        </is>
+      </c>
+      <c r="C132" s="20" t="inlineStr">
+        <is>
+          <t>00:10</t>
+        </is>
+      </c>
+      <c r="D132" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E132" s="20" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="F132" s="13" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="G132" s="14" t="n">
+        <v>182</v>
+      </c>
+      <c r="H132" s="15" t="n"/>
+      <c r="I132" s="13">
+        <f>IF($H$132="","",IF($H$132&lt;0,-$H$132/(-$H$132+100),100/($H$132+100)))</f>
+        <v/>
+      </c>
+      <c r="J132" s="16">
+        <f>IF($H$132="","",$F$132*IF($H$132&lt;0,-100/$H$132,$H$132/100)-(1-$F$132))</f>
+        <v/>
+      </c>
+      <c r="K132" s="17">
+        <f>IF($H$132="","",MAX(0,($F$132*IF($H$132&lt;0,-100/$H$132,$H$132/100)-(1-$F$132))/IF($H$132&lt;0,-100/$H$132,$H$132/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L132" s="18">
+        <f>IF($H$132="","",ROUND(MIN($K$132,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M132" s="12">
+        <f>IF($J$132="","",IF($J$132&lt;0,"Pass",IF($J$132&lt;'Settings'!$B$4,"Thin",IF($J$132&lt;0.06,"✅ Sharp band",IF($J$132&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N132" s="19" t="inlineStr">
+        <is>
+          <t>Model 35.5% (fair +182). Your call.</t>
+        </is>
+      </c>
+      <c r="O132" s="15" t="n"/>
+      <c r="P132" s="16">
+        <f>IF(OR($H$132="",$O$132=""),"",(1+IF($H$132&lt;0,-100/$H$132,$H$132/100))/(1+IF($O$132&lt;0,-100/$O$132,$O$132/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t>Miami Marlins @ Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>00:40</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="F133" s="13" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="G133" s="14" t="n">
+        <v>126</v>
+      </c>
+      <c r="H133" s="15" t="n"/>
+      <c r="I133" s="13">
+        <f>IF($H$133="","",IF($H$133&lt;0,-$H$133/(-$H$133+100),100/($H$133+100)))</f>
+        <v/>
+      </c>
+      <c r="J133" s="16">
+        <f>IF($H$133="","",$F$133*IF($H$133&lt;0,-100/$H$133,$H$133/100)-(1-$F$133))</f>
+        <v/>
+      </c>
+      <c r="K133" s="17">
+        <f>IF($H$133="","",MAX(0,($F$133*IF($H$133&lt;0,-100/$H$133,$H$133/100)-(1-$F$133))/IF($H$133&lt;0,-100/$H$133,$H$133/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L133" s="18">
+        <f>IF($H$133="","",ROUND(MIN($K$133,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M133" s="12">
+        <f>IF($J$133="","",IF($J$133&lt;0,"Pass",IF($J$133&lt;'Settings'!$B$4,"Thin",IF($J$133&lt;0.06,"✅ Sharp band",IF($J$133&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N133" s="19" t="inlineStr">
+        <is>
+          <t>Model 44.2% (fair +126). Your call.</t>
+        </is>
+      </c>
+      <c r="O133" s="15" t="n"/>
+      <c r="P133" s="16">
+        <f>IF(OR($H$133="",$O$133=""),"",(1+IF($H$133&lt;0,-100/$H$133,$H$133/100))/(1+IF($O$133&lt;0,-100/$O$133,$O$133/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B134" s="20" t="inlineStr">
+        <is>
+          <t>Miami Marlins @ Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="C134" s="20" t="inlineStr">
+        <is>
+          <t>00:40</t>
+        </is>
+      </c>
+      <c r="D134" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E134" s="20" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="F134" s="13" t="n">
+        <v>0.5575</v>
+      </c>
+      <c r="G134" s="14" t="n">
+        <v>-126</v>
+      </c>
+      <c r="H134" s="15" t="n"/>
+      <c r="I134" s="13">
+        <f>IF($H$134="","",IF($H$134&lt;0,-$H$134/(-$H$134+100),100/($H$134+100)))</f>
+        <v/>
+      </c>
+      <c r="J134" s="16">
+        <f>IF($H$134="","",$F$134*IF($H$134&lt;0,-100/$H$134,$H$134/100)-(1-$F$134))</f>
+        <v/>
+      </c>
+      <c r="K134" s="17">
+        <f>IF($H$134="","",MAX(0,($F$134*IF($H$134&lt;0,-100/$H$134,$H$134/100)-(1-$F$134))/IF($H$134&lt;0,-100/$H$134,$H$134/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L134" s="18">
+        <f>IF($H$134="","",ROUND(MIN($K$134,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M134" s="12">
+        <f>IF($J$134="","",IF($J$134&lt;0,"Pass",IF($J$134&lt;'Settings'!$B$4,"Thin",IF($J$134&lt;0.06,"✅ Sharp band",IF($J$134&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N134" s="19" t="inlineStr">
+        <is>
+          <t>Model 55.8% (fair -126). Your call.</t>
+        </is>
+      </c>
+      <c r="O134" s="15" t="n"/>
+      <c r="P134" s="16">
+        <f>IF(OR($H$134="",$O$134=""),"",(1+IF($H$134&lt;0,-100/$H$134,$H$134/100))/(1+IF($O$134&lt;0,-100/$O$134,$O$134/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers @ Athletics</t>
+        </is>
+      </c>
+      <c r="C135" s="12" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D135" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="F135" s="13" t="n">
+        <v>0.6152</v>
+      </c>
+      <c r="G135" s="14" t="n">
+        <v>-160</v>
+      </c>
+      <c r="H135" s="15" t="n"/>
+      <c r="I135" s="13">
+        <f>IF($H$135="","",IF($H$135&lt;0,-$H$135/(-$H$135+100),100/($H$135+100)))</f>
+        <v/>
+      </c>
+      <c r="J135" s="16">
+        <f>IF($H$135="","",$F$135*IF($H$135&lt;0,-100/$H$135,$H$135/100)-(1-$F$135))</f>
+        <v/>
+      </c>
+      <c r="K135" s="17">
+        <f>IF($H$135="","",MAX(0,($F$135*IF($H$135&lt;0,-100/$H$135,$H$135/100)-(1-$F$135))/IF($H$135&lt;0,-100/$H$135,$H$135/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L135" s="18">
+        <f>IF($H$135="","",ROUND(MIN($K$135,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M135" s="12">
+        <f>IF($J$135="","",IF($J$135&lt;0,"Pass",IF($J$135&lt;'Settings'!$B$4,"Thin",IF($J$135&lt;0.06,"✅ Sharp band",IF($J$135&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N135" s="19" t="inlineStr">
+        <is>
+          <t>Model 61.5% (fair -160). Your call.</t>
+        </is>
+      </c>
+      <c r="O135" s="15" t="n"/>
+      <c r="P135" s="16">
+        <f>IF(OR($H$135="",$O$135=""),"",(1+IF($H$135&lt;0,-100/$H$135,$H$135/100))/(1+IF($O$135&lt;0,-100/$O$135,$O$135/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B136" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers @ Athletics</t>
+        </is>
+      </c>
+      <c r="C136" s="20" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D136" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E136" s="20" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="F136" s="13" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="G136" s="14" t="n">
+        <v>160</v>
+      </c>
+      <c r="H136" s="15" t="n"/>
+      <c r="I136" s="13">
+        <f>IF($H$136="","",IF($H$136&lt;0,-$H$136/(-$H$136+100),100/($H$136+100)))</f>
+        <v/>
+      </c>
+      <c r="J136" s="16">
+        <f>IF($H$136="","",$F$136*IF($H$136&lt;0,-100/$H$136,$H$136/100)-(1-$F$136))</f>
+        <v/>
+      </c>
+      <c r="K136" s="17">
+        <f>IF($H$136="","",MAX(0,($F$136*IF($H$136&lt;0,-100/$H$136,$H$136/100)-(1-$F$136))/IF($H$136&lt;0,-100/$H$136,$H$136/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L136" s="18">
+        <f>IF($H$136="","",ROUND(MIN($K$136,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M136" s="12">
+        <f>IF($J$136="","",IF($J$136&lt;0,"Pass",IF($J$136&lt;'Settings'!$B$4,"Thin",IF($J$136&lt;0.06,"✅ Sharp band",IF($J$136&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N136" s="19" t="inlineStr">
+        <is>
+          <t>Model 38.5% (fair +160). Your call.</t>
+        </is>
+      </c>
+      <c r="O136" s="15" t="n"/>
+      <c r="P136" s="16">
+        <f>IF(OR($H$136="",$O$136=""),"",(1+IF($H$136&lt;0,-100/$H$136,$H$136/100))/(1+IF($O$136&lt;0,-100/$O$136,$O$136/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="F137" s="13" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="G137" s="14" t="n">
+        <v>118</v>
+      </c>
+      <c r="H137" s="15" t="n"/>
+      <c r="I137" s="13">
+        <f>IF($H$137="","",IF($H$137&lt;0,-$H$137/(-$H$137+100),100/($H$137+100)))</f>
+        <v/>
+      </c>
+      <c r="J137" s="16">
+        <f>IF($H$137="","",$F$137*IF($H$137&lt;0,-100/$H$137,$H$137/100)-(1-$F$137))</f>
+        <v/>
+      </c>
+      <c r="K137" s="17">
+        <f>IF($H$137="","",MAX(0,($F$137*IF($H$137&lt;0,-100/$H$137,$H$137/100)-(1-$F$137))/IF($H$137&lt;0,-100/$H$137,$H$137/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L137" s="18">
+        <f>IF($H$137="","",ROUND(MIN($K$137,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M137" s="12">
+        <f>IF($J$137="","",IF($J$137&lt;0,"Pass",IF($J$137&lt;'Settings'!$B$4,"Thin",IF($J$137&lt;0.06,"✅ Sharp band",IF($J$137&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N137" s="19" t="inlineStr">
+        <is>
+          <t>Model 45.9% (fair +118). Your call.</t>
+        </is>
+      </c>
+      <c r="O137" s="15" t="n"/>
+      <c r="P137" s="16">
+        <f>IF(OR($H$137="",$O$137=""),"",(1+IF($H$137&lt;0,-100/$H$137,$H$137/100))/(1+IF($O$137&lt;0,-100/$O$137,$O$137/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B138" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="C138" s="20" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D138" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E138" s="20" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="F138" s="13" t="n">
+        <v>0.5413</v>
+      </c>
+      <c r="G138" s="14" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H138" s="15" t="n"/>
+      <c r="I138" s="13">
+        <f>IF($H$138="","",IF($H$138&lt;0,-$H$138/(-$H$138+100),100/($H$138+100)))</f>
+        <v/>
+      </c>
+      <c r="J138" s="16">
+        <f>IF($H$138="","",$F$138*IF($H$138&lt;0,-100/$H$138,$H$138/100)-(1-$F$138))</f>
+        <v/>
+      </c>
+      <c r="K138" s="17">
+        <f>IF($H$138="","",MAX(0,($F$138*IF($H$138&lt;0,-100/$H$138,$H$138/100)-(1-$F$138))/IF($H$138&lt;0,-100/$H$138,$H$138/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L138" s="18">
+        <f>IF($H$138="","",ROUND(MIN($K$138,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M138" s="12">
+        <f>IF($J$138="","",IF($J$138&lt;0,"Pass",IF($J$138&lt;'Settings'!$B$4,"Thin",IF($J$138&lt;0.06,"✅ Sharp band",IF($J$138&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N138" s="19" t="inlineStr">
+        <is>
+          <t>Model 54.1% (fair -118). Your call.</t>
+        </is>
+      </c>
+      <c r="O138" s="15" t="n"/>
+      <c r="P138" s="16">
+        <f>IF(OR($H$138="",$O$138=""),"",(1+IF($H$138&lt;0,-100/$H$138,$H$138/100))/(1+IF($O$138&lt;0,-100/$O$138,$O$138/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="inlineStr">
+        <is>
+          <t>San Francisco Giants @ Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D139" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="F139" s="13" t="n">
+        <v>0.6268</v>
+      </c>
+      <c r="G139" s="14" t="n">
+        <v>-168</v>
+      </c>
+      <c r="H139" s="15" t="n"/>
+      <c r="I139" s="13">
+        <f>IF($H$139="","",IF($H$139&lt;0,-$H$139/(-$H$139+100),100/($H$139+100)))</f>
+        <v/>
+      </c>
+      <c r="J139" s="16">
+        <f>IF($H$139="","",$F$139*IF($H$139&lt;0,-100/$H$139,$H$139/100)-(1-$F$139))</f>
+        <v/>
+      </c>
+      <c r="K139" s="17">
+        <f>IF($H$139="","",MAX(0,($F$139*IF($H$139&lt;0,-100/$H$139,$H$139/100)-(1-$F$139))/IF($H$139&lt;0,-100/$H$139,$H$139/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L139" s="18">
+        <f>IF($H$139="","",ROUND(MIN($K$139,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M139" s="12">
+        <f>IF($J$139="","",IF($J$139&lt;0,"Pass",IF($J$139&lt;'Settings'!$B$4,"Thin",IF($J$139&lt;0.06,"✅ Sharp band",IF($J$139&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N139" s="19" t="inlineStr">
+        <is>
+          <t>Model 62.7% (fair -168). Your call.</t>
+        </is>
+      </c>
+      <c r="O139" s="15" t="n"/>
+      <c r="P139" s="16">
+        <f>IF(OR($H$139="",$O$139=""),"",(1+IF($H$139&lt;0,-100/$H$139,$H$139/100))/(1+IF($O$139&lt;0,-100/$O$139,$O$139/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B140" s="20" t="inlineStr">
+        <is>
+          <t>San Francisco Giants @ Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="C140" s="20" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D140" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E140" s="20" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="F140" s="13" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="G140" s="14" t="n">
+        <v>168</v>
+      </c>
+      <c r="H140" s="15" t="n"/>
+      <c r="I140" s="13">
+        <f>IF($H$140="","",IF($H$140&lt;0,-$H$140/(-$H$140+100),100/($H$140+100)))</f>
+        <v/>
+      </c>
+      <c r="J140" s="16">
+        <f>IF($H$140="","",$F$140*IF($H$140&lt;0,-100/$H$140,$H$140/100)-(1-$F$140))</f>
+        <v/>
+      </c>
+      <c r="K140" s="17">
+        <f>IF($H$140="","",MAX(0,($F$140*IF($H$140&lt;0,-100/$H$140,$H$140/100)-(1-$F$140))/IF($H$140&lt;0,-100/$H$140,$H$140/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L140" s="18">
+        <f>IF($H$140="","",ROUND(MIN($K$140,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M140" s="12">
+        <f>IF($J$140="","",IF($J$140&lt;0,"Pass",IF($J$140&lt;'Settings'!$B$4,"Thin",IF($J$140&lt;0.06,"✅ Sharp band",IF($J$140&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N140" s="19" t="inlineStr">
+        <is>
+          <t>Model 37.3% (fair +168). Your call.</t>
+        </is>
+      </c>
+      <c r="O140" s="15" t="n"/>
+      <c r="P140" s="16">
+        <f>IF(OR($H$140="",$O$140=""),"",(1+IF($H$140&lt;0,-100/$H$140,$H$140/100))/(1+IF($O$140&lt;0,-100/$O$140,$O$140/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J100">
+  <conditionalFormatting sqref="J5:J140">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -15847,10 +19015,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4423</v>
+        <v>0.5591</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>126</v>
+        <v>-127</v>
       </c>
       <c r="H5" s="15" t="n"/>
       <c r="I5" s="13">
@@ -15875,7 +19043,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -15911,10 +19079,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5577</v>
+        <v>0.4409</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-126</v>
+        <v>127</v>
       </c>
       <c r="H6" s="15" t="n"/>
       <c r="I6" s="13">
@@ -15939,7 +19107,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>

--- a/data/output/workbook/2026-06-29.xlsx
+++ b/data/output/workbook/2026-06-29.xlsx
@@ -490,7 +490,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10086975"/>
+    <ext cx="10125075" cy="9648825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -520,7 +520,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9467850"/>
+    <ext cx="10125075" cy="9086850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -550,7 +550,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9610725"/>
+    <ext cx="10125075" cy="10048875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29 15:07</t>
+          <t>2026-06-29 17:27</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q78"/>
+  <dimension ref="A1:Q76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2850,183 +2850,317 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="28" t="inlineStr">
+        <is>
+          <t>Washington Nationals offense vs Boston Red Sox defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B63" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C63" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D63" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E63" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F63" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G63" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H63" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I63" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J63" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K63" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L63" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M63" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N63" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O63" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P63" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q63" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="64">
-      <c r="A64" s="28" t="inlineStr">
-        <is>
-          <t>Washington Nationals offense vs Boston Red Sox defense</t>
+      <c r="A64" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B64" s="31" t="n">
+        <v>5.317</v>
+      </c>
+      <c r="C64" s="31" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="D64" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E64" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F64" s="31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G64" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H64" s="32" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I64" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J64" s="35" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="K64" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L64" s="31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M64" s="31" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="N64" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O64" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P64" s="31" t="n">
+        <v>4.324</v>
+      </c>
+      <c r="Q64" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B65" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C65" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D65" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E65" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F65" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G65" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H65" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I65" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J65" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K65" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L65" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M65" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N65" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O65" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P65" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q65" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A65" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B65" s="31" t="n">
+        <v>8.462</v>
+      </c>
+      <c r="C65" s="31" t="n">
+        <v>7.893</v>
+      </c>
+      <c r="D65" s="31" t="n">
+        <v>7.611</v>
+      </c>
+      <c r="E65" s="31" t="n">
+        <v>7.571</v>
+      </c>
+      <c r="F65" s="31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G65" s="31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H65" s="35" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="I65" s="31" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J65" s="33" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K65" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="L65" s="31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M65" s="31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="N65" s="31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O65" s="31" t="n">
+        <v>8.345000000000001</v>
+      </c>
+      <c r="P65" s="31" t="n">
+        <v>8.305999999999999</v>
+      </c>
+      <c r="Q65" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B66" s="31" t="n">
-        <v>5.317</v>
+        <v>1.256</v>
       </c>
       <c r="C66" s="31" t="n">
-        <v>4.933</v>
+        <v>1.179</v>
       </c>
       <c r="D66" s="31" t="n">
-        <v>5</v>
+        <v>1.444</v>
       </c>
       <c r="E66" s="31" t="n">
-        <v>4.8</v>
+        <v>1.357</v>
       </c>
       <c r="F66" s="31" t="n">
-        <v>5.7</v>
+        <v>1.5</v>
       </c>
       <c r="G66" s="31" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="H66" s="32" t="inlineStr">
         <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I66" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J66" s="35" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="K66" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L66" s="31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="M66" s="31" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="N66" s="31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O66" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P66" s="31" t="n">
-        <v>4.324</v>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I66" s="31" t="inlineStr"/>
+      <c r="J66" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K66" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L66" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M66" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N66" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O66" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P66" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q66" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B67" s="31" t="n">
-        <v>8.462</v>
+        <v>8.026</v>
       </c>
       <c r="C67" s="31" t="n">
-        <v>7.893</v>
+        <v>7.714</v>
       </c>
       <c r="D67" s="31" t="n">
-        <v>7.611</v>
+        <v>8.055999999999999</v>
       </c>
       <c r="E67" s="31" t="n">
         <v>7.571</v>
       </c>
       <c r="F67" s="31" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="G67" s="31" t="n">
         <v>8.199999999999999</v>
@@ -3038,639 +3172,505 @@
       </c>
       <c r="I67" s="31" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J67" s="33" t="inlineStr">
-        <is>
-          <t>22nd</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J67" s="35" t="inlineStr">
+        <is>
+          <t>17th</t>
         </is>
       </c>
       <c r="K67" s="31" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L67" s="31" t="n">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M67" s="31" t="n">
-        <v>8.800000000000001</v>
+        <v>8.667</v>
       </c>
       <c r="N67" s="31" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O67" s="31" t="n">
-        <v>8.345000000000001</v>
+        <v>8.034000000000001</v>
       </c>
       <c r="P67" s="31" t="n">
-        <v>8.305999999999999</v>
+        <v>8.138999999999999</v>
       </c>
       <c r="Q67" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B68" s="31" t="n">
-        <v>1.256</v>
+        <v>1</v>
       </c>
       <c r="C68" s="31" t="n">
-        <v>1.179</v>
+        <v>0.929</v>
       </c>
       <c r="D68" s="31" t="n">
-        <v>1.444</v>
+        <v>1.056</v>
       </c>
       <c r="E68" s="31" t="n">
-        <v>1.357</v>
+        <v>0.714</v>
       </c>
       <c r="F68" s="31" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="G68" s="31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H68" s="32" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I68" s="31" t="inlineStr"/>
-      <c r="J68" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P68" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.6</v>
+      </c>
+      <c r="H68" s="35" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I68" s="31" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J68" s="33" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K68" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M68" s="31" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="N68" s="31" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O68" s="31" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="P68" s="31" t="n">
+        <v>0.75</v>
       </c>
       <c r="Q68" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B69" s="31" t="n">
-        <v>8.026</v>
-      </c>
-      <c r="C69" s="31" t="n">
-        <v>7.714</v>
-      </c>
-      <c r="D69" s="31" t="n">
-        <v>8.055999999999999</v>
-      </c>
-      <c r="E69" s="31" t="n">
-        <v>7.571</v>
-      </c>
-      <c r="F69" s="31" t="n">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="28" t="inlineStr">
+        <is>
+          <t>Boston Red Sox offense vs Washington Nationals defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B71" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C71" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D71" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E71" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F71" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G71" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H71" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I71" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J71" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K71" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L71" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M71" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N71" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O71" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P71" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q71" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B72" s="31" t="n">
+        <v>4.027</v>
+      </c>
+      <c r="C72" s="31" t="n">
+        <v>4.233</v>
+      </c>
+      <c r="D72" s="31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E72" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F72" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G72" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="I72" s="31" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K72" s="31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L72" s="31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M72" s="31" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="N72" s="31" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="O72" s="31" t="n">
+        <v>5.033</v>
+      </c>
+      <c r="P72" s="31" t="n">
+        <v>5.439</v>
+      </c>
+      <c r="Q72" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B73" s="31" t="n">
+        <v>7.833</v>
+      </c>
+      <c r="C73" s="31" t="n">
+        <v>7.966</v>
+      </c>
+      <c r="D73" s="31" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="E73" s="31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F73" s="31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G73" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="H73" s="32" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J73" s="32" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="G69" s="31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="I69" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K69" s="31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L69" s="31" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="M69" s="31" t="n">
-        <v>8.667</v>
-      </c>
-      <c r="N69" s="31" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="O69" s="31" t="n">
-        <v>8.034000000000001</v>
-      </c>
-      <c r="P69" s="31" t="n">
-        <v>8.138999999999999</v>
-      </c>
-      <c r="Q69" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>0.929</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>1.056</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J70" s="33" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="O70" s="31" t="n">
-        <v>0.724</v>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="28" t="inlineStr">
-        <is>
-          <t>Boston Red Sox offense vs Washington Nationals defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B73" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C73" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D73" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E73" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F73" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G73" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H73" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I73" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J73" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K73" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L73" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M73" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N73" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O73" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P73" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q73" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="L73" s="31" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M73" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="N73" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="O73" s="31" t="n">
+        <v>8.643000000000001</v>
+      </c>
+      <c r="P73" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q73" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B74" s="31" t="n">
-        <v>4.027</v>
+        <v>0.694</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>4.233</v>
+        <v>0.586</v>
       </c>
       <c r="D74" s="31" t="n">
-        <v>3.95</v>
+        <v>0.7</v>
       </c>
       <c r="E74" s="31" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="F74" s="31" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="G74" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>13th</t>
+        <v>0.6</v>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>22nd</t>
         </is>
       </c>
       <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L74" s="31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M74" s="31" t="n">
-        <v>3.933</v>
-      </c>
-      <c r="N74" s="31" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="O74" s="31" t="n">
-        <v>5.033</v>
-      </c>
-      <c r="P74" s="31" t="n">
-        <v>5.439</v>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B75" s="31" t="n">
-        <v>7.833</v>
+        <v>8.305999999999999</v>
       </c>
       <c r="C75" s="31" t="n">
-        <v>7.966</v>
+        <v>7.724</v>
       </c>
       <c r="D75" s="31" t="n">
-        <v>7.85</v>
+        <v>7.9</v>
       </c>
       <c r="E75" s="31" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="F75" s="31" t="n">
-        <v>8.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="G75" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="H75" s="32" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+        <v>8.4</v>
+      </c>
+      <c r="H75" s="35" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="I75" s="31" t="inlineStr"/>
       <c r="J75" s="32" t="inlineStr">
         <is>
-          <t>9th</t>
+          <t>8th</t>
         </is>
       </c>
       <c r="K75" s="31" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="L75" s="31" t="n">
-        <v>7.9</v>
+        <v>9.4</v>
       </c>
       <c r="M75" s="31" t="n">
-        <v>8</v>
+        <v>9.929</v>
       </c>
       <c r="N75" s="31" t="n">
-        <v>8</v>
+        <v>8.944000000000001</v>
       </c>
       <c r="O75" s="31" t="n">
         <v>8.643000000000001</v>
       </c>
       <c r="P75" s="31" t="n">
-        <v>9</v>
+        <v>8.333</v>
       </c>
       <c r="Q75" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B76" s="31" t="n">
-        <v>0.694</v>
+        <v>0.278</v>
       </c>
       <c r="C76" s="31" t="n">
-        <v>0.586</v>
+        <v>0.31</v>
       </c>
       <c r="D76" s="31" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="E76" s="31" t="n">
-        <v>0.8</v>
+        <v>0.333</v>
       </c>
       <c r="F76" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G76" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G76" s="31" t="n">
+      <c r="H76" s="32" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I76" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J76" s="35" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="K76" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="H76" s="33" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="I76" s="31" t="inlineStr"/>
-      <c r="J76" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P76" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="L76" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M76" s="31" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="N76" s="31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O76" s="31" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="P76" s="31" t="n">
+        <v>0.436</v>
       </c>
       <c r="Q76" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B77" s="31" t="n">
-        <v>8.305999999999999</v>
-      </c>
-      <c r="C77" s="31" t="n">
-        <v>7.724</v>
-      </c>
-      <c r="D77" s="31" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="E77" s="31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="F77" s="31" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="G77" s="31" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I77" s="31" t="inlineStr"/>
-      <c r="J77" s="32" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="K77" s="31" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="L77" s="31" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="M77" s="31" t="n">
-        <v>9.929</v>
-      </c>
-      <c r="N77" s="31" t="n">
-        <v>8.944000000000001</v>
-      </c>
-      <c r="O77" s="31" t="n">
-        <v>8.643000000000001</v>
-      </c>
-      <c r="P77" s="31" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="Q77" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B78" s="31" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="C78" s="31" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="D78" s="31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E78" s="31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F78" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G78" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78" s="32" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I78" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L78" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M78" s="31" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="N78" s="31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O78" s="31" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="P78" s="31" t="n">
-        <v>0.436</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -3689,7 +3689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3706,811 +3706,811 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="28" t="inlineStr">
+        <is>
+          <t>Texas Rangers offense vs Cleveland Guardians defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B60" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C60" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D60" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E60" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F60" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G60" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H60" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I60" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J60" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K60" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L60" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M60" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N60" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O60" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P60" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q60" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="61">
-      <c r="A61" s="28" t="inlineStr">
-        <is>
-          <t>Texas Rangers offense vs Cleveland Guardians defense</t>
+      <c r="A61" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B61" s="31" t="n">
+        <v>3.909</v>
+      </c>
+      <c r="C61" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D61" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E61" s="31" t="n">
+        <v>3.467</v>
+      </c>
+      <c r="F61" s="31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G61" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H61" s="35" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="I61" s="31" t="inlineStr"/>
+      <c r="J61" s="32" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K61" s="31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L61" s="31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M61" s="31" t="n">
+        <v>3.533</v>
+      </c>
+      <c r="N61" s="31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O61" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P61" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q61" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B62" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C62" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D62" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E62" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F62" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G62" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H62" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I62" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J62" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K62" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L62" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M62" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N62" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O62" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P62" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q62" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A62" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B62" s="31" t="n">
+        <v>7.919</v>
+      </c>
+      <c r="C62" s="31" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="D62" s="31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E62" s="31" t="n">
+        <v>7.692</v>
+      </c>
+      <c r="F62" s="31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G62" s="31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H62" s="32" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I62" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J62" s="32" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="K62" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="L62" s="31" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="M62" s="31" t="n">
+        <v>7.533</v>
+      </c>
+      <c r="N62" s="31" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="O62" s="31" t="n">
+        <v>7.833</v>
+      </c>
+      <c r="P62" s="31" t="n">
+        <v>7.538</v>
+      </c>
+      <c r="Q62" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B63" s="31" t="n">
-        <v>3.909</v>
+        <v>1</v>
       </c>
       <c r="C63" s="31" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="D63" s="31" t="n">
-        <v>3.6</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E63" s="31" t="n">
-        <v>3.467</v>
+        <v>0.923</v>
       </c>
       <c r="F63" s="31" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="G63" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H63" s="35" t="inlineStr">
-        <is>
-          <t>11th</t>
+        <v>1.2</v>
+      </c>
+      <c r="H63" s="32" t="inlineStr">
+        <is>
+          <t>10th</t>
         </is>
       </c>
       <c r="I63" s="31" t="inlineStr"/>
-      <c r="J63" s="32" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K63" s="31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L63" s="31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M63" s="31" t="n">
-        <v>3.533</v>
-      </c>
-      <c r="N63" s="31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O63" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P63" s="31" t="n">
-        <v>4</v>
+      <c r="J63" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K63" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L63" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M63" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N63" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O63" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P63" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q63" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B64" s="31" t="n">
-        <v>7.919</v>
+        <v>8.595000000000001</v>
       </c>
       <c r="C64" s="31" t="n">
-        <v>7.96</v>
+        <v>8.44</v>
       </c>
       <c r="D64" s="31" t="n">
         <v>7.5</v>
       </c>
       <c r="E64" s="31" t="n">
-        <v>7.692</v>
+        <v>6.846</v>
       </c>
       <c r="F64" s="31" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="G64" s="31" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="H64" s="32" t="inlineStr">
         <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I64" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I64" s="31" t="inlineStr"/>
       <c r="J64" s="32" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="K64" s="31" t="n">
-        <v>6</v>
+        <v>11.2</v>
       </c>
       <c r="L64" s="31" t="n">
-        <v>7.3</v>
+        <v>10.3</v>
       </c>
       <c r="M64" s="31" t="n">
-        <v>7.533</v>
+        <v>9.132999999999999</v>
       </c>
       <c r="N64" s="31" t="n">
-        <v>7.3</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O64" s="31" t="n">
-        <v>7.833</v>
+        <v>9.233000000000001</v>
       </c>
       <c r="P64" s="31" t="n">
-        <v>7.538</v>
+        <v>9.487</v>
       </c>
       <c r="Q64" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B65" s="31" t="n">
-        <v>1</v>
+        <v>0.297</v>
       </c>
       <c r="C65" s="31" t="n">
-        <v>1.04</v>
+        <v>0.32</v>
       </c>
       <c r="D65" s="31" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.125</v>
       </c>
       <c r="E65" s="31" t="n">
-        <v>0.923</v>
+        <v>0.154</v>
       </c>
       <c r="F65" s="31" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="G65" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H65" s="32" t="inlineStr">
-        <is>
-          <t>10th</t>
+        <v>0.4</v>
+      </c>
+      <c r="H65" s="35" t="inlineStr">
+        <is>
+          <t>19th</t>
         </is>
       </c>
       <c r="I65" s="31" t="inlineStr"/>
-      <c r="J65" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K65" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L65" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M65" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N65" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O65" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P65" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J65" s="32" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K65" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M65" s="31" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N65" s="31" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O65" s="31" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="P65" s="31" t="n">
+        <v>0.308</v>
       </c>
       <c r="Q65" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B66" s="31" t="n">
-        <v>8.595000000000001</v>
-      </c>
-      <c r="C66" s="31" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="D66" s="31" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E66" s="31" t="n">
-        <v>6.846</v>
-      </c>
-      <c r="F66" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="G66" s="31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H66" s="32" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I66" s="31" t="inlineStr"/>
-      <c r="J66" s="32" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K66" s="31" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="L66" s="31" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="M66" s="31" t="n">
-        <v>9.132999999999999</v>
-      </c>
-      <c r="N66" s="31" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="O66" s="31" t="n">
-        <v>9.233000000000001</v>
-      </c>
-      <c r="P66" s="31" t="n">
-        <v>9.487</v>
-      </c>
-      <c r="Q66" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B67" s="31" t="n">
-        <v>0.297</v>
-      </c>
-      <c r="C67" s="31" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="D67" s="31" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E67" s="31" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="F67" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G67" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H67" s="35" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I67" s="31" t="inlineStr"/>
-      <c r="J67" s="32" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K67" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="31" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M67" s="31" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N67" s="31" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O67" s="31" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="P67" s="31" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="Q67" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians offense vs Texas Rangers defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="28" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians offense vs Texas Rangers defense</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C69" s="31" t="n">
+        <v>4.367</v>
+      </c>
+      <c r="D69" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E69" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" s="31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G69" s="31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="I69" s="31" t="inlineStr"/>
+      <c r="J69" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="L69" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M69" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N69" s="31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O69" s="31" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="P69" s="31" t="n">
+        <v>3.773</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="n">
+        <v>7.308</v>
+      </c>
+      <c r="C70" s="31" t="n">
+        <v>7.733</v>
+      </c>
+      <c r="D70" s="31" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="E70" s="31" t="n">
+        <v>7.267</v>
+      </c>
+      <c r="F70" s="31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G70" s="31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L70" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="M70" s="31" t="n">
+        <v>7.769</v>
+      </c>
+      <c r="N70" s="31" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="O70" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="P70" s="31" t="n">
+        <v>7.703</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>4</v>
+        <v>0.949</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>4.367</v>
+        <v>0.967</v>
       </c>
       <c r="D71" s="31" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="E71" s="31" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="F71" s="31" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="G71" s="31" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="H71" s="33" t="inlineStr">
         <is>
-          <t>27th</t>
+          <t>26th</t>
         </is>
       </c>
       <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="L71" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M71" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N71" s="31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O71" s="31" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="P71" s="31" t="n">
-        <v>3.773</v>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>7.308</v>
+        <v>7.821</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>7.733</v>
+        <v>7.5</v>
       </c>
       <c r="D72" s="31" t="n">
-        <v>7.15</v>
+        <v>8.1</v>
       </c>
       <c r="E72" s="31" t="n">
-        <v>7.267</v>
+        <v>7.933</v>
       </c>
       <c r="F72" s="31" t="n">
-        <v>6.6</v>
+        <v>7.7</v>
       </c>
       <c r="G72" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H72" s="33" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I72" s="31" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>13th</t>
+        <v>7.8</v>
+      </c>
+      <c r="H72" s="32" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I72" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J72" s="33" t="inlineStr">
+        <is>
+          <t>23rd</t>
         </is>
       </c>
       <c r="K72" s="31" t="n">
         <v>7.4</v>
       </c>
       <c r="L72" s="31" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="M72" s="31" t="n">
-        <v>7.769</v>
+        <v>7.385</v>
       </c>
       <c r="N72" s="31" t="n">
-        <v>7.75</v>
+        <v>7.562</v>
       </c>
       <c r="O72" s="31" t="n">
-        <v>8</v>
+        <v>7.84</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>7.703</v>
+        <v>8.513999999999999</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>0.949</v>
+        <v>0.641</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>0.967</v>
+        <v>0.767</v>
       </c>
       <c r="D73" s="31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E73" s="31" t="n">
-        <v>0.8</v>
+        <v>0.867</v>
       </c>
       <c r="F73" s="31" t="n">
         <v>0.7</v>
       </c>
       <c r="G73" s="31" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="H73" s="33" t="inlineStr">
         <is>
-          <t>26th</t>
+          <t>30th</t>
         </is>
       </c>
       <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L73" s="31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M73" s="31" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="N73" s="31" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="O73" s="31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="P73" s="31" t="n">
+        <v>0.892</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="31" t="n">
-        <v>7.821</v>
-      </c>
-      <c r="C74" s="31" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="D74" s="31" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="E74" s="31" t="n">
-        <v>7.933</v>
-      </c>
-      <c r="F74" s="31" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="G74" s="31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H74" s="32" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J74" s="33" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L74" s="31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="M74" s="31" t="n">
-        <v>7.385</v>
-      </c>
-      <c r="N74" s="31" t="n">
-        <v>7.562</v>
-      </c>
-      <c r="O74" s="31" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="P74" s="31" t="n">
-        <v>8.513999999999999</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="31" t="n">
-        <v>0.641</v>
-      </c>
-      <c r="C75" s="31" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="D75" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E75" s="31" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="F75" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G75" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr"/>
-      <c r="J75" s="33" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L75" s="31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M75" s="31" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="N75" s="31" t="n">
-        <v>1.188</v>
-      </c>
-      <c r="O75" s="31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="P75" s="31" t="n">
-        <v>0.892</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -4529,7 +4529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:Q78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4546,823 +4546,823 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="28" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="28" t="inlineStr">
         <is>
           <t>Cincinnati Reds offense vs Milwaukee Brewers defense</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="29" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B63" s="29" t="inlineStr">
+      <c r="B65" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C63" s="29" t="inlineStr">
+      <c r="C65" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D63" s="29" t="inlineStr">
+      <c r="D65" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E63" s="29" t="inlineStr">
+      <c r="E65" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F63" s="29" t="inlineStr">
+      <c r="F65" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G63" s="29" t="inlineStr">
+      <c r="G65" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H63" s="29" t="inlineStr">
+      <c r="H65" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I63" s="29" t="inlineStr">
+      <c r="I65" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J63" s="29" t="inlineStr">
+      <c r="J65" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K63" s="29" t="inlineStr">
+      <c r="K65" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L63" s="29" t="inlineStr">
+      <c r="L65" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M63" s="29" t="inlineStr">
+      <c r="M65" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N63" s="29" t="inlineStr">
+      <c r="N65" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O63" s="29" t="inlineStr">
+      <c r="O65" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P63" s="29" t="inlineStr">
+      <c r="P65" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q63" s="29" t="inlineStr">
+      <c r="Q65" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B64" s="31" t="n">
-        <v>4.132</v>
-      </c>
-      <c r="C64" s="31" t="n">
-        <v>4.433</v>
-      </c>
-      <c r="D64" s="31" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="E64" s="31" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="F64" s="31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="G64" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="H64" s="32" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I64" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J64" s="35" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K64" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="L64" s="31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M64" s="31" t="n">
-        <v>3.267</v>
-      </c>
-      <c r="N64" s="31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O64" s="31" t="n">
-        <v>4.033</v>
-      </c>
-      <c r="P64" s="31" t="n">
-        <v>3.784</v>
-      </c>
-      <c r="Q64" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B65" s="31" t="n">
-        <v>7.216</v>
-      </c>
-      <c r="C65" s="31" t="n">
-        <v>7.345</v>
-      </c>
-      <c r="D65" s="31" t="n">
-        <v>7.632</v>
-      </c>
-      <c r="E65" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="F65" s="31" t="n">
-        <v>7.667</v>
-      </c>
-      <c r="G65" s="31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H65" s="35" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I65" s="31" t="inlineStr"/>
-      <c r="J65" s="32" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="K65" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L65" s="31" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="M65" s="31" t="n">
-        <v>6.308</v>
-      </c>
-      <c r="N65" s="31" t="n">
-        <v>6.722</v>
-      </c>
-      <c r="O65" s="31" t="n">
-        <v>7.536</v>
-      </c>
-      <c r="P65" s="31" t="n">
-        <v>7.371</v>
-      </c>
-      <c r="Q65" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B66" s="31" t="n">
-        <v>1.216</v>
+        <v>4.132</v>
       </c>
       <c r="C66" s="31" t="n">
-        <v>1.241</v>
+        <v>4.433</v>
       </c>
       <c r="D66" s="31" t="n">
-        <v>1.263</v>
+        <v>4.65</v>
       </c>
       <c r="E66" s="31" t="n">
-        <v>1.643</v>
+        <v>4.867</v>
       </c>
       <c r="F66" s="31" t="n">
-        <v>0.889</v>
+        <v>3.9</v>
       </c>
       <c r="G66" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H66" s="35" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="I66" s="31" t="inlineStr"/>
-      <c r="J66" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K66" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L66" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M66" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N66" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O66" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P66" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="H66" s="32" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I66" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J66" s="35" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K66" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L66" s="31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M66" s="31" t="n">
+        <v>3.267</v>
+      </c>
+      <c r="N66" s="31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O66" s="31" t="n">
+        <v>4.033</v>
+      </c>
+      <c r="P66" s="31" t="n">
+        <v>3.784</v>
       </c>
       <c r="Q66" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B67" s="31" t="n">
-        <v>9.27</v>
+        <v>7.216</v>
       </c>
       <c r="C67" s="31" t="n">
-        <v>9.103</v>
+        <v>7.345</v>
       </c>
       <c r="D67" s="31" t="n">
-        <v>9.420999999999999</v>
+        <v>7.632</v>
       </c>
       <c r="E67" s="31" t="n">
-        <v>9.286</v>
+        <v>8</v>
       </c>
       <c r="F67" s="31" t="n">
-        <v>8.888999999999999</v>
+        <v>7.667</v>
       </c>
       <c r="G67" s="31" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H67" s="33" t="inlineStr">
-        <is>
-          <t>22nd</t>
+        <v>7.8</v>
+      </c>
+      <c r="H67" s="35" t="inlineStr">
+        <is>
+          <t>16th</t>
         </is>
       </c>
       <c r="I67" s="31" t="inlineStr"/>
       <c r="J67" s="32" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="K67" s="31" t="n">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="L67" s="31" t="n">
-        <v>10.625</v>
+        <v>5.75</v>
       </c>
       <c r="M67" s="31" t="n">
-        <v>10.538</v>
+        <v>6.308</v>
       </c>
       <c r="N67" s="31" t="n">
-        <v>10</v>
+        <v>6.722</v>
       </c>
       <c r="O67" s="31" t="n">
-        <v>8.929</v>
+        <v>7.536</v>
       </c>
       <c r="P67" s="31" t="n">
-        <v>9.571</v>
+        <v>7.371</v>
       </c>
       <c r="Q67" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="30" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B68" s="31" t="n">
+        <v>1.216</v>
+      </c>
+      <c r="C68" s="31" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="D68" s="31" t="n">
+        <v>1.263</v>
+      </c>
+      <c r="E68" s="31" t="n">
+        <v>1.643</v>
+      </c>
+      <c r="F68" s="31" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="G68" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="35" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="I68" s="31" t="inlineStr"/>
+      <c r="J68" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q68" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="C69" s="31" t="n">
+        <v>9.103</v>
+      </c>
+      <c r="D69" s="31" t="n">
+        <v>9.420999999999999</v>
+      </c>
+      <c r="E69" s="31" t="n">
+        <v>9.286</v>
+      </c>
+      <c r="F69" s="31" t="n">
+        <v>8.888999999999999</v>
+      </c>
+      <c r="G69" s="31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="I69" s="31" t="inlineStr"/>
+      <c r="J69" s="32" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="L69" s="31" t="n">
+        <v>10.625</v>
+      </c>
+      <c r="M69" s="31" t="n">
+        <v>10.538</v>
+      </c>
+      <c r="N69" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="O69" s="31" t="n">
+        <v>8.929</v>
+      </c>
+      <c r="P69" s="31" t="n">
+        <v>9.571</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B68" s="31" t="n">
+      <c r="B70" s="31" t="n">
         <v>0.595</v>
       </c>
-      <c r="C68" s="31" t="n">
+      <c r="C70" s="31" t="n">
         <v>0.621</v>
       </c>
-      <c r="D68" s="31" t="n">
+      <c r="D70" s="31" t="n">
         <v>0.421</v>
       </c>
-      <c r="E68" s="31" t="n">
+      <c r="E70" s="31" t="n">
         <v>0.429</v>
       </c>
-      <c r="F68" s="31" t="n">
+      <c r="F70" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G68" s="31" t="n">
+      <c r="G70" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H68" s="33" t="inlineStr">
+      <c r="H70" s="33" t="inlineStr">
         <is>
           <t>26th</t>
         </is>
       </c>
-      <c r="I68" s="31" t="inlineStr"/>
-      <c r="J68" s="32" t="inlineStr">
+      <c r="I70" s="31" t="inlineStr"/>
+      <c r="J70" s="32" t="inlineStr">
         <is>
           <t>5th</t>
         </is>
       </c>
-      <c r="K68" s="31" t="n">
+      <c r="K70" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="L68" s="31" t="n">
+      <c r="L70" s="31" t="n">
         <v>0.125</v>
       </c>
-      <c r="M68" s="31" t="n">
+      <c r="M70" s="31" t="n">
         <v>0.231</v>
       </c>
-      <c r="N68" s="31" t="n">
+      <c r="N70" s="31" t="n">
         <v>0.333</v>
       </c>
-      <c r="O68" s="31" t="n">
+      <c r="O70" s="31" t="n">
         <v>0.357</v>
       </c>
-      <c r="P68" s="31" t="n">
+      <c r="P70" s="31" t="n">
         <v>0.486</v>
       </c>
-      <c r="Q68" s="34" t="inlineStr">
+      <c r="Q70" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="28" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="28" t="inlineStr">
         <is>
           <t>Milwaukee Brewers offense vs Cincinnati Reds defense</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="29" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B71" s="29" t="inlineStr">
+      <c r="B73" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C71" s="29" t="inlineStr">
+      <c r="C73" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D71" s="29" t="inlineStr">
+      <c r="D73" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E71" s="29" t="inlineStr">
+      <c r="E73" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F71" s="29" t="inlineStr">
+      <c r="F73" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G71" s="29" t="inlineStr">
+      <c r="G73" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H71" s="29" t="inlineStr">
+      <c r="H73" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I71" s="29" t="inlineStr">
+      <c r="I73" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J71" s="29" t="inlineStr">
+      <c r="J73" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K71" s="29" t="inlineStr">
+      <c r="K73" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L71" s="29" t="inlineStr">
+      <c r="L73" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M71" s="29" t="inlineStr">
+      <c r="M73" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N71" s="29" t="inlineStr">
+      <c r="N73" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O71" s="29" t="inlineStr">
+      <c r="O73" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P71" s="29" t="inlineStr">
+      <c r="P73" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q71" s="29" t="inlineStr">
+      <c r="Q73" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B72" s="31" t="n">
-        <v>4.703</v>
-      </c>
-      <c r="C72" s="31" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="D72" s="31" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="E72" s="31" t="n">
-        <v>3.733</v>
-      </c>
-      <c r="F72" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G72" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="H72" s="35" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I72" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J72" s="33" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K72" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L72" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="M72" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="N72" s="31" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="O72" s="31" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="P72" s="31" t="n">
-        <v>4.658</v>
-      </c>
-      <c r="Q72" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B73" s="31" t="n">
-        <v>7.629</v>
-      </c>
-      <c r="C73" s="31" t="n">
-        <v>7.143</v>
-      </c>
-      <c r="D73" s="31" t="n">
-        <v>7.389</v>
-      </c>
-      <c r="E73" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="F73" s="31" t="n">
-        <v>7.625</v>
-      </c>
-      <c r="G73" s="31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="I73" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J73" s="33" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="L73" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="M73" s="31" t="n">
-        <v>8.714</v>
-      </c>
-      <c r="N73" s="31" t="n">
-        <v>8.263</v>
-      </c>
-      <c r="O73" s="31" t="n">
-        <v>8.207000000000001</v>
-      </c>
-      <c r="P73" s="31" t="n">
-        <v>8.054</v>
-      </c>
-      <c r="Q73" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B74" s="31" t="n">
-        <v>0.657</v>
+        <v>4.703</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>0.5</v>
+        <v>4.133</v>
       </c>
       <c r="D74" s="31" t="n">
-        <v>0.278</v>
+        <v>4.25</v>
       </c>
       <c r="E74" s="31" t="n">
-        <v>0.308</v>
+        <v>3.733</v>
       </c>
       <c r="F74" s="31" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="G74" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L74" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="M74" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="N74" s="31" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="O74" s="31" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>4.658</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B75" s="31" t="n">
-        <v>8.228999999999999</v>
+        <v>7.629</v>
       </c>
       <c r="C75" s="31" t="n">
-        <v>8.179</v>
+        <v>7.143</v>
       </c>
       <c r="D75" s="31" t="n">
-        <v>7.944</v>
+        <v>7.389</v>
       </c>
       <c r="E75" s="31" t="n">
-        <v>8.077</v>
+        <v>7</v>
       </c>
       <c r="F75" s="31" t="n">
-        <v>7.875</v>
+        <v>7.625</v>
       </c>
       <c r="G75" s="31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H75" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="I75" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J75" s="33" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K75" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="H75" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J75" s="35" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="n">
-        <v>8.4</v>
-      </c>
       <c r="L75" s="31" t="n">
-        <v>6.667</v>
+        <v>8</v>
       </c>
       <c r="M75" s="31" t="n">
-        <v>7.143</v>
+        <v>8.714</v>
       </c>
       <c r="N75" s="31" t="n">
-        <v>7.105</v>
+        <v>8.263</v>
       </c>
       <c r="O75" s="31" t="n">
-        <v>6.966</v>
+        <v>8.207000000000001</v>
       </c>
       <c r="P75" s="31" t="n">
-        <v>7.432</v>
+        <v>8.054</v>
       </c>
       <c r="Q75" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="30" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B76" s="31" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="C76" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D76" s="31" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="E76" s="31" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="F76" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G76" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H76" s="33" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="I76" s="31" t="inlineStr"/>
+      <c r="J76" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q76" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B77" s="31" t="n">
+        <v>8.228999999999999</v>
+      </c>
+      <c r="C77" s="31" t="n">
+        <v>8.179</v>
+      </c>
+      <c r="D77" s="31" t="n">
+        <v>7.944</v>
+      </c>
+      <c r="E77" s="31" t="n">
+        <v>8.077</v>
+      </c>
+      <c r="F77" s="31" t="n">
+        <v>7.875</v>
+      </c>
+      <c r="G77" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I77" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K77" s="31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L77" s="31" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="M77" s="31" t="n">
+        <v>7.143</v>
+      </c>
+      <c r="N77" s="31" t="n">
+        <v>7.105</v>
+      </c>
+      <c r="O77" s="31" t="n">
+        <v>6.966</v>
+      </c>
+      <c r="P77" s="31" t="n">
+        <v>7.432</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B76" s="31" t="n">
+      <c r="B78" s="31" t="n">
         <v>0.629</v>
       </c>
-      <c r="C76" s="31" t="n">
+      <c r="C78" s="31" t="n">
         <v>0.536</v>
       </c>
-      <c r="D76" s="31" t="n">
+      <c r="D78" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="E76" s="31" t="n">
+      <c r="E78" s="31" t="n">
         <v>0.6919999999999999</v>
       </c>
-      <c r="F76" s="31" t="n">
+      <c r="F78" s="31" t="n">
         <v>1.125</v>
       </c>
-      <c r="G76" s="31" t="n">
+      <c r="G78" s="31" t="n">
         <v>1.6</v>
       </c>
-      <c r="H76" s="32" t="inlineStr">
+      <c r="H78" s="32" t="inlineStr">
         <is>
           <t>2nd</t>
         </is>
       </c>
-      <c r="I76" s="31" t="inlineStr">
+      <c r="I78" s="31" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J76" s="32" t="inlineStr">
+      <c r="J78" s="32" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
       </c>
-      <c r="K76" s="31" t="n">
+      <c r="K78" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="L76" s="31" t="n">
+      <c r="L78" s="31" t="n">
         <v>0.111</v>
       </c>
-      <c r="M76" s="31" t="n">
+      <c r="M78" s="31" t="n">
         <v>0.286</v>
       </c>
-      <c r="N76" s="31" t="n">
+      <c r="N78" s="31" t="n">
         <v>0.421</v>
       </c>
-      <c r="O76" s="31" t="n">
+      <c r="O78" s="31" t="n">
         <v>0.483</v>
       </c>
-      <c r="P76" s="31" t="n">
+      <c r="P78" s="31" t="n">
         <v>0.459</v>
       </c>
-      <c r="Q76" s="34" t="inlineStr">
+      <c r="Q78" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8139,13 +8139,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6805024390243902</v>
+        <v>0.6879737089201877</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-213</v>
+        <v>-220</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-105</v>
+        <v>-113</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 68.1% (fair -213). Your call.</t>
+          <t>Model 68.8% (fair -220). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8181,37 +8181,37 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees -1.5</t>
+          <t>Under 12</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.4086785714285715</v>
+        <v>0.5832211538461538</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>145</v>
+        <v>-140</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +145). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8247,37 +8247,37 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>New York Yankees -1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6332695652173914</v>
+        <v>0.4086785714285715</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-173</v>
+        <v>145</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-130</v>
+        <v>180</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 63.3% (fair -173). Your call.</t>
+          <t>Model 40.9% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8313,12 +8313,12 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -8328,22 +8328,22 @@
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5712512195121952</v>
+        <v>0.6320348017621146</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-133</v>
+        <v>-172</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-105</v>
+        <v>-127</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 63.2% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8379,37 +8379,37 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.549059405940594</v>
+        <v>0.5718980392156862</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-122</v>
+        <v>-134</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>102</v>
+        <v>-104</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8445,37 +8445,37 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5650024390243903</v>
+        <v>0.547843137254902</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-130</v>
+        <v>-121</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-105</v>
+        <v>104</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8516,32 +8516,32 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Washington Nationals @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5104651162790698</v>
+        <v>0.57645</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-104</v>
+        <v>-136</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>115</v>
+        <v>-108</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -8597,17 +8597,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5272115384615385</v>
+        <v>0.5644039215686274</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-112</v>
+        <v>-130</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -112). Your call.</t>
+          <t>Model 56.4% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8643,37 +8643,37 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4716379310344827</v>
+        <v>0.4571487603305786</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8714,32 +8714,32 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5355392156862745</v>
+        <v>0.4728755364806866</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-115</v>
+        <v>111</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -115). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8775,37 +8775,37 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4803964757709251</v>
+        <v>0.506774193548387</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>108</v>
+        <v>-103</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8841,17 +8841,17 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8861,17 +8861,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4602118644067796</v>
+        <v>0.3734693877551021</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>117</v>
+        <v>168</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 37.3% (fair +168). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8912,32 +8912,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals +1.5</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.6254067226890756</v>
+        <v>0.5367647058823529</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-167</v>
+        <v>-116</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-138</v>
+        <v>104</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -167). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8973,17 +8973,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8993,17 +8993,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4821171171171172</v>
+        <v>0.4808370044052863</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9039,37 +9039,37 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4641304347826087</v>
+        <v>0.5227884615384615</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>115</v>
+        <v>-110</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +115). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9105,17 +9105,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9125,17 +9125,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4407053941908713</v>
+        <v>0.4614893617021277</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9176,12 +9176,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9191,17 +9191,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.3814748201438848</v>
+        <v>0.5145673076923077</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>162</v>
+        <v>-106</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 38.1% (fair +162). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9242,32 +9242,32 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers -1.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.3998113207547169</v>
+        <v>0.4410788381742738</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9303,37 +9303,37 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4859447004608295</v>
+        <v>0.6269326530612244</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>106</v>
+        <v>-168</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>117</v>
+        <v>-145</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 62.7% (fair -168). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9374,12 +9374,12 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -9389,17 +9389,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4607929515418502</v>
+        <v>0.4864055299539171</v>
       </c>
       <c r="G24" s="14" t="n">
+        <v>106</v>
+      </c>
+      <c r="H24" s="15" t="n">
         <v>117</v>
-      </c>
-      <c r="H24" s="15" t="n">
-        <v>127</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9459,13 +9459,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4487124463519314</v>
+        <v>0.4476595744680851</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>123</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9501,17 +9501,17 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -9521,17 +9521,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4600881057268723</v>
+        <v>0.5874449339207048</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>117</v>
+        <v>-142</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>127</v>
+        <v>-127</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9555,7 +9555,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9591,7 +9591,7 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4460515021459227</v>
+        <v>0.4468240343347639</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>124</v>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9633,37 +9633,37 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Boston Red Sox</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals +1.5</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.6436330798479087</v>
+        <v>0.4585462555066079</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-181</v>
+        <v>118</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-163</v>
+        <v>127</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9704,32 +9704,32 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Texas Rangers -1.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5899377682403434</v>
+        <v>0.4057421875</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-144</v>
+        <v>146</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-133</v>
+        <v>156</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 40.6% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -9930,13 +9930,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4600881057268723</v>
+        <v>0.4628378378378379</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5399444444444444</v>
+        <v>0.5371666666666667</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-117</v>
+        <v>-116</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-125</v>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10058,17 +10058,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.3786</v>
+        <v>0.4763</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 37.9% (fair +164). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10124,17 +10124,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6214</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-164</v>
+        <v>-110</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 62.1% (fair -164). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10200,7 +10200,7 @@
         <v>155</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -10266,7 +10266,7 @@
         <v>-155</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -10326,13 +10326,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.549059405940594</v>
+        <v>0.547843137254902</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-122</v>
+        <v>-121</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10392,10 +10392,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4509215686274509</v>
+        <v>0.4521450980392157</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-104</v>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 45.1% (fair +122). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10464,7 +10464,7 @@
         <v>103</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -10722,10 +10722,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4607929515418502</v>
+        <v>0.4585462555066079</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>127</v>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10788,13 +10788,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5392180180180179</v>
+        <v>0.5414563876651982</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-117</v>
+        <v>-118</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10860,7 +10860,7 @@
         <v>106</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>104</v>
+        <v>-104</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10926,7 +10926,7 @@
         <v>-106</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -10992,7 +10992,7 @@
         <v>162</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11058,7 +11058,7 @@
         <v>-162</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-125</v>
+        <v>-122</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11118,7 +11118,7 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4859447004608295</v>
+        <v>0.4864055299539171</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>106</v>
@@ -11184,13 +11184,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5140577981651376</v>
+        <v>0.5135599078341013</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>-106</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-118</v>
+        <v>-117</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11256,7 +11256,7 @@
         <v>196</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-101</v>
+        <v>122</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11322,7 +11322,7 @@
         <v>-196</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -11388,7 +11388,7 @@
         <v>187</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -11520,7 +11520,7 @@
         <v>157</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11586,7 +11586,7 @@
         <v>-157</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -11642,17 +11642,17 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.3833</v>
+        <v>0.4783</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>161</v>
+        <v>109</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -11708,17 +11708,17 @@
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.6167</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-161</v>
+        <v>-109</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -11742,7 +11742,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -11778,13 +11778,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4737</v>
+        <v>0.4558590308370044</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -11808,7 +11808,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 45.6% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11844,13 +11844,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5263</v>
+        <v>0.5441347826086956</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-111</v>
+        <v>-119</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>109</v>
+        <v>-130</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 54.4% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11910,13 +11910,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4602118644067796</v>
+        <v>0.4571487603305786</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11976,10 +11976,10 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5397630901287553</v>
+        <v>0.5428454935622318</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-117</v>
+        <v>-119</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>-133</v>
@@ -12006,7 +12006,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12048,7 +12048,7 @@
         <v>161</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12306,10 +12306,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.3666960352422908</v>
+        <v>0.3679735682819383</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>127</v>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 36.7% (fair +173). Your call.</t>
+          <t>Model 36.8% (fair +172). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -12372,13 +12372,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.6332695652173914</v>
+        <v>0.6320348017621146</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-173</v>
+        <v>-172</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-130</v>
+        <v>-127</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 63.3% (fair -173). Your call.</t>
+          <t>Model 63.2% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12434,7 +12434,7 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
@@ -12444,7 +12444,7 @@
         <v>111</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-101</v>
+        <v>122</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
@@ -12576,7 +12576,7 @@
         <v>-133</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12642,7 +12642,7 @@
         <v>133</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-112</v>
+        <v>-116</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12830,17 +12830,17 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Over 11.5</t>
+          <t>Over 12</t>
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.2407</v>
+        <v>0.1578</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>315</v>
+        <v>534</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 24.1% (fair +315). Your call.</t>
+          <t>Model 15.8% (fair +534). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12896,17 +12896,17 @@
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>Under 11.5</t>
+          <t>Under 12</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.7593</v>
+        <v>0.8422000000000001</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-315</v>
+        <v>-534</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -12930,7 +12930,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 75.9% (fair -315). Your call.</t>
+          <t>Model 84.2% (fair -534). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12966,7 +12966,7 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4460515021459227</v>
+        <v>0.4468240343347639</v>
       </c>
       <c r="G51" s="14" t="n">
         <v>124</v>
@@ -12996,7 +12996,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13032,13 +13032,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5539694915254237</v>
+        <v>0.5531794871794872</v>
       </c>
       <c r="G52" s="14" t="n">
         <v>-124</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>-136</v>
+        <v>-134</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13062,7 +13062,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13098,7 +13098,7 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4803964757709251</v>
+        <v>0.4808370044052863</v>
       </c>
       <c r="G53" s="14" t="n">
         <v>108</v>
@@ -13128,7 +13128,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13164,13 +13164,13 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5195810572687225</v>
+        <v>0.5191646017699115</v>
       </c>
       <c r="G54" s="14" t="n">
         <v>-108</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>-127</v>
+        <v>-126</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F55" s="13" t="n">
@@ -13236,7 +13236,7 @@
         <v>107</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>-103</v>
+        <v>127</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13292,7 +13292,7 @@
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F56" s="13" t="n">
@@ -13302,7 +13302,7 @@
         <v>-107</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -13368,7 +13368,7 @@
         <v>183</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -13434,7 +13434,7 @@
         <v>-183</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-117</v>
+        <v>-122</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13494,10 +13494,10 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5358815450643777</v>
+        <v>0.5385072961373391</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>-115</v>
+        <v>-117</v>
       </c>
       <c r="H59" s="15" t="n">
         <v>-133</v>
@@ -13524,7 +13524,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -115). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -13560,13 +13560,13 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4641304347826087</v>
+        <v>0.4614893617021277</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -13590,7 +13590,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +115). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -13622,17 +13622,17 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Over 11.5</t>
+          <t>Over 12</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4303</v>
+        <v>0.4167694581280788</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>-108</v>
+        <v>-103</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -13656,7 +13656,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 43.0% (fair +132). Your call.</t>
+          <t>Model 41.7% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -13688,17 +13688,17 @@
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>Under 11.5</t>
+          <t>Under 12</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5697</v>
+        <v>0.5832211538461538</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-132</v>
+        <v>-140</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -132). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14274,13 +14274,13 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4487124463519314</v>
+        <v>0.4476595744680851</v>
       </c>
       <c r="G71" s="14" t="n">
         <v>123</v>
       </c>
       <c r="H71" s="15" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
@@ -14304,7 +14304,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -14340,7 +14340,7 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5513042016806722</v>
+        <v>0.5523478991596639</v>
       </c>
       <c r="G72" s="14" t="n">
         <v>-123</v>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -14406,13 +14406,13 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5433</v>
+        <v>0.506774193548387</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-119</v>
+        <v>-103</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4567</v>
+        <v>0.4932173076923076</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>100</v>
+        <v>-108</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14670,10 +14670,10 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.5355392156862745</v>
+        <v>0.5367647058823529</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="H77" s="15" t="n">
         <v>104</v>
@@ -14700,7 +14700,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -115). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14736,13 +14736,13 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.4645049504950495</v>
+        <v>0.463235294117647</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -14766,7 +14766,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14802,10 +14802,10 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5134235294117647</v>
+        <v>0.5158196078431372</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-106</v>
+        <v>-107</v>
       </c>
       <c r="H79" s="15" t="n">
         <v>-104</v>
@@ -14832,7 +14832,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -106). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14868,13 +14868,13 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4866078431372549</v>
+        <v>0.48415</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14898,7 +14898,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +106). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14934,13 +14934,13 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.6001629629629629</v>
+        <v>0.5942372623574145</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-150</v>
+        <v>-146</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>-170</v>
+        <v>-163</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -14964,7 +14964,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 60.0% (fair -150). Your call.</t>
+          <t>Model 59.4% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15000,13 +15000,13 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.3998113207547169</v>
+        <v>0.4057421875</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -15030,7 +15030,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 40.6% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15066,13 +15066,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.3814748201438848</v>
+        <v>0.3734693877551021</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 38.1% (fair +162). Your call.</t>
+          <t>Model 37.3% (fair +168). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15132,13 +15132,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.6185475524475526</v>
+        <v>0.6265408163265307</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-162</v>
+        <v>-168</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-186</v>
+        <v>-194</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15162,7 +15162,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 62.7% (fair -168). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15198,10 +15198,10 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.5272115384615385</v>
+        <v>0.5227884615384615</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="H85" s="15" t="n">
         <v>108</v>
@@ -15228,7 +15228,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -112). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15264,13 +15264,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.4728073170731708</v>
+        <v>0.4771995305164319</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-105</v>
+        <v>-113</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +112). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15330,13 +15330,13 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.4586854460093897</v>
+        <v>0.4611059907834101</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15396,13 +15396,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.5412777777777777</v>
+        <v>0.5388953488372094</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-118</v>
+        <v>-117</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-125</v>
+        <v>-115</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15462,10 +15462,10 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.4100873362445415</v>
+        <v>0.4125327510917031</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H89" s="15" t="n">
         <v>129</v>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15528,13 +15528,13 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.5899377682403434</v>
+        <v>0.5874449339207048</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>-144</v>
+        <v>-142</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>-133</v>
+        <v>-127</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15594,13 +15594,13 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.493921568627451</v>
+        <v>0.4914903846153846</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 49.1% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15660,10 +15660,10 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5060654377880184</v>
+        <v>0.5084917050691244</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="H92" s="15" t="n">
         <v>-117</v>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -15858,10 +15858,10 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.4821171171171172</v>
+        <v>0.505</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>107</v>
+        <v>-102</v>
       </c>
       <c r="H95" s="15" t="n">
         <v>122</v>
@@ -15888,7 +15888,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -15924,13 +15924,13 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.5178901408450703</v>
+        <v>0.495</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>-107</v>
+        <v>102</v>
       </c>
       <c r="H96" s="15" t="n">
-        <v>-113</v>
+        <v>-111</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -15986,7 +15986,7 @@
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
@@ -15996,7 +15996,7 @@
         <v>127</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>-105</v>
+        <v>104</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
@@ -16062,7 +16062,7 @@
         <v>-127</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -16128,7 +16128,7 @@
         <v>183</v>
       </c>
       <c r="H99" s="15" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
@@ -16326,7 +16326,7 @@
         <v>121</v>
       </c>
       <c r="H102" s="15" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I102" s="13">
         <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
@@ -16386,13 +16386,13 @@
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.3769</v>
+        <v>0.4235483870967742</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 37.7% (fair +165). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -16452,13 +16452,13 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.6231</v>
+        <v>0.57645</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>-165</v>
+        <v>-136</v>
       </c>
       <c r="H104" s="15" t="n">
-        <v>100</v>
+        <v>-108</v>
       </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 62.3% (fair -165). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -16650,7 +16650,7 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.4407053941908713</v>
+        <v>0.4410788381742738</v>
       </c>
       <c r="G107" s="14" t="n">
         <v>127</v>
@@ -16716,13 +16716,13 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.5592983606557377</v>
+        <v>0.5589358024691359</v>
       </c>
       <c r="G108" s="14" t="n">
         <v>-127</v>
       </c>
       <c r="H108" s="15" t="n">
-        <v>-144</v>
+        <v>-143</v>
       </c>
       <c r="I108" s="13">
         <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
@@ -16782,7 +16782,7 @@
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.435</v>
+        <v>0.4355882352941177</v>
       </c>
       <c r="G109" s="14" t="n">
         <v>130</v>
@@ -16812,7 +16812,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 43.6% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -16848,13 +16848,13 @@
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.5650024390243903</v>
+        <v>0.5644039215686274</v>
       </c>
       <c r="G110" s="14" t="n">
         <v>-130</v>
       </c>
       <c r="H110" s="15" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="I110" s="13">
         <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
@@ -16878,7 +16878,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 56.4% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -16914,13 +16914,13 @@
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.4051282051282051</v>
+        <v>0.4017213114754098</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H111" s="15" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="I111" s="13">
         <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
@@ -16944,7 +16944,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 40.2% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -16980,13 +16980,13 @@
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.59484</v>
+        <v>0.5982877551020408</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>-147</v>
+        <v>-149</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>-150</v>
+        <v>-145</v>
       </c>
       <c r="I112" s="13">
         <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -17046,10 +17046,10 @@
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.4895307692307692</v>
+        <v>0.4854288461538461</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H113" s="15" t="n">
         <v>-108</v>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17112,13 +17112,13 @@
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.5104651162790698</v>
+        <v>0.5145673076923077</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>-104</v>
+        <v>-106</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -17142,7 +17142,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17178,13 +17178,13 @@
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.4287534653465346</v>
+        <v>0.4281</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H115" s="15" t="n">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="I115" s="13">
         <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
@@ -17208,7 +17208,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -17244,13 +17244,13 @@
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.5712512195121952</v>
+        <v>0.5718980392156862</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>-133</v>
+        <v>-134</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.6254067226890756</v>
+        <v>0.6269326530612244</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>-167</v>
+        <v>-168</v>
       </c>
       <c r="H117" s="15" t="n">
-        <v>-138</v>
+        <v>-145</v>
       </c>
       <c r="I117" s="13">
         <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
@@ -17340,7 +17340,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -167). Your call.</t>
+          <t>Model 62.7% (fair -168). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -17376,13 +17376,13 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.3745833333333334</v>
+        <v>0.373109243697479</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -17406,7 +17406,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 37.5% (fair +167). Your call.</t>
+          <t>Model 37.3% (fair +168). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -17442,13 +17442,13 @@
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.3634765625</v>
+        <v>0.3613688212927757</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H119" s="15" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="I119" s="13">
         <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
@@ -17472,7 +17472,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 36.3% (fair +175). Your call.</t>
+          <t>Model 36.1% (fair +177). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -17508,13 +17508,13 @@
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.6365389513108615</v>
+        <v>0.638612927756654</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>-175</v>
+        <v>-177</v>
       </c>
       <c r="H120" s="15" t="n">
-        <v>-167</v>
+        <v>-163</v>
       </c>
       <c r="I120" s="13">
         <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
@@ -17538,7 +17538,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 63.7% (fair -175). Your call.</t>
+          <t>Model 63.9% (fair -177). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -17570,17 +17570,17 @@
       </c>
       <c r="E121" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.49195</v>
+        <v>0.5498802816901408</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>103</v>
+        <v>-122</v>
       </c>
       <c r="H121" s="15" t="n">
-        <v>100</v>
+        <v>-113</v>
       </c>
       <c r="I121" s="13">
         <f>IF($H$121="","",IF($H$121&lt;0,-$H$121/(-$H$121+100),100/($H$121+100)))</f>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -17636,17 +17636,17 @@
       </c>
       <c r="E122" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.50805</v>
+        <v>0.4500980392156863</v>
       </c>
       <c r="G122" s="14" t="n">
-        <v>-103</v>
+        <v>122</v>
       </c>
       <c r="H122" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I122" s="13">
         <f>IF($H$122="","",IF($H$122&lt;0,-$H$122/(-$H$122+100),100/($H$122+100)))</f>
@@ -17670,7 +17670,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 45.0% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -17706,13 +17706,13 @@
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>0.4716379310344827</v>
+        <v>0.4728755364806866</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H123" s="15" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I123" s="13">
         <f>IF($H$123="","",IF($H$123&lt;0,-$H$123/(-$H$123+100),100/($H$123+100)))</f>
@@ -17736,7 +17736,7 @@
       </c>
       <c r="N123" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O123" s="15" t="n"/>
@@ -17772,13 +17772,13 @@
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.5283326530612245</v>
+        <v>0.5270999999999999</v>
       </c>
       <c r="G124" s="14" t="n">
-        <v>-112</v>
+        <v>-111</v>
       </c>
       <c r="H124" s="15" t="n">
-        <v>-145</v>
+        <v>-140</v>
       </c>
       <c r="I124" s="13">
         <f>IF($H$124="","",IF($H$124&lt;0,-$H$124/(-$H$124+100),100/($H$124+100)))</f>
@@ -17802,7 +17802,7 @@
       </c>
       <c r="N124" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O124" s="15" t="n"/>
@@ -17838,13 +17838,13 @@
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.413175965665236</v>
+        <v>0.4102127659574468</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H125" s="15" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I125" s="13">
         <f>IF($H$125="","",IF($H$125&lt;0,-$H$125/(-$H$125+100),100/($H$125+100)))</f>
@@ -17868,7 +17868,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 41.3% (fair +142). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -17904,13 +17904,13 @@
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.5867982832618026</v>
+        <v>0.5897470588235293</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>-142</v>
+        <v>-144</v>
       </c>
       <c r="H126" s="15" t="n">
-        <v>-133</v>
+        <v>-138</v>
       </c>
       <c r="I126" s="13">
         <f>IF($H$126="","",IF($H$126&lt;0,-$H$126/(-$H$126+100),100/($H$126+100)))</f>
@@ -17934,7 +17934,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -17970,13 +17970,13 @@
         </is>
       </c>
       <c r="F127" s="13" t="n">
-        <v>0.3195</v>
+        <v>0.312</v>
       </c>
       <c r="G127" s="14" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="H127" s="15" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I127" s="13">
         <f>IF($H$127="","",IF($H$127&lt;0,-$H$127/(-$H$127+100),100/($H$127+100)))</f>
@@ -18000,7 +18000,7 @@
       </c>
       <c r="N127" s="19" t="inlineStr">
         <is>
-          <t>Model 31.9% (fair +213). Your call.</t>
+          <t>Model 31.2% (fair +221). Your call.</t>
         </is>
       </c>
       <c r="O127" s="15" t="n"/>
@@ -18036,13 +18036,13 @@
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.6805024390243902</v>
+        <v>0.6879737089201877</v>
       </c>
       <c r="G128" s="14" t="n">
-        <v>-213</v>
+        <v>-220</v>
       </c>
       <c r="H128" s="15" t="n">
-        <v>-105</v>
+        <v>-113</v>
       </c>
       <c r="I128" s="13">
         <f>IF($H$128="","",IF($H$128&lt;0,-$H$128/(-$H$128+100),100/($H$128+100)))</f>
@@ -18066,7 +18066,7 @@
       </c>
       <c r="N128" s="19" t="inlineStr">
         <is>
-          <t>Model 68.1% (fair -213). Your call.</t>
+          <t>Model 68.8% (fair -220). Your call.</t>
         </is>
       </c>
       <c r="O128" s="15" t="n"/>
@@ -18102,13 +18102,13 @@
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.4438222222222222</v>
+        <v>0.4452422907488987</v>
       </c>
       <c r="G129" s="14" t="n">
         <v>125</v>
       </c>
       <c r="H129" s="15" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I129" s="13">
         <f>IF($H$129="","",IF($H$129&lt;0,-$H$129/(-$H$129+100),100/($H$129+100)))</f>
@@ -18132,7 +18132,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -18168,13 +18168,13 @@
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.5562081632653061</v>
+        <v>0.5547831932773108</v>
       </c>
       <c r="G130" s="14" t="n">
         <v>-125</v>
       </c>
       <c r="H130" s="15" t="n">
-        <v>-145</v>
+        <v>-138</v>
       </c>
       <c r="I130" s="13">
         <f>IF($H$130="","",IF($H$130&lt;0,-$H$130/(-$H$130+100),100/($H$130+100)))</f>
@@ -18198,7 +18198,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>

--- a/data/output/workbook/2026-06-29.xlsx
+++ b/data/output/workbook/2026-06-29.xlsx
@@ -490,7 +490,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9648825"/>
+    <ext cx="10125075" cy="10086975"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -520,7 +520,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9086850"/>
+    <ext cx="10125075" cy="9467850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29 17:27</t>
+          <t>2026-06-29 18:56</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:Q78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2850,317 +2850,183 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="28" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="28" t="inlineStr">
         <is>
           <t>Washington Nationals offense vs Boston Red Sox defense</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="29" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B63" s="29" t="inlineStr">
+      <c r="B65" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C63" s="29" t="inlineStr">
+      <c r="C65" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D63" s="29" t="inlineStr">
+      <c r="D65" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E63" s="29" t="inlineStr">
+      <c r="E65" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F63" s="29" t="inlineStr">
+      <c r="F65" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G63" s="29" t="inlineStr">
+      <c r="G65" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H63" s="29" t="inlineStr">
+      <c r="H65" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I63" s="29" t="inlineStr">
+      <c r="I65" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J63" s="29" t="inlineStr">
+      <c r="J65" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K63" s="29" t="inlineStr">
+      <c r="K65" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L63" s="29" t="inlineStr">
+      <c r="L65" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M63" s="29" t="inlineStr">
+      <c r="M65" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N63" s="29" t="inlineStr">
+      <c r="N65" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O63" s="29" t="inlineStr">
+      <c r="O65" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P63" s="29" t="inlineStr">
+      <c r="P65" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q63" s="29" t="inlineStr">
+      <c r="Q65" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B64" s="31" t="n">
-        <v>5.317</v>
-      </c>
-      <c r="C64" s="31" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="D64" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="E64" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F64" s="31" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="G64" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H64" s="32" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I64" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J64" s="35" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="K64" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L64" s="31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="M64" s="31" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="N64" s="31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O64" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P64" s="31" t="n">
-        <v>4.324</v>
-      </c>
-      <c r="Q64" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B65" s="31" t="n">
-        <v>8.462</v>
-      </c>
-      <c r="C65" s="31" t="n">
-        <v>7.893</v>
-      </c>
-      <c r="D65" s="31" t="n">
-        <v>7.611</v>
-      </c>
-      <c r="E65" s="31" t="n">
-        <v>7.571</v>
-      </c>
-      <c r="F65" s="31" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G65" s="31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H65" s="35" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="I65" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J65" s="33" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="K65" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="L65" s="31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="M65" s="31" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="N65" s="31" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O65" s="31" t="n">
-        <v>8.345000000000001</v>
-      </c>
-      <c r="P65" s="31" t="n">
-        <v>8.305999999999999</v>
-      </c>
-      <c r="Q65" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B66" s="31" t="n">
-        <v>1.256</v>
+        <v>5.317</v>
       </c>
       <c r="C66" s="31" t="n">
-        <v>1.179</v>
+        <v>4.933</v>
       </c>
       <c r="D66" s="31" t="n">
-        <v>1.444</v>
+        <v>5</v>
       </c>
       <c r="E66" s="31" t="n">
-        <v>1.357</v>
+        <v>4.8</v>
       </c>
       <c r="F66" s="31" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="G66" s="31" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="H66" s="32" t="inlineStr">
         <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I66" s="31" t="inlineStr"/>
-      <c r="J66" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K66" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L66" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M66" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N66" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O66" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P66" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I66" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J66" s="35" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="K66" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L66" s="31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M66" s="31" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="N66" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O66" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P66" s="31" t="n">
+        <v>4.324</v>
       </c>
       <c r="Q66" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B67" s="31" t="n">
-        <v>8.026</v>
+        <v>8.462</v>
       </c>
       <c r="C67" s="31" t="n">
-        <v>7.714</v>
+        <v>7.893</v>
       </c>
       <c r="D67" s="31" t="n">
-        <v>8.055999999999999</v>
+        <v>7.611</v>
       </c>
       <c r="E67" s="31" t="n">
         <v>7.571</v>
       </c>
       <c r="F67" s="31" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="G67" s="31" t="n">
         <v>8.199999999999999</v>
@@ -3172,505 +3038,639 @@
       </c>
       <c r="I67" s="31" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J67" s="35" t="inlineStr">
-        <is>
-          <t>17th</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J67" s="33" t="inlineStr">
+        <is>
+          <t>22nd</t>
         </is>
       </c>
       <c r="K67" s="31" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="L67" s="31" t="n">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="M67" s="31" t="n">
-        <v>8.667</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N67" s="31" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="O67" s="31" t="n">
-        <v>8.034000000000001</v>
+        <v>8.345000000000001</v>
       </c>
       <c r="P67" s="31" t="n">
-        <v>8.138999999999999</v>
+        <v>8.305999999999999</v>
       </c>
       <c r="Q67" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="30" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B68" s="31" t="n">
+        <v>1.256</v>
+      </c>
+      <c r="C68" s="31" t="n">
+        <v>1.179</v>
+      </c>
+      <c r="D68" s="31" t="n">
+        <v>1.444</v>
+      </c>
+      <c r="E68" s="31" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="F68" s="31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G68" s="31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H68" s="32" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I68" s="31" t="inlineStr"/>
+      <c r="J68" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q68" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="n">
+        <v>8.026</v>
+      </c>
+      <c r="C69" s="31" t="n">
+        <v>7.714</v>
+      </c>
+      <c r="D69" s="31" t="n">
+        <v>8.055999999999999</v>
+      </c>
+      <c r="E69" s="31" t="n">
+        <v>7.571</v>
+      </c>
+      <c r="F69" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="G69" s="31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="I69" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J69" s="35" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L69" s="31" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="M69" s="31" t="n">
+        <v>8.667</v>
+      </c>
+      <c r="N69" s="31" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="O69" s="31" t="n">
+        <v>8.034000000000001</v>
+      </c>
+      <c r="P69" s="31" t="n">
+        <v>8.138999999999999</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B68" s="31" t="n">
+      <c r="B70" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="C68" s="31" t="n">
+      <c r="C70" s="31" t="n">
         <v>0.929</v>
       </c>
-      <c r="D68" s="31" t="n">
+      <c r="D70" s="31" t="n">
         <v>1.056</v>
       </c>
-      <c r="E68" s="31" t="n">
+      <c r="E70" s="31" t="n">
         <v>0.714</v>
       </c>
-      <c r="F68" s="31" t="n">
+      <c r="F70" s="31" t="n">
         <v>0.9</v>
       </c>
-      <c r="G68" s="31" t="n">
+      <c r="G70" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="H68" s="35" t="inlineStr">
+      <c r="H70" s="35" t="inlineStr">
         <is>
           <t>15th</t>
         </is>
       </c>
-      <c r="I68" s="31" t="inlineStr">
+      <c r="I70" s="31" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
-      <c r="J68" s="33" t="inlineStr">
+      <c r="J70" s="33" t="inlineStr">
         <is>
           <t>24th</t>
         </is>
       </c>
-      <c r="K68" s="31" t="n">
+      <c r="K70" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="L68" s="31" t="n">
+      <c r="L70" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="M68" s="31" t="n">
+      <c r="M70" s="31" t="n">
         <v>0.867</v>
       </c>
-      <c r="N68" s="31" t="n">
+      <c r="N70" s="31" t="n">
         <v>0.85</v>
       </c>
-      <c r="O68" s="31" t="n">
+      <c r="O70" s="31" t="n">
         <v>0.724</v>
       </c>
-      <c r="P68" s="31" t="n">
+      <c r="P70" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q68" s="34" t="inlineStr">
+      <c r="Q70" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="28" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="28" t="inlineStr">
         <is>
           <t>Boston Red Sox offense vs Washington Nationals defense</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="29" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B71" s="29" t="inlineStr">
+      <c r="B73" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C71" s="29" t="inlineStr">
+      <c r="C73" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D71" s="29" t="inlineStr">
+      <c r="D73" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E71" s="29" t="inlineStr">
+      <c r="E73" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F71" s="29" t="inlineStr">
+      <c r="F73" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G71" s="29" t="inlineStr">
+      <c r="G73" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H71" s="29" t="inlineStr">
+      <c r="H73" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I71" s="29" t="inlineStr">
+      <c r="I73" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J71" s="29" t="inlineStr">
+      <c r="J73" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K71" s="29" t="inlineStr">
+      <c r="K73" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L71" s="29" t="inlineStr">
+      <c r="L73" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M71" s="29" t="inlineStr">
+      <c r="M73" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N71" s="29" t="inlineStr">
+      <c r="N73" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O71" s="29" t="inlineStr">
+      <c r="O73" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P71" s="29" t="inlineStr">
+      <c r="P73" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q71" s="29" t="inlineStr">
+      <c r="Q73" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B72" s="31" t="n">
-        <v>4.027</v>
-      </c>
-      <c r="C72" s="31" t="n">
-        <v>4.233</v>
-      </c>
-      <c r="D72" s="31" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="E72" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F72" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G72" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H72" s="35" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="I72" s="31" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K72" s="31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L72" s="31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M72" s="31" t="n">
-        <v>3.933</v>
-      </c>
-      <c r="N72" s="31" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="O72" s="31" t="n">
-        <v>5.033</v>
-      </c>
-      <c r="P72" s="31" t="n">
-        <v>5.439</v>
-      </c>
-      <c r="Q72" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B73" s="31" t="n">
-        <v>7.833</v>
-      </c>
-      <c r="C73" s="31" t="n">
-        <v>7.966</v>
-      </c>
-      <c r="D73" s="31" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="E73" s="31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="F73" s="31" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="G73" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="H73" s="32" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="I73" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J73" s="32" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="L73" s="31" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="M73" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="N73" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="O73" s="31" t="n">
-        <v>8.643000000000001</v>
-      </c>
-      <c r="P73" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q73" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B74" s="31" t="n">
-        <v>0.694</v>
+        <v>4.027</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>0.586</v>
+        <v>4.233</v>
       </c>
       <c r="D74" s="31" t="n">
-        <v>0.7</v>
+        <v>3.95</v>
       </c>
       <c r="E74" s="31" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="F74" s="31" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="G74" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>22nd</t>
+        <v>4.4</v>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>13th</t>
         </is>
       </c>
       <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L74" s="31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M74" s="31" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="N74" s="31" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="O74" s="31" t="n">
+        <v>5.033</v>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>5.439</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B75" s="31" t="n">
-        <v>8.305999999999999</v>
+        <v>7.833</v>
       </c>
       <c r="C75" s="31" t="n">
-        <v>7.724</v>
+        <v>7.966</v>
       </c>
       <c r="D75" s="31" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="E75" s="31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F75" s="31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G75" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="H75" s="32" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="I75" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J75" s="32" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="K75" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="L75" s="31" t="n">
         <v>7.9</v>
       </c>
-      <c r="E75" s="31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="F75" s="31" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="G75" s="31" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H75" s="35" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr"/>
-      <c r="J75" s="32" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="L75" s="31" t="n">
-        <v>9.4</v>
-      </c>
       <c r="M75" s="31" t="n">
-        <v>9.929</v>
+        <v>8</v>
       </c>
       <c r="N75" s="31" t="n">
-        <v>8.944000000000001</v>
+        <v>8</v>
       </c>
       <c r="O75" s="31" t="n">
         <v>8.643000000000001</v>
       </c>
       <c r="P75" s="31" t="n">
-        <v>8.333</v>
+        <v>9</v>
       </c>
       <c r="Q75" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="30" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B76" s="31" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="C76" s="31" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="D76" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E76" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F76" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H76" s="33" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="I76" s="31" t="inlineStr"/>
+      <c r="J76" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q76" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B77" s="31" t="n">
+        <v>8.305999999999999</v>
+      </c>
+      <c r="C77" s="31" t="n">
+        <v>7.724</v>
+      </c>
+      <c r="D77" s="31" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E77" s="31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F77" s="31" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="G77" s="31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="I77" s="31" t="inlineStr"/>
+      <c r="J77" s="32" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="K77" s="31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L77" s="31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="M77" s="31" t="n">
+        <v>9.929</v>
+      </c>
+      <c r="N77" s="31" t="n">
+        <v>8.944000000000001</v>
+      </c>
+      <c r="O77" s="31" t="n">
+        <v>8.643000000000001</v>
+      </c>
+      <c r="P77" s="31" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B76" s="31" t="n">
+      <c r="B78" s="31" t="n">
         <v>0.278</v>
       </c>
-      <c r="C76" s="31" t="n">
+      <c r="C78" s="31" t="n">
         <v>0.31</v>
       </c>
-      <c r="D76" s="31" t="n">
+      <c r="D78" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="E76" s="31" t="n">
+      <c r="E78" s="31" t="n">
         <v>0.333</v>
       </c>
-      <c r="F76" s="31" t="n">
+      <c r="F78" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="G76" s="31" t="n">
+      <c r="G78" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H76" s="32" t="inlineStr">
+      <c r="H78" s="32" t="inlineStr">
         <is>
           <t>4th</t>
         </is>
       </c>
-      <c r="I76" s="31" t="inlineStr">
+      <c r="I78" s="31" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J76" s="35" t="inlineStr">
+      <c r="J78" s="35" t="inlineStr">
         <is>
           <t>19th</t>
         </is>
       </c>
-      <c r="K76" s="31" t="n">
+      <c r="K78" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="L76" s="31" t="n">
+      <c r="L78" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="M76" s="31" t="n">
+      <c r="M78" s="31" t="n">
         <v>0.357</v>
       </c>
-      <c r="N76" s="31" t="n">
+      <c r="N78" s="31" t="n">
         <v>0.333</v>
       </c>
-      <c r="O76" s="31" t="n">
+      <c r="O78" s="31" t="n">
         <v>0.429</v>
       </c>
-      <c r="P76" s="31" t="n">
+      <c r="P78" s="31" t="n">
         <v>0.436</v>
       </c>
-      <c r="Q76" s="34" t="inlineStr">
+      <c r="Q78" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -3689,7 +3689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3706,811 +3706,811 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="28" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="28" t="inlineStr">
         <is>
           <t>Texas Rangers offense vs Cleveland Guardians defense</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="29" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B60" s="29" t="inlineStr">
+      <c r="B62" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C60" s="29" t="inlineStr">
+      <c r="C62" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D60" s="29" t="inlineStr">
+      <c r="D62" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E60" s="29" t="inlineStr">
+      <c r="E62" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F60" s="29" t="inlineStr">
+      <c r="F62" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G60" s="29" t="inlineStr">
+      <c r="G62" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H60" s="29" t="inlineStr">
+      <c r="H62" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I60" s="29" t="inlineStr">
+      <c r="I62" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J60" s="29" t="inlineStr">
+      <c r="J62" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K60" s="29" t="inlineStr">
+      <c r="K62" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L60" s="29" t="inlineStr">
+      <c r="L62" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M60" s="29" t="inlineStr">
+      <c r="M62" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N60" s="29" t="inlineStr">
+      <c r="N62" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O60" s="29" t="inlineStr">
+      <c r="O62" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P60" s="29" t="inlineStr">
+      <c r="P62" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q60" s="29" t="inlineStr">
+      <c r="Q62" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B61" s="31" t="n">
-        <v>3.909</v>
-      </c>
-      <c r="C61" s="31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D61" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E61" s="31" t="n">
-        <v>3.467</v>
-      </c>
-      <c r="F61" s="31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G61" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H61" s="35" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="I61" s="31" t="inlineStr"/>
-      <c r="J61" s="32" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K61" s="31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L61" s="31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M61" s="31" t="n">
-        <v>3.533</v>
-      </c>
-      <c r="N61" s="31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O61" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P61" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q61" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B62" s="31" t="n">
-        <v>7.919</v>
-      </c>
-      <c r="C62" s="31" t="n">
-        <v>7.96</v>
-      </c>
-      <c r="D62" s="31" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E62" s="31" t="n">
-        <v>7.692</v>
-      </c>
-      <c r="F62" s="31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="G62" s="31" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H62" s="32" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I62" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J62" s="32" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K62" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="L62" s="31" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="M62" s="31" t="n">
-        <v>7.533</v>
-      </c>
-      <c r="N62" s="31" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O62" s="31" t="n">
-        <v>7.833</v>
-      </c>
-      <c r="P62" s="31" t="n">
-        <v>7.538</v>
-      </c>
-      <c r="Q62" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B63" s="31" t="n">
-        <v>1</v>
+        <v>3.909</v>
       </c>
       <c r="C63" s="31" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="D63" s="31" t="n">
-        <v>0.8120000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="E63" s="31" t="n">
-        <v>0.923</v>
+        <v>3.467</v>
       </c>
       <c r="F63" s="31" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="G63" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H63" s="32" t="inlineStr">
-        <is>
-          <t>10th</t>
+        <v>4.6</v>
+      </c>
+      <c r="H63" s="35" t="inlineStr">
+        <is>
+          <t>11th</t>
         </is>
       </c>
       <c r="I63" s="31" t="inlineStr"/>
-      <c r="J63" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K63" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L63" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M63" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N63" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O63" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P63" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J63" s="32" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K63" s="31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L63" s="31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M63" s="31" t="n">
+        <v>3.533</v>
+      </c>
+      <c r="N63" s="31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O63" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P63" s="31" t="n">
+        <v>4</v>
       </c>
       <c r="Q63" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B64" s="31" t="n">
-        <v>8.595000000000001</v>
+        <v>7.919</v>
       </c>
       <c r="C64" s="31" t="n">
-        <v>8.44</v>
+        <v>7.96</v>
       </c>
       <c r="D64" s="31" t="n">
         <v>7.5</v>
       </c>
       <c r="E64" s="31" t="n">
-        <v>6.846</v>
+        <v>7.692</v>
       </c>
       <c r="F64" s="31" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="G64" s="31" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H64" s="32" t="inlineStr">
         <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I64" s="31" t="inlineStr"/>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I64" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
       <c r="J64" s="32" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="K64" s="31" t="n">
-        <v>11.2</v>
+        <v>6</v>
       </c>
       <c r="L64" s="31" t="n">
-        <v>10.3</v>
+        <v>7.3</v>
       </c>
       <c r="M64" s="31" t="n">
-        <v>9.132999999999999</v>
+        <v>7.533</v>
       </c>
       <c r="N64" s="31" t="n">
-        <v>9.449999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="O64" s="31" t="n">
-        <v>9.233000000000001</v>
+        <v>7.833</v>
       </c>
       <c r="P64" s="31" t="n">
-        <v>9.487</v>
+        <v>7.538</v>
       </c>
       <c r="Q64" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="30" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B65" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" s="31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D65" s="31" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="E65" s="31" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="F65" s="31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G65" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H65" s="32" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I65" s="31" t="inlineStr"/>
+      <c r="J65" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K65" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L65" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M65" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N65" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O65" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P65" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q65" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B66" s="31" t="n">
+        <v>8.595000000000001</v>
+      </c>
+      <c r="C66" s="31" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="D66" s="31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E66" s="31" t="n">
+        <v>6.846</v>
+      </c>
+      <c r="F66" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="G66" s="31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H66" s="32" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I66" s="31" t="inlineStr"/>
+      <c r="J66" s="32" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K66" s="31" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="L66" s="31" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="M66" s="31" t="n">
+        <v>9.132999999999999</v>
+      </c>
+      <c r="N66" s="31" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="O66" s="31" t="n">
+        <v>9.233000000000001</v>
+      </c>
+      <c r="P66" s="31" t="n">
+        <v>9.487</v>
+      </c>
+      <c r="Q66" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B65" s="31" t="n">
+      <c r="B67" s="31" t="n">
         <v>0.297</v>
       </c>
-      <c r="C65" s="31" t="n">
+      <c r="C67" s="31" t="n">
         <v>0.32</v>
       </c>
-      <c r="D65" s="31" t="n">
+      <c r="D67" s="31" t="n">
         <v>0.125</v>
       </c>
-      <c r="E65" s="31" t="n">
+      <c r="E67" s="31" t="n">
         <v>0.154</v>
       </c>
-      <c r="F65" s="31" t="n">
+      <c r="F67" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="G65" s="31" t="n">
+      <c r="G67" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="H65" s="35" t="inlineStr">
+      <c r="H67" s="35" t="inlineStr">
         <is>
           <t>19th</t>
         </is>
       </c>
-      <c r="I65" s="31" t="inlineStr"/>
-      <c r="J65" s="32" t="inlineStr">
+      <c r="I67" s="31" t="inlineStr"/>
+      <c r="J67" s="32" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="K65" s="31" t="n">
+      <c r="K67" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="L65" s="31" t="n">
+      <c r="L67" s="31" t="n">
         <v>0.1</v>
       </c>
-      <c r="M65" s="31" t="n">
+      <c r="M67" s="31" t="n">
         <v>0.467</v>
       </c>
-      <c r="N65" s="31" t="n">
+      <c r="N67" s="31" t="n">
         <v>0.45</v>
       </c>
-      <c r="O65" s="31" t="n">
+      <c r="O67" s="31" t="n">
         <v>0.367</v>
       </c>
-      <c r="P65" s="31" t="n">
+      <c r="P67" s="31" t="n">
         <v>0.308</v>
       </c>
-      <c r="Q65" s="34" t="inlineStr">
+      <c r="Q67" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="28" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>Cleveland Guardians offense vs Texas Rangers defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="29" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="29" t="inlineStr">
+      <c r="C70" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="29" t="inlineStr">
+      <c r="D70" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="29" t="inlineStr">
+      <c r="E70" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="29" t="inlineStr">
+      <c r="F70" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="29" t="inlineStr">
+      <c r="G70" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="29" t="inlineStr">
+      <c r="H70" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="29" t="inlineStr">
+      <c r="I70" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="29" t="inlineStr">
+      <c r="J70" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="29" t="inlineStr">
+      <c r="K70" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="29" t="inlineStr">
+      <c r="L70" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="29" t="inlineStr">
+      <c r="M70" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="29" t="inlineStr">
+      <c r="N70" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="29" t="inlineStr">
+      <c r="O70" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="29" t="inlineStr">
+      <c r="P70" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="29" t="inlineStr">
+      <c r="Q70" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C69" s="31" t="n">
-        <v>4.367</v>
-      </c>
-      <c r="D69" s="31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E69" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="F69" s="31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="G69" s="31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="I69" s="31" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="K69" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="L69" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M69" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N69" s="31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O69" s="31" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="P69" s="31" t="n">
-        <v>3.773</v>
-      </c>
-      <c r="Q69" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>7.308</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>7.733</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>7.267</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>7.769</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="O70" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>7.703</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>0.949</v>
+        <v>4</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>0.967</v>
+        <v>4.367</v>
       </c>
       <c r="D71" s="31" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="E71" s="31" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="F71" s="31" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="G71" s="31" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="H71" s="33" t="inlineStr">
         <is>
-          <t>26th</t>
+          <t>27th</t>
         </is>
       </c>
       <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="L71" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M71" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O71" s="31" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="P71" s="31" t="n">
+        <v>3.773</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>7.821</v>
+        <v>7.308</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>7.5</v>
+        <v>7.733</v>
       </c>
       <c r="D72" s="31" t="n">
-        <v>8.1</v>
+        <v>7.15</v>
       </c>
       <c r="E72" s="31" t="n">
-        <v>7.933</v>
+        <v>7.267</v>
       </c>
       <c r="F72" s="31" t="n">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
       <c r="G72" s="31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H72" s="32" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I72" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J72" s="33" t="inlineStr">
-        <is>
-          <t>23rd</t>
+        <v>5.4</v>
+      </c>
+      <c r="H72" s="33" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="I72" s="31" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>13th</t>
         </is>
       </c>
       <c r="K72" s="31" t="n">
         <v>7.4</v>
       </c>
       <c r="L72" s="31" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="M72" s="31" t="n">
-        <v>7.385</v>
+        <v>7.769</v>
       </c>
       <c r="N72" s="31" t="n">
-        <v>7.562</v>
+        <v>7.75</v>
       </c>
       <c r="O72" s="31" t="n">
-        <v>7.84</v>
+        <v>8</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>8.513999999999999</v>
+        <v>7.703</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>1st Inn R/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>0.641</v>
+        <v>0.949</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>0.767</v>
+        <v>0.967</v>
       </c>
       <c r="D73" s="31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E73" s="31" t="n">
         <v>0.8</v>
-      </c>
-      <c r="E73" s="31" t="n">
-        <v>0.867</v>
       </c>
       <c r="F73" s="31" t="n">
         <v>0.7</v>
       </c>
       <c r="G73" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr"/>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q73" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>7.821</v>
+      </c>
+      <c r="C74" s="31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D74" s="31" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E74" s="31" t="n">
+        <v>7.933</v>
+      </c>
+      <c r="F74" s="31" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="G74" s="31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H74" s="32" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L74" s="31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M74" s="31" t="n">
+        <v>7.385</v>
+      </c>
+      <c r="N74" s="31" t="n">
+        <v>7.562</v>
+      </c>
+      <c r="O74" s="31" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>8.513999999999999</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
+          <t>1st Inn R/G</t>
+        </is>
+      </c>
+      <c r="B75" s="31" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="C75" s="31" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="D75" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E75" s="31" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="F75" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G75" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="33" t="inlineStr">
+      <c r="H75" s="33" t="inlineStr">
         <is>
           <t>30th</t>
         </is>
       </c>
-      <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="33" t="inlineStr">
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="33" t="inlineStr">
         <is>
           <t>29th</t>
         </is>
       </c>
-      <c r="K73" s="31" t="n">
+      <c r="K75" s="31" t="n">
         <v>1.4</v>
       </c>
-      <c r="L73" s="31" t="n">
+      <c r="L75" s="31" t="n">
         <v>1.3</v>
       </c>
-      <c r="M73" s="31" t="n">
+      <c r="M75" s="31" t="n">
         <v>1.231</v>
       </c>
-      <c r="N73" s="31" t="n">
+      <c r="N75" s="31" t="n">
         <v>1.188</v>
       </c>
-      <c r="O73" s="31" t="n">
+      <c r="O75" s="31" t="n">
         <v>1.04</v>
       </c>
-      <c r="P73" s="31" t="n">
+      <c r="P75" s="31" t="n">
         <v>0.892</v>
       </c>
-      <c r="Q73" s="34" t="inlineStr">
+      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8139,10 +8139,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6879737089201877</v>
+        <v>0.6897774647887324</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-220</v>
+        <v>-222</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>-113</v>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 68.8% (fair -220). Your call.</t>
+          <t>Model 69.0% (fair -222). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8186,12 +8186,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>San Diego Padres @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8201,17 +8201,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Under 12</t>
+          <t>Under 11.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5832211538461538</v>
+        <v>0.6345499999999999</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-140</v>
+        <v>-174</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 63.5% (fair -174). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8247,37 +8247,37 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees -1.5</t>
+          <t>Under 12</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4086785714285715</v>
+        <v>0.5832211538461538</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>145</v>
+        <v>-140</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +145). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8313,37 +8313,37 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>New York Yankees -1.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6320348017621146</v>
+        <v>0.4086785714285715</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-172</v>
+        <v>145</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-127</v>
+        <v>180</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 63.2% (fair -172). Your call.</t>
+          <t>Model 40.9% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8379,37 +8379,37 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5718980392156862</v>
+        <v>0.5466346153846153</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-134</v>
+        <v>-121</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-104</v>
+        <v>108</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8450,12 +8450,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -8465,17 +8465,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.547843137254902</v>
+        <v>0.6284444444444445</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-121</v>
+        <v>-169</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>104</v>
+        <v>-125</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 62.8% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8516,12 +8516,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Boston Red Sox</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -8535,13 +8535,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.57645</v>
+        <v>0.5718980392156862</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-136</v>
+        <v>-134</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8582,32 +8582,32 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5644039215686274</v>
+        <v>0.4702941176470588</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-130</v>
+        <v>113</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-104</v>
+        <v>138</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -130). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8643,17 +8643,17 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4571487603305786</v>
+        <v>0.371571906354515</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>119</v>
+        <v>169</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>142</v>
+        <v>199</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 37.2% (fair +169). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8714,32 +8714,32 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4728755364806866</v>
+        <v>0.5644039215686274</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>111</v>
+        <v>-130</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>133</v>
+        <v>-104</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 56.4% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8775,37 +8775,37 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.506774193548387</v>
+        <v>0.4521311475409836</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-103</v>
+        <v>121</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8846,32 +8846,32 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Washington Nationals @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.3734693877551021</v>
+        <v>0.5712057692307693</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>168</v>
+        <v>-133</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>194</v>
+        <v>-108</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 37.3% (fair +168). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8907,17 +8907,17 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -8927,17 +8927,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5367647058823529</v>
+        <v>0.4599579831932774</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-116</v>
+        <v>117</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8973,17 +8973,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8993,17 +8993,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4808370044052863</v>
+        <v>0.5355392156862745</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>108</v>
+        <v>-115</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9039,37 +9039,37 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5227884615384615</v>
+        <v>0.4803964757709251</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-110</v>
+        <v>108</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9105,37 +9105,37 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4614893617021277</v>
+        <v>0.5238461538461537</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>117</v>
+        <v>-110</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9176,12 +9176,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9191,17 +9191,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5145673076923077</v>
+        <v>0.4395491803278689</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-106</v>
+        <v>128</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 44.0% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9237,37 +9237,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4410788381742738</v>
+        <v>0.53515</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>127</v>
+        <v>-115</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9318,22 +9318,22 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals +1.5</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.6269326530612244</v>
+        <v>0.5129326923076922</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-168</v>
+        <v>-105</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-145</v>
+        <v>108</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 62.7% (fair -168). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9369,37 +9369,37 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4864055299539171</v>
+        <v>0.5120673076923077</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>106</v>
+        <v>-105</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9459,13 +9459,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4476595744680851</v>
+        <v>0.4461344537815127</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9506,32 +9506,32 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5874449339207048</v>
+        <v>0.6269326530612244</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-142</v>
+        <v>-168</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-127</v>
+        <v>-145</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9555,7 +9555,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 62.7% (fair -168). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9572,32 +9572,32 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4468240343347639</v>
+        <v>0.4864055299539171</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9633,7 +9633,7 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
@@ -9653,17 +9653,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4585462555066079</v>
+        <v>0.5874449339207048</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>118</v>
+        <v>-142</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>127</v>
+        <v>-127</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9704,32 +9704,32 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers -1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4057421875</v>
+        <v>0.5523206572769952</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>146</v>
+        <v>-123</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>156</v>
+        <v>-113</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4628378378378379</v>
+        <v>0.4650900900900901</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>122</v>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9996,13 +9996,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5371666666666667</v>
+        <v>0.5348727272727273</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-116</v>
+        <v>-115</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-125</v>
+        <v>-120</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10134,7 +10134,7 @@
         <v>-110</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10200,7 +10200,7 @@
         <v>155</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -10266,7 +10266,7 @@
         <v>-155</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -10326,13 +10326,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.547843137254902</v>
+        <v>0.5466346153846153</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>-121</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10392,13 +10392,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4521450980392157</v>
+        <v>0.4533950495049505</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>121</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-104</v>
+        <v>-102</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10464,7 +10464,7 @@
         <v>103</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -10530,7 +10530,7 @@
         <v>-103</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -10722,13 +10722,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4585462555066079</v>
+        <v>0.4591150442477877</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>118</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5414563876651982</v>
+        <v>0.5408969162995595</v>
       </c>
       <c r="G18" s="14" t="n">
         <v>-118</v>
@@ -10860,7 +10860,7 @@
         <v>106</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10992,7 +10992,7 @@
         <v>162</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11058,7 +11058,7 @@
         <v>-162</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-122</v>
+        <v>-116</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11246,17 +11246,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.3375</v>
+        <v>0.46485</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>196</v>
+        <v>115</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 33.8% (fair +196). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -11312,14 +11312,14 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.6625</v>
+        <v>0.53515</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-196</v>
+        <v>-115</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>100</v>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 66.2% (fair -196). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -11388,7 +11388,7 @@
         <v>187</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -11718,7 +11718,7 @@
         <v>-109</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -11778,13 +11778,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4558590308370044</v>
+        <v>0.4737</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -11808,7 +11808,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11844,10 +11844,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5441347826086956</v>
+        <v>0.5263</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-119</v>
+        <v>-111</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>-130</v>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11910,13 +11910,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4571487603305786</v>
+        <v>0.4521311475409836</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11976,13 +11976,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5428454935622318</v>
+        <v>0.5479081967213115</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-119</v>
+        <v>-121</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-133</v>
+        <v>-144</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -12006,7 +12006,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12048,7 +12048,7 @@
         <v>161</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12114,7 +12114,7 @@
         <v>-161</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12180,7 +12180,7 @@
         <v>179</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12306,13 +12306,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.3679735682819383</v>
+        <v>0.3715765765765766</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 36.8% (fair +172). Your call.</t>
+          <t>Model 37.2% (fair +169). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -12372,13 +12372,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.6320348017621146</v>
+        <v>0.6284444444444445</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-172</v>
+        <v>-169</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-127</v>
+        <v>-125</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 63.2% (fair -172). Your call.</t>
+          <t>Model 62.8% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12444,7 +12444,7 @@
         <v>111</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -12510,7 +12510,7 @@
         <v>-111</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12576,7 +12576,7 @@
         <v>-133</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12642,7 +12642,7 @@
         <v>133</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-116</v>
+        <v>-119</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12702,13 +12702,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4030327868852459</v>
+        <v>0.4015384615384616</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12732,7 +12732,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 40.3% (fair +148). Your call.</t>
+          <t>Model 40.2% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12768,10 +12768,10 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5970098360655738</v>
+        <v>0.5984852459016393</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-148</v>
+        <v>-149</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>-144</v>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 59.7% (fair -148). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12830,17 +12830,17 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Over 12</t>
+          <t>Over 11.5</t>
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.1578</v>
+        <v>0.3654326923076923</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>534</v>
+        <v>174</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 15.8% (fair +534). Your call.</t>
+          <t>Model 36.5% (fair +174). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12896,14 +12896,14 @@
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>Under 12</t>
+          <t>Under 11.5</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.8422000000000001</v>
+        <v>0.6345499999999999</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-534</v>
+        <v>-174</v>
       </c>
       <c r="H50" s="15" t="n">
         <v>100</v>
@@ -12930,7 +12930,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 84.2% (fair -534). Your call.</t>
+          <t>Model 63.5% (fair -174). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12966,13 +12966,13 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4468240343347639</v>
+        <v>0.4533039647577092</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -12996,7 +12996,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13032,13 +13032,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5531794871794872</v>
+        <v>0.5467061946902656</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-124</v>
+        <v>-121</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>-134</v>
+        <v>-126</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13062,7 +13062,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13098,7 +13098,7 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4808370044052863</v>
+        <v>0.4803964757709251</v>
       </c>
       <c r="G53" s="14" t="n">
         <v>108</v>
@@ -13128,7 +13128,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13164,13 +13164,13 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5191646017699115</v>
+        <v>0.5195810572687225</v>
       </c>
       <c r="G54" s="14" t="n">
         <v>-108</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>-126</v>
+        <v>-127</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13434,7 +13434,7 @@
         <v>-183</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-122</v>
+        <v>-118</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13494,7 +13494,7 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5385072961373391</v>
+        <v>0.5400484978540773</v>
       </c>
       <c r="G59" s="14" t="n">
         <v>-117</v>
@@ -13524,7 +13524,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -13560,13 +13560,13 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4614893617021277</v>
+        <v>0.4599579831932774</v>
       </c>
       <c r="G60" s="14" t="n">
         <v>117</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -13590,7 +13590,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -13830,7 +13830,7 @@
         <v>-166</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -14274,13 +14274,13 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4476595744680851</v>
+        <v>0.4461344537815127</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H71" s="15" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
@@ -14304,7 +14304,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -14340,10 +14340,10 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5523478991596639</v>
+        <v>0.5538554621848739</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-123</v>
+        <v>-124</v>
       </c>
       <c r="H72" s="15" t="n">
         <v>-138</v>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -14406,13 +14406,13 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.506774193548387</v>
+        <v>0.5120673076923077</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-103</v>
+        <v>-105</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -14472,10 +14472,10 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4932173076923076</v>
+        <v>0.4879730769230769</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H74" s="15" t="n">
         <v>-108</v>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14544,7 +14544,7 @@
         <v>144</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -14670,10 +14670,10 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.5367647058823529</v>
+        <v>0.5355392156862745</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>-116</v>
+        <v>-115</v>
       </c>
       <c r="H77" s="15" t="n">
         <v>104</v>
@@ -14700,7 +14700,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14736,13 +14736,13 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.463235294117647</v>
+        <v>0.4645049504950495</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -14766,7 +14766,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15066,13 +15066,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.3734693877551021</v>
+        <v>0.371571906354515</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 37.3% (fair +168). Your call.</t>
+          <t>Model 37.2% (fair +169). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15132,10 +15132,10 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.6265408163265307</v>
+        <v>0.6283884353741497</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-168</v>
+        <v>-169</v>
       </c>
       <c r="H84" s="15" t="n">
         <v>-194</v>
@@ -15162,7 +15162,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 62.7% (fair -168). Your call.</t>
+          <t>Model 62.8% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15198,7 +15198,7 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.5227884615384615</v>
+        <v>0.5238461538461537</v>
       </c>
       <c r="G85" s="14" t="n">
         <v>-110</v>
@@ -15228,7 +15228,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15264,13 +15264,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.4771995305164319</v>
+        <v>0.476142654028436</v>
       </c>
       <c r="G86" s="14" t="n">
         <v>110</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-113</v>
+        <v>-111</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15330,13 +15330,13 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.4611059907834101</v>
+        <v>0.4634272300469484</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15396,10 +15396,10 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.5388953488372094</v>
+        <v>0.5365953488372094</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-117</v>
+        <v>-116</v>
       </c>
       <c r="H88" s="15" t="n">
         <v>-115</v>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16194,7 +16194,7 @@
         <v>-183</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -16326,7 +16326,7 @@
         <v>121</v>
       </c>
       <c r="H102" s="15" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I102" s="13">
         <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
@@ -16386,13 +16386,13 @@
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.4235483870967742</v>
+        <v>0.4287980769230769</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -16452,10 +16452,10 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.57645</v>
+        <v>0.5712057692307693</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>-136</v>
+        <v>-133</v>
       </c>
       <c r="H104" s="15" t="n">
         <v>-108</v>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -16650,13 +16650,13 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.4410788381742738</v>
+        <v>0.4395491803278689</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H107" s="15" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I107" s="13">
         <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
@@ -16680,7 +16680,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 44.0% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -16716,7 +16716,7 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.5589358024691359</v>
+        <v>0.5604069958847737</v>
       </c>
       <c r="G108" s="14" t="n">
         <v>-127</v>
@@ -16746,7 +16746,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -16914,7 +16914,7 @@
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.4017213114754098</v>
+        <v>0.4020491803278688</v>
       </c>
       <c r="G111" s="14" t="n">
         <v>149</v>
@@ -16980,13 +16980,13 @@
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.5982877551020408</v>
+        <v>0.5979540983606558</v>
       </c>
       <c r="G112" s="14" t="n">
         <v>-149</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>-145</v>
+        <v>-144</v>
       </c>
       <c r="I112" s="13">
         <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
@@ -17046,13 +17046,13 @@
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.4854288461538461</v>
+        <v>0.4870322274881516</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H113" s="15" t="n">
-        <v>-108</v>
+        <v>-111</v>
       </c>
       <c r="I113" s="13">
         <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17112,10 +17112,10 @@
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.5145673076923077</v>
+        <v>0.5129326923076922</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="H114" s="15" t="n">
         <v>108</v>
@@ -17142,7 +17142,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17574,10 +17574,10 @@
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.5498802816901408</v>
+        <v>0.5523206572769952</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>-122</v>
+        <v>-123</v>
       </c>
       <c r="H121" s="15" t="n">
         <v>-113</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -17640,13 +17640,13 @@
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.4500980392156863</v>
+        <v>0.4476923076923077</v>
       </c>
       <c r="G122" s="14" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H122" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I122" s="13">
         <f>IF($H$122="","",IF($H$122&lt;0,-$H$122/(-$H$122+100),100/($H$122+100)))</f>
@@ -17670,7 +17670,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -17706,13 +17706,13 @@
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>0.4728755364806866</v>
+        <v>0.4702941176470588</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H123" s="15" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I123" s="13">
         <f>IF($H$123="","",IF($H$123&lt;0,-$H$123/(-$H$123+100),100/($H$123+100)))</f>
@@ -17736,7 +17736,7 @@
       </c>
       <c r="N123" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O123" s="15" t="n"/>
@@ -17772,10 +17772,10 @@
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.5270999999999999</v>
+        <v>0.529725</v>
       </c>
       <c r="G124" s="14" t="n">
-        <v>-111</v>
+        <v>-113</v>
       </c>
       <c r="H124" s="15" t="n">
         <v>-140</v>
@@ -17802,7 +17802,7 @@
       </c>
       <c r="N124" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O124" s="15" t="n"/>
@@ -17970,13 +17970,13 @@
         </is>
       </c>
       <c r="F127" s="13" t="n">
-        <v>0.312</v>
+        <v>0.3101923076923077</v>
       </c>
       <c r="G127" s="14" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H127" s="15" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I127" s="13">
         <f>IF($H$127="","",IF($H$127&lt;0,-$H$127/(-$H$127+100),100/($H$127+100)))</f>
@@ -18000,7 +18000,7 @@
       </c>
       <c r="N127" s="19" t="inlineStr">
         <is>
-          <t>Model 31.2% (fair +221). Your call.</t>
+          <t>Model 31.0% (fair +222). Your call.</t>
         </is>
       </c>
       <c r="O127" s="15" t="n"/>
@@ -18036,10 +18036,10 @@
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.6879737089201877</v>
+        <v>0.6897774647887324</v>
       </c>
       <c r="G128" s="14" t="n">
-        <v>-220</v>
+        <v>-222</v>
       </c>
       <c r="H128" s="15" t="n">
         <v>-113</v>
@@ -18066,7 +18066,7 @@
       </c>
       <c r="N128" s="19" t="inlineStr">
         <is>
-          <t>Model 68.8% (fair -220). Your call.</t>
+          <t>Model 69.0% (fair -222). Your call.</t>
         </is>
       </c>
       <c r="O128" s="15" t="n"/>
@@ -18102,13 +18102,13 @@
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.4452422907488987</v>
+        <v>0.4420600858369099</v>
       </c>
       <c r="G129" s="14" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H129" s="15" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I129" s="13">
         <f>IF($H$129="","",IF($H$129&lt;0,-$H$129/(-$H$129+100),100/($H$129+100)))</f>
@@ -18132,7 +18132,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -18168,10 +18168,10 @@
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.5547831932773108</v>
+        <v>0.557972268907563</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>-125</v>
+        <v>-126</v>
       </c>
       <c r="H130" s="15" t="n">
         <v>-138</v>
@@ -18198,7 +18198,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>

--- a/data/output/workbook/2026-06-29.xlsx
+++ b/data/output/workbook/2026-06-29.xlsx
@@ -953,7 +953,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29 18:56</t>
+          <t>2026-06-29 20:06</t>
         </is>
       </c>
     </row>
@@ -8186,32 +8186,32 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Under 11.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6345499999999999</v>
+        <v>0.627090990990991</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-174</v>
+        <v>-168</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>100</v>
+        <v>-122</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 63.5% (fair -174). Your call.</t>
+          <t>Model 62.7% (fair -168). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8252,29 +8252,29 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Under 12</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5832211538461538</v>
+        <v>0.5466346153846153</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-140</v>
+        <v>-121</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>108</v>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8318,32 +8318,32 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Washington Nationals @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees -1.5</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4086785714285715</v>
+        <v>0.56645</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>145</v>
+        <v>-131</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +145). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8379,37 +8379,37 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>New York Yankees -1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5466346153846153</v>
+        <v>0.4103260869565218</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-121</v>
+        <v>144</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8450,12 +8450,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -8465,17 +8465,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6284444444444445</v>
+        <v>0.4492</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-169</v>
+        <v>123</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-125</v>
+        <v>150</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 62.8% (fair -169). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8709,37 +8709,37 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5644039215686274</v>
+        <v>0.455</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-130</v>
+        <v>120</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-104</v>
+        <v>144</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -130). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8775,37 +8775,37 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4521311475409836</v>
+        <v>0.5644039215686274</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>121</v>
+        <v>-130</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>144</v>
+        <v>-104</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 56.4% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8846,12 +8846,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Boston Red Sox</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8861,17 +8861,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5712057692307693</v>
+        <v>0.5266346153846153</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-133</v>
+        <v>-111</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-108</v>
+        <v>108</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8907,17 +8907,17 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -8927,17 +8927,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4599579831932774</v>
+        <v>0.5355392156862745</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>117</v>
+        <v>-115</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8973,17 +8973,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8993,17 +8993,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5355392156862745</v>
+        <v>0.4803964757709251</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-115</v>
+        <v>108</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -115). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9039,37 +9039,37 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4803964757709251</v>
+        <v>0.5213942307692307</v>
       </c>
       <c r="G19" s="14" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H19" s="15" t="n">
         <v>108</v>
-      </c>
-      <c r="H19" s="15" t="n">
-        <v>127</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9110,12 +9110,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9125,14 +9125,14 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5238461538461537</v>
+        <v>0.5167788461538462</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-110</v>
+        <v>-107</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>108</v>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4395491803278689</v>
+        <v>0.4399180327868852</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>144</v>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +128). Your call.</t>
+          <t>Model 44.0% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9237,37 +9237,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.53515</v>
+        <v>0.5157766990291262</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-115</v>
+        <v>-107</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9308,12 +9308,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -9323,17 +9323,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5129326923076922</v>
+        <v>0.4461344537815127</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-105</v>
+        <v>124</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9374,32 +9374,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5120673076923077</v>
+        <v>0.626577049180328</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-105</v>
+        <v>-168</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>108</v>
+        <v>-144</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 62.7% (fair -168). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9435,17 +9435,17 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -9455,17 +9455,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4461344537815127</v>
+        <v>0.4864055299539171</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9506,32 +9506,32 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals +1.5</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.6269326530612244</v>
+        <v>0.5874449339207048</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-168</v>
+        <v>-142</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-145</v>
+        <v>-127</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9555,7 +9555,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 62.7% (fair -168). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9572,12 +9572,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -9587,17 +9587,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4864055299539171</v>
+        <v>0.4580263157894736</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9638,32 +9638,32 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5874449339207048</v>
+        <v>0.5523206572769952</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-142</v>
+        <v>-123</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-127</v>
+        <v>-113</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9699,37 +9699,37 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5523206572769952</v>
+        <v>0.4650900900900901</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-123</v>
+        <v>115</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-113</v>
+        <v>122</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10058,14 +10058,14 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4763</v>
+        <v>0.576</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>110</v>
+        <v>-136</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>113</v>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10124,17 +10124,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.424</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-110</v>
+        <v>136</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10266,7 +10266,7 @@
         <v>-155</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -10722,13 +10722,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4591150442477877</v>
+        <v>0.4580263157894736</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>118</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5408969162995595</v>
+        <v>0.5419599118942732</v>
       </c>
       <c r="G18" s="14" t="n">
         <v>-118</v>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10860,7 +10860,7 @@
         <v>106</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>100</v>
+        <v>-105</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -11058,7 +11058,7 @@
         <v>-162</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-116</v>
+        <v>-113</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11246,17 +11246,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.46485</v>
+        <v>0.3375</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>115</v>
+        <v>196</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 33.8% (fair +196). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -11312,14 +11312,14 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.53515</v>
+        <v>0.6625</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-115</v>
+        <v>-196</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>100</v>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 66.2% (fair -196). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -11520,7 +11520,7 @@
         <v>157</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11642,14 +11642,14 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4783</v>
+        <v>0.5783</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>109</v>
+        <v>-137</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>113</v>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -11708,17 +11708,17 @@
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.4217</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-109</v>
+        <v>137</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -11742,7 +11742,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -11784,7 +11784,7 @@
         <v>111</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -11850,7 +11850,7 @@
         <v>-111</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-130</v>
+        <v>107</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11910,13 +11910,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4521311475409836</v>
+        <v>0.4492</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11976,10 +11976,10 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5479081967213115</v>
+        <v>0.5508000000000001</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-121</v>
+        <v>-123</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>-144</v>
@@ -12006,7 +12006,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12038,17 +12038,17 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.3837</v>
+        <v>0.4625</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>112</v>
+        <v>-104</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12072,7 +12072,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 38.4% (fair +161). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12104,17 +12104,17 @@
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.6163000000000001</v>
+        <v>0.5375</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-161</v>
+        <v>-116</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -161). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12306,10 +12306,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.3715765765765766</v>
+        <v>0.3729279279279279</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>122</v>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 37.2% (fair +169). Your call.</t>
+          <t>Model 37.3% (fair +168). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -12372,13 +12372,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.6284444444444445</v>
+        <v>0.627090990990991</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-169</v>
+        <v>-168</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-125</v>
+        <v>-122</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 62.8% (fair -169). Your call.</t>
+          <t>Model 62.7% (fair -168). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12510,7 +12510,7 @@
         <v>-111</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12642,7 +12642,7 @@
         <v>133</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-119</v>
+        <v>138</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12834,13 +12834,13 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.3654326923076923</v>
+        <v>0.2407</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>174</v>
+        <v>315</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 36.5% (fair +174). Your call.</t>
+          <t>Model 24.1% (fair +315). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12900,13 +12900,13 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.6345499999999999</v>
+        <v>0.7593</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-174</v>
+        <v>-315</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -12930,7 +12930,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 63.5% (fair -174). Your call.</t>
+          <t>Model 75.9% (fair -315). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12966,7 +12966,7 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4533039647577092</v>
+        <v>0.4516299559471365</v>
       </c>
       <c r="G51" s="14" t="n">
         <v>121</v>
@@ -12996,7 +12996,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13032,13 +13032,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5467061946902656</v>
+        <v>0.5483739130434783</v>
       </c>
       <c r="G52" s="14" t="n">
         <v>-121</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>-126</v>
+        <v>-130</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13062,7 +13062,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13236,7 +13236,7 @@
         <v>107</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13302,7 +13302,7 @@
         <v>-107</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -13494,13 +13494,13 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5400484978540773</v>
+        <v>0.5449840336134453</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>-117</v>
+        <v>-120</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>-133</v>
+        <v>-138</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -13524,7 +13524,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -13560,13 +13560,13 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4599579831932774</v>
+        <v>0.455</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -13590,7 +13590,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -13626,13 +13626,13 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4167694581280788</v>
+        <v>0.3201</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>140</v>
+        <v>212</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>-103</v>
+        <v>106</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -13656,7 +13656,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 41.7% (fair +140). Your call.</t>
+          <t>Model 32.0% (fair +212). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -13692,10 +13692,10 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5832211538461538</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-140</v>
+        <v>-212</v>
       </c>
       <c r="H62" s="15" t="n">
         <v>108</v>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 68.0% (fair -212). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -13830,7 +13830,7 @@
         <v>-166</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -14406,10 +14406,10 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5120673076923077</v>
+        <v>0.5167788461538462</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-105</v>
+        <v>-107</v>
       </c>
       <c r="H73" s="15" t="n">
         <v>108</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4879730769230769</v>
+        <v>0.48325</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>-108</v>
+        <v>100</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14610,7 +14610,7 @@
         <v>-144</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -14934,10 +14934,10 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5942372623574145</v>
+        <v>0.5914482889733841</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-146</v>
+        <v>-145</v>
       </c>
       <c r="H81" s="15" t="n">
         <v>-163</v>
@@ -14964,7 +14964,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -146). Your call.</t>
+          <t>Model 59.1% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15000,13 +15000,13 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4057421875</v>
+        <v>0.40856</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -15030,7 +15030,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 40.9% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15198,10 +15198,10 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.5238461538461537</v>
+        <v>0.5266346153846153</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="H85" s="15" t="n">
         <v>108</v>
@@ -15228,7 +15228,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15264,13 +15264,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.476142654028436</v>
+        <v>0.4733980582524272</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-111</v>
+        <v>-106</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15594,7 +15594,7 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.4914903846153846</v>
+        <v>0.4935096153846154</v>
       </c>
       <c r="G91" s="14" t="n">
         <v>103</v>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +103). Your call.</t>
+          <t>Model 49.4% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15660,13 +15660,13 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5084917050691244</v>
+        <v>0.5064840375586854</v>
       </c>
       <c r="G92" s="14" t="n">
         <v>-103</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>-117</v>
+        <v>-113</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 50.6% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -15726,13 +15726,13 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.4086785714285715</v>
+        <v>0.4103260869565218</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -15756,7 +15756,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +145). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15792,10 +15792,10 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.5913057553956834</v>
+        <v>0.5896410071942446</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-145</v>
+        <v>-144</v>
       </c>
       <c r="H94" s="15" t="n">
         <v>-178</v>
@@ -15822,7 +15822,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -145). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -15930,7 +15930,7 @@
         <v>102</v>
       </c>
       <c r="H96" s="15" t="n">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -15986,17 +15986,17 @@
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.4414</v>
+        <v>0.4785951219512195</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>104</v>
+        <v>-105</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -16020,7 +16020,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16052,14 +16052,14 @@
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.5586</v>
+        <v>0.5213942307692307</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-127</v>
+        <v>-109</v>
       </c>
       <c r="H98" s="15" t="n">
         <v>108</v>
@@ -16086,7 +16086,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16194,7 +16194,7 @@
         <v>-183</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -16260,7 +16260,7 @@
         <v>-121</v>
       </c>
       <c r="H101" s="15" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
@@ -16386,10 +16386,10 @@
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.4287980769230769</v>
+        <v>0.4335096153846154</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H103" s="15" t="n">
         <v>108</v>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -16452,13 +16452,13 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.5712057692307693</v>
+        <v>0.56645</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>-133</v>
+        <v>-131</v>
       </c>
       <c r="H104" s="15" t="n">
-        <v>-108</v>
+        <v>100</v>
       </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -16518,13 +16518,13 @@
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.3563461538461538</v>
+        <v>0.3297</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -16548,7 +16548,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 35.6% (fair +181). Your call.</t>
+          <t>Model 33.0% (fair +203). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -16584,13 +16584,13 @@
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.6436330798479087</v>
+        <v>0.6703</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>-181</v>
+        <v>-203</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>-163</v>
+        <v>156</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -16614,7 +16614,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 67.0% (fair -203). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -16650,10 +16650,10 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.4395491803278689</v>
+        <v>0.4399180327868852</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H107" s="15" t="n">
         <v>144</v>
@@ -16680,7 +16680,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +128). Your call.</t>
+          <t>Model 44.0% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -16716,13 +16716,13 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.5604069958847737</v>
+        <v>0.5600785123966943</v>
       </c>
       <c r="G108" s="14" t="n">
         <v>-127</v>
       </c>
       <c r="H108" s="15" t="n">
-        <v>-143</v>
+        <v>-142</v>
       </c>
       <c r="I108" s="13">
         <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
@@ -17046,13 +17046,13 @@
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.4870322274881516</v>
+        <v>0.4842346153846154</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H113" s="15" t="n">
-        <v>-111</v>
+        <v>-108</v>
       </c>
       <c r="I113" s="13">
         <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17112,13 +17112,13 @@
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.5129326923076922</v>
+        <v>0.5157766990291262</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>-105</v>
+        <v>-107</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -17142,7 +17142,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.6269326530612244</v>
+        <v>0.626577049180328</v>
       </c>
       <c r="G117" s="14" t="n">
         <v>-168</v>
       </c>
       <c r="H117" s="15" t="n">
-        <v>-145</v>
+        <v>-144</v>
       </c>
       <c r="I117" s="13">
         <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
@@ -17376,7 +17376,7 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.373109243697479</v>
+        <v>0.3734453781512606</v>
       </c>
       <c r="G118" s="14" t="n">
         <v>168</v>
@@ -17442,13 +17442,13 @@
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.3613688212927757</v>
+        <v>0.3627307692307692</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H119" s="15" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I119" s="13">
         <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
@@ -17472,7 +17472,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 36.1% (fair +177). Your call.</t>
+          <t>Model 36.3% (fair +176). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -17508,10 +17508,10 @@
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.638612927756654</v>
+        <v>0.6373114068441065</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>-177</v>
+        <v>-176</v>
       </c>
       <c r="H120" s="15" t="n">
         <v>-163</v>
@@ -17538,7 +17538,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 63.9% (fair -177). Your call.</t>
+          <t>Model 63.7% (fair -176). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
